--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>113354383</v>
       </c>
       <c r="B3" t="n">
-        <v>90040</v>
+        <v>90056</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113399427</v>
+        <v>113399434</v>
       </c>
       <c r="B5" t="n">
         <v>56781</v>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>286422</v>
+        <v>286601</v>
       </c>
       <c r="R5" t="n">
-        <v>6508051</v>
+        <v>6508623</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113399464</v>
+        <v>113399425</v>
       </c>
       <c r="B6" t="n">
-        <v>94092</v>
+        <v>56781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>286444</v>
+        <v>286469</v>
       </c>
       <c r="R6" t="n">
-        <v>6508165</v>
+        <v>6508059</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1180,6 +1180,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,7 +1211,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113399441</v>
+        <v>113399442</v>
       </c>
       <c r="B7" t="n">
         <v>56781</v>
@@ -1246,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>286510</v>
+        <v>286541</v>
       </c>
       <c r="R7" t="n">
-        <v>6508675</v>
+        <v>6508510</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1286,7 +1291,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113399442</v>
+        <v>113399463</v>
       </c>
       <c r="B8" t="n">
-        <v>56781</v>
+        <v>99570</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,25 +1330,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1353,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>286541</v>
+        <v>286229</v>
       </c>
       <c r="R8" t="n">
-        <v>6508510</v>
+        <v>6507839</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,11 +1394,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,7 +1420,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399430</v>
+        <v>113399441</v>
       </c>
       <c r="B9" t="n">
         <v>56781</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>286476</v>
+        <v>286510</v>
       </c>
       <c r="R9" t="n">
-        <v>6508348</v>
+        <v>6508675</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399419</v>
+        <v>113399420</v>
       </c>
       <c r="B10" t="n">
         <v>56781</v>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>286311</v>
+        <v>286325</v>
       </c>
       <c r="R10" t="n">
-        <v>6507585</v>
+        <v>6507609</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399433</v>
+        <v>113399432</v>
       </c>
       <c r="B11" t="n">
         <v>56781</v>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>286505</v>
+        <v>286495</v>
       </c>
       <c r="R11" t="n">
-        <v>6508433</v>
+        <v>6508424</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399405</v>
+        <v>113399449</v>
       </c>
       <c r="B12" t="n">
-        <v>93739</v>
+        <v>91329</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,25 +1753,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2810</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>286655</v>
+        <v>286530</v>
       </c>
       <c r="R12" t="n">
-        <v>6508854</v>
+        <v>6508258</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113399413</v>
+        <v>113399456</v>
       </c>
       <c r="B13" t="n">
-        <v>56781</v>
+        <v>95950</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,25 +1855,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>286327</v>
+        <v>286522</v>
       </c>
       <c r="R13" t="n">
-        <v>6508012</v>
+        <v>6508764</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1919,11 +1919,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1950,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113399463</v>
+        <v>113399459</v>
       </c>
       <c r="B14" t="n">
-        <v>99554</v>
+        <v>95950</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,21 +1961,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>2606</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>286229</v>
+        <v>286600</v>
       </c>
       <c r="R14" t="n">
-        <v>6507839</v>
+        <v>6508882</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2052,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399459</v>
+        <v>113399409</v>
       </c>
       <c r="B15" t="n">
-        <v>95934</v>
+        <v>56765</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2064,25 +2059,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2606</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2092,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>286600</v>
+        <v>286461</v>
       </c>
       <c r="R15" t="n">
-        <v>6508882</v>
+        <v>6508704</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2128,6 +2123,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2154,7 +2154,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399432</v>
+        <v>113399427</v>
       </c>
       <c r="B16" t="n">
         <v>56781</v>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>286495</v>
+        <v>286422</v>
       </c>
       <c r="R16" t="n">
-        <v>6508424</v>
+        <v>6508051</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2261,7 +2261,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399425</v>
+        <v>113399435</v>
       </c>
       <c r="B17" t="n">
         <v>56781</v>
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>286469</v>
+        <v>286667</v>
       </c>
       <c r="R17" t="n">
-        <v>6508059</v>
+        <v>6508726</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399423</v>
+        <v>113399433</v>
       </c>
       <c r="B18" t="n">
         <v>56781</v>
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>286426</v>
+        <v>286505</v>
       </c>
       <c r="R18" t="n">
-        <v>6507790</v>
+        <v>6508433</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2475,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399440</v>
+        <v>113399405</v>
       </c>
       <c r="B19" t="n">
-        <v>56781</v>
+        <v>93755</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2487,25 +2487,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>286483</v>
+        <v>286655</v>
       </c>
       <c r="R19" t="n">
-        <v>6508722</v>
+        <v>6508854</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2551,11 +2551,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2582,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399439</v>
+        <v>113399404</v>
       </c>
       <c r="B20" t="n">
-        <v>56781</v>
+        <v>93755</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2594,25 +2589,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2622,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>286834</v>
+        <v>286719</v>
       </c>
       <c r="R20" t="n">
-        <v>6508948</v>
+        <v>6508879</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2658,11 +2653,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2689,10 +2679,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113399409</v>
+        <v>113399457</v>
       </c>
       <c r="B21" t="n">
-        <v>56765</v>
+        <v>95950</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2691,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>2606</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2719,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>286461</v>
+        <v>286398</v>
       </c>
       <c r="R21" t="n">
-        <v>6508704</v>
+        <v>6508131</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2765,11 +2755,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2796,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113399408</v>
+        <v>113399455</v>
       </c>
       <c r="B22" t="n">
-        <v>56765</v>
+        <v>95950</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2808,25 +2793,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2606</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2836,10 +2821,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>286479</v>
+        <v>286525</v>
       </c>
       <c r="R22" t="n">
-        <v>6508372</v>
+        <v>6508767</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2872,11 +2857,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3010,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113399412</v>
+        <v>113399430</v>
       </c>
       <c r="B24" t="n">
-        <v>95574</v>
+        <v>56781</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3022,25 +3002,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3050,10 +3030,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>286668</v>
+        <v>286476</v>
       </c>
       <c r="R24" t="n">
-        <v>6508839</v>
+        <v>6508348</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3086,6 +3066,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3112,7 +3097,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113399426</v>
+        <v>113399423</v>
       </c>
       <c r="B25" t="n">
         <v>56781</v>
@@ -3152,10 +3137,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>286454</v>
+        <v>286426</v>
       </c>
       <c r="R25" t="n">
-        <v>6508073</v>
+        <v>6507790</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3219,10 +3204,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113399448</v>
+        <v>113399418</v>
       </c>
       <c r="B26" t="n">
-        <v>91313</v>
+        <v>56781</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3235,21 +3220,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3259,10 +3244,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>286525</v>
+        <v>286273</v>
       </c>
       <c r="R26" t="n">
-        <v>6508258</v>
+        <v>6507549</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3299,7 +3284,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>9 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3326,7 +3311,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113399428</v>
+        <v>113399443</v>
       </c>
       <c r="B27" t="n">
         <v>56781</v>
@@ -3366,10 +3351,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>286459</v>
+        <v>286465</v>
       </c>
       <c r="R27" t="n">
-        <v>6508160</v>
+        <v>6508688</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3406,7 +3391,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3433,10 +3418,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113399429</v>
+        <v>113399464</v>
       </c>
       <c r="B28" t="n">
-        <v>56781</v>
+        <v>94108</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3445,25 +3430,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3473,10 +3458,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>286485</v>
+        <v>286444</v>
       </c>
       <c r="R28" t="n">
-        <v>6508336</v>
+        <v>6508165</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3509,11 +3494,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3540,7 +3520,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113399443</v>
+        <v>113399424</v>
       </c>
       <c r="B29" t="n">
         <v>56781</v>
@@ -3580,10 +3560,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>286465</v>
+        <v>286495</v>
       </c>
       <c r="R29" t="n">
-        <v>6508688</v>
+        <v>6508076</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3620,7 +3600,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3647,10 +3627,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113399410</v>
+        <v>113399411</v>
       </c>
       <c r="B30" t="n">
-        <v>95574</v>
+        <v>95590</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3687,10 +3667,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>286724</v>
+        <v>286712</v>
       </c>
       <c r="R30" t="n">
-        <v>6508823</v>
+        <v>6508906</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3752,7 +3732,7 @@
         <v>113399458</v>
       </c>
       <c r="B31" t="n">
-        <v>95934</v>
+        <v>95950</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3851,7 +3831,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113399437</v>
+        <v>113399413</v>
       </c>
       <c r="B32" t="n">
         <v>56781</v>
@@ -3891,10 +3871,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>286715</v>
+        <v>286327</v>
       </c>
       <c r="R32" t="n">
-        <v>6508776</v>
+        <v>6508012</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3958,10 +3938,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113399411</v>
+        <v>113399426</v>
       </c>
       <c r="B33" t="n">
-        <v>95574</v>
+        <v>56781</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3970,25 +3950,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3998,10 +3978,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>286712</v>
+        <v>286454</v>
       </c>
       <c r="R33" t="n">
-        <v>6508906</v>
+        <v>6508073</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4034,6 +4014,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4060,7 +4045,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113399438</v>
+        <v>113399428</v>
       </c>
       <c r="B34" t="n">
         <v>56781</v>
@@ -4100,10 +4085,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>286835</v>
+        <v>286459</v>
       </c>
       <c r="R34" t="n">
-        <v>6508956</v>
+        <v>6508160</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4167,7 +4152,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113399418</v>
+        <v>113399419</v>
       </c>
       <c r="B35" t="n">
         <v>56781</v>
@@ -4207,10 +4192,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>286273</v>
+        <v>286311</v>
       </c>
       <c r="R35" t="n">
-        <v>6507549</v>
+        <v>6507585</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4274,10 +4259,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113399457</v>
+        <v>113399417</v>
       </c>
       <c r="B36" t="n">
-        <v>95934</v>
+        <v>56781</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4286,25 +4271,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4314,10 +4299,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>286398</v>
+        <v>286266</v>
       </c>
       <c r="R36" t="n">
-        <v>6508131</v>
+        <v>6507549</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4350,6 +4335,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4376,7 +4366,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113399420</v>
+        <v>113399422</v>
       </c>
       <c r="B37" t="n">
         <v>56781</v>
@@ -4416,10 +4406,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>286325</v>
+        <v>286408</v>
       </c>
       <c r="R37" t="n">
-        <v>6507609</v>
+        <v>6507718</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4483,7 +4473,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113399417</v>
+        <v>113399437</v>
       </c>
       <c r="B38" t="n">
         <v>56781</v>
@@ -4523,10 +4513,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>286266</v>
+        <v>286715</v>
       </c>
       <c r="R38" t="n">
-        <v>6507549</v>
+        <v>6508776</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4590,7 +4580,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113399435</v>
+        <v>113399436</v>
       </c>
       <c r="B39" t="n">
         <v>56781</v>
@@ -4630,10 +4620,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>286667</v>
+        <v>286684</v>
       </c>
       <c r="R39" t="n">
-        <v>6508726</v>
+        <v>6508737</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4697,10 +4687,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113399434</v>
+        <v>113399448</v>
       </c>
       <c r="B40" t="n">
-        <v>56781</v>
+        <v>91329</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4713,21 +4703,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4737,10 +4727,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>286601</v>
+        <v>286525</v>
       </c>
       <c r="R40" t="n">
-        <v>6508623</v>
+        <v>6508258</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4777,7 +4767,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4804,10 +4794,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113399461</v>
+        <v>113399460</v>
       </c>
       <c r="B41" t="n">
-        <v>99554</v>
+        <v>95950</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4820,21 +4810,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>2606</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4844,10 +4834,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>286239</v>
+        <v>286595</v>
       </c>
       <c r="R41" t="n">
-        <v>6507778</v>
+        <v>6508872</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4906,10 +4896,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113399460</v>
+        <v>113399461</v>
       </c>
       <c r="B42" t="n">
-        <v>95934</v>
+        <v>99570</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4922,21 +4912,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2606</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4946,10 +4936,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>286595</v>
+        <v>286239</v>
       </c>
       <c r="R42" t="n">
-        <v>6508872</v>
+        <v>6507778</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5008,7 +4998,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399424</v>
+        <v>113399440</v>
       </c>
       <c r="B43" t="n">
         <v>56781</v>
@@ -5048,10 +5038,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286495</v>
+        <v>286483</v>
       </c>
       <c r="R43" t="n">
-        <v>6508076</v>
+        <v>6508722</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5115,10 +5105,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399455</v>
+        <v>113399439</v>
       </c>
       <c r="B44" t="n">
-        <v>95934</v>
+        <v>56781</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5127,25 +5117,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5155,10 +5145,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>286525</v>
+        <v>286834</v>
       </c>
       <c r="R44" t="n">
-        <v>6508767</v>
+        <v>6508948</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5191,6 +5181,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5217,10 +5212,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113399436</v>
+        <v>113399412</v>
       </c>
       <c r="B45" t="n">
-        <v>56781</v>
+        <v>95590</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5229,25 +5224,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5257,10 +5252,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>286684</v>
+        <v>286668</v>
       </c>
       <c r="R45" t="n">
-        <v>6508737</v>
+        <v>6508839</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5293,11 +5288,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5324,10 +5314,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113399421</v>
+        <v>113399410</v>
       </c>
       <c r="B46" t="n">
-        <v>56781</v>
+        <v>95590</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5336,25 +5326,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5364,10 +5354,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>286411</v>
+        <v>286724</v>
       </c>
       <c r="R46" t="n">
-        <v>6507674</v>
+        <v>6508823</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5400,11 +5390,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5431,10 +5416,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113399456</v>
+        <v>113399438</v>
       </c>
       <c r="B47" t="n">
-        <v>95934</v>
+        <v>56781</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5443,25 +5428,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5471,10 +5456,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>286522</v>
+        <v>286835</v>
       </c>
       <c r="R47" t="n">
-        <v>6508764</v>
+        <v>6508956</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5507,6 +5492,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5533,7 +5523,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113399422</v>
+        <v>113399421</v>
       </c>
       <c r="B48" t="n">
         <v>56781</v>
@@ -5573,10 +5563,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>286408</v>
+        <v>286411</v>
       </c>
       <c r="R48" t="n">
-        <v>6507718</v>
+        <v>6507674</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5640,10 +5630,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113399449</v>
+        <v>113399429</v>
       </c>
       <c r="B49" t="n">
-        <v>91313</v>
+        <v>56781</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5656,21 +5646,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5680,10 +5670,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>286530</v>
+        <v>286485</v>
       </c>
       <c r="R49" t="n">
-        <v>6508258</v>
+        <v>6508336</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5716,6 +5706,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5742,10 +5737,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113399404</v>
+        <v>113399408</v>
       </c>
       <c r="B50" t="n">
-        <v>93739</v>
+        <v>56765</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5754,25 +5749,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2810</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5782,10 +5777,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>286719</v>
+        <v>286479</v>
       </c>
       <c r="R50" t="n">
-        <v>6508879</v>
+        <v>6508372</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5818,6 +5813,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -4896,10 +4896,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113399461</v>
+        <v>113399440</v>
       </c>
       <c r="B42" t="n">
-        <v>99570</v>
+        <v>56781</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4908,25 +4908,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>286239</v>
+        <v>286483</v>
       </c>
       <c r="R42" t="n">
-        <v>6507778</v>
+        <v>6508722</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4972,6 +4972,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4998,7 +5003,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399440</v>
+        <v>113399439</v>
       </c>
       <c r="B43" t="n">
         <v>56781</v>
@@ -5038,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286483</v>
+        <v>286834</v>
       </c>
       <c r="R43" t="n">
-        <v>6508722</v>
+        <v>6508948</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5105,10 +5110,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399439</v>
+        <v>113399461</v>
       </c>
       <c r="B44" t="n">
-        <v>56781</v>
+        <v>99570</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5117,25 +5122,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5145,10 +5150,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>286834</v>
+        <v>286239</v>
       </c>
       <c r="R44" t="n">
-        <v>6508948</v>
+        <v>6507778</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5181,11 +5186,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113399414</v>
+        <v>113399449</v>
       </c>
       <c r="B4" t="n">
-        <v>56781</v>
+        <v>91329</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>286242</v>
+        <v>286530</v>
       </c>
       <c r="R4" t="n">
-        <v>6507840</v>
+        <v>6508258</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,11 +966,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,7 +992,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113399434</v>
+        <v>113399419</v>
       </c>
       <c r="B5" t="n">
         <v>56781</v>
@@ -1037,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>286601</v>
+        <v>286311</v>
       </c>
       <c r="R5" t="n">
-        <v>6508623</v>
+        <v>6507585</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113399425</v>
+        <v>113399463</v>
       </c>
       <c r="B6" t="n">
-        <v>56781</v>
+        <v>99570</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>286469</v>
+        <v>286229</v>
       </c>
       <c r="R6" t="n">
-        <v>6508059</v>
+        <v>6507839</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1180,11 +1175,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113399442</v>
+        <v>113399448</v>
       </c>
       <c r="B7" t="n">
-        <v>56781</v>
+        <v>91329</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,21 +1217,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>286541</v>
+        <v>286525</v>
       </c>
       <c r="R7" t="n">
-        <v>6508510</v>
+        <v>6508258</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1291,7 +1281,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,10 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113399463</v>
+        <v>113399404</v>
       </c>
       <c r="B8" t="n">
-        <v>99570</v>
+        <v>93755</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1334,21 +1324,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1358,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>286229</v>
+        <v>286719</v>
       </c>
       <c r="R8" t="n">
-        <v>6507839</v>
+        <v>6508879</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1420,7 +1410,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399441</v>
+        <v>113399433</v>
       </c>
       <c r="B9" t="n">
         <v>56781</v>
@@ -1460,10 +1450,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>286510</v>
+        <v>286505</v>
       </c>
       <c r="R9" t="n">
-        <v>6508675</v>
+        <v>6508433</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1527,7 +1517,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399420</v>
+        <v>113399439</v>
       </c>
       <c r="B10" t="n">
         <v>56781</v>
@@ -1567,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>286325</v>
+        <v>286834</v>
       </c>
       <c r="R10" t="n">
-        <v>6507609</v>
+        <v>6508948</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1634,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399432</v>
+        <v>113399455</v>
       </c>
       <c r="B11" t="n">
-        <v>56781</v>
+        <v>95950</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1636,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>286495</v>
+        <v>286525</v>
       </c>
       <c r="R11" t="n">
-        <v>6508424</v>
+        <v>6508767</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1710,11 +1700,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,10 +1726,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399449</v>
+        <v>113399420</v>
       </c>
       <c r="B12" t="n">
-        <v>91329</v>
+        <v>56781</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,21 +1742,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>286530</v>
+        <v>286325</v>
       </c>
       <c r="R12" t="n">
-        <v>6508258</v>
+        <v>6507609</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1817,6 +1802,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113399456</v>
+        <v>113399421</v>
       </c>
       <c r="B13" t="n">
-        <v>95950</v>
+        <v>56781</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,25 +1845,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1873,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>286522</v>
+        <v>286411</v>
       </c>
       <c r="R13" t="n">
-        <v>6508764</v>
+        <v>6507674</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1919,6 +1909,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1945,10 +1940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113399459</v>
+        <v>113399443</v>
       </c>
       <c r="B14" t="n">
-        <v>95950</v>
+        <v>56781</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,25 +1952,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>286600</v>
+        <v>286465</v>
       </c>
       <c r="R14" t="n">
-        <v>6508882</v>
+        <v>6508688</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2021,6 +2016,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,10 +2154,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399427</v>
+        <v>113399411</v>
       </c>
       <c r="B16" t="n">
-        <v>56781</v>
+        <v>95590</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2166,25 +2166,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>286422</v>
+        <v>286712</v>
       </c>
       <c r="R16" t="n">
-        <v>6508051</v>
+        <v>6508906</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2230,11 +2230,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2261,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399435</v>
+        <v>113399412</v>
       </c>
       <c r="B17" t="n">
-        <v>56781</v>
+        <v>95590</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2273,25 +2268,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2301,10 +2296,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>286667</v>
+        <v>286668</v>
       </c>
       <c r="R17" t="n">
-        <v>6508726</v>
+        <v>6508839</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2337,11 +2332,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2368,10 +2358,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399433</v>
+        <v>113399459</v>
       </c>
       <c r="B18" t="n">
-        <v>56781</v>
+        <v>95950</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2380,25 +2370,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2408,10 +2398,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>286505</v>
+        <v>286600</v>
       </c>
       <c r="R18" t="n">
-        <v>6508433</v>
+        <v>6508882</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2444,11 +2434,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2475,10 +2460,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399405</v>
+        <v>113399458</v>
       </c>
       <c r="B19" t="n">
-        <v>93755</v>
+        <v>95950</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,21 +2476,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2515,10 +2500,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>286655</v>
+        <v>286751</v>
       </c>
       <c r="R19" t="n">
-        <v>6508854</v>
+        <v>6508904</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2577,10 +2562,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399404</v>
+        <v>113399461</v>
       </c>
       <c r="B20" t="n">
-        <v>93755</v>
+        <v>99570</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2593,21 +2578,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2810</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2617,10 +2602,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>286719</v>
+        <v>286239</v>
       </c>
       <c r="R20" t="n">
-        <v>6508879</v>
+        <v>6507778</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2679,10 +2664,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113399457</v>
+        <v>113399417</v>
       </c>
       <c r="B21" t="n">
-        <v>95950</v>
+        <v>56781</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2691,25 +2676,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2719,10 +2704,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>286398</v>
+        <v>286266</v>
       </c>
       <c r="R21" t="n">
-        <v>6508131</v>
+        <v>6507549</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2755,6 +2740,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2781,10 +2771,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113399455</v>
+        <v>113399464</v>
       </c>
       <c r="B22" t="n">
-        <v>95950</v>
+        <v>94108</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2797,21 +2787,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2606</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2821,10 +2811,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>286525</v>
+        <v>286444</v>
       </c>
       <c r="R22" t="n">
-        <v>6508767</v>
+        <v>6508165</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2883,7 +2873,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113399431</v>
+        <v>113399434</v>
       </c>
       <c r="B23" t="n">
         <v>56781</v>
@@ -2923,10 +2913,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>286459</v>
+        <v>286601</v>
       </c>
       <c r="R23" t="n">
-        <v>6508392</v>
+        <v>6508623</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2990,7 +2980,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113399430</v>
+        <v>113399432</v>
       </c>
       <c r="B24" t="n">
         <v>56781</v>
@@ -3030,10 +3020,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>286476</v>
+        <v>286495</v>
       </c>
       <c r="R24" t="n">
-        <v>6508348</v>
+        <v>6508424</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3097,10 +3087,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113399423</v>
+        <v>113399405</v>
       </c>
       <c r="B25" t="n">
-        <v>56781</v>
+        <v>93755</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3109,25 +3099,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3137,10 +3127,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>286426</v>
+        <v>286655</v>
       </c>
       <c r="R25" t="n">
-        <v>6507790</v>
+        <v>6508854</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3173,11 +3163,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3204,7 +3189,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113399418</v>
+        <v>113399435</v>
       </c>
       <c r="B26" t="n">
         <v>56781</v>
@@ -3244,10 +3229,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>286273</v>
+        <v>286667</v>
       </c>
       <c r="R26" t="n">
-        <v>6507549</v>
+        <v>6508726</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3311,7 +3296,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113399443</v>
+        <v>113399423</v>
       </c>
       <c r="B27" t="n">
         <v>56781</v>
@@ -3351,10 +3336,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>286465</v>
+        <v>286426</v>
       </c>
       <c r="R27" t="n">
-        <v>6508688</v>
+        <v>6507790</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3391,7 +3376,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3418,10 +3403,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113399464</v>
+        <v>113399422</v>
       </c>
       <c r="B28" t="n">
-        <v>94108</v>
+        <v>56781</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3430,25 +3415,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3458,10 +3443,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>286444</v>
+        <v>286408</v>
       </c>
       <c r="R28" t="n">
-        <v>6508165</v>
+        <v>6507718</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3494,6 +3479,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3520,10 +3510,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113399424</v>
+        <v>113399457</v>
       </c>
       <c r="B29" t="n">
-        <v>56781</v>
+        <v>95950</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3532,25 +3522,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3560,10 +3550,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>286495</v>
+        <v>286398</v>
       </c>
       <c r="R29" t="n">
-        <v>6508076</v>
+        <v>6508131</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3596,11 +3586,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3627,10 +3612,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113399411</v>
+        <v>113399430</v>
       </c>
       <c r="B30" t="n">
-        <v>95590</v>
+        <v>56781</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3639,25 +3624,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3667,10 +3652,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>286712</v>
+        <v>286476</v>
       </c>
       <c r="R30" t="n">
-        <v>6508906</v>
+        <v>6508348</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3703,6 +3688,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3729,10 +3719,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113399458</v>
+        <v>113399441</v>
       </c>
       <c r="B31" t="n">
-        <v>95950</v>
+        <v>56781</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3741,25 +3731,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3769,10 +3759,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>286751</v>
+        <v>286510</v>
       </c>
       <c r="R31" t="n">
-        <v>6508904</v>
+        <v>6508675</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3805,6 +3795,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3831,7 +3826,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113399413</v>
+        <v>113399431</v>
       </c>
       <c r="B32" t="n">
         <v>56781</v>
@@ -3871,10 +3866,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>286327</v>
+        <v>286459</v>
       </c>
       <c r="R32" t="n">
-        <v>6508012</v>
+        <v>6508392</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3938,7 +3933,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113399426</v>
+        <v>113399437</v>
       </c>
       <c r="B33" t="n">
         <v>56781</v>
@@ -3978,10 +3973,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>286454</v>
+        <v>286715</v>
       </c>
       <c r="R33" t="n">
-        <v>6508073</v>
+        <v>6508776</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4045,7 +4040,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113399428</v>
+        <v>113399414</v>
       </c>
       <c r="B34" t="n">
         <v>56781</v>
@@ -4085,10 +4080,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>286459</v>
+        <v>286242</v>
       </c>
       <c r="R34" t="n">
-        <v>6508160</v>
+        <v>6507840</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4152,7 +4147,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113399419</v>
+        <v>113399436</v>
       </c>
       <c r="B35" t="n">
         <v>56781</v>
@@ -4192,10 +4187,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>286311</v>
+        <v>286684</v>
       </c>
       <c r="R35" t="n">
-        <v>6507585</v>
+        <v>6508737</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4259,10 +4254,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113399417</v>
+        <v>113399410</v>
       </c>
       <c r="B36" t="n">
-        <v>56781</v>
+        <v>95590</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4271,25 +4266,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4299,10 +4294,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>286266</v>
+        <v>286724</v>
       </c>
       <c r="R36" t="n">
-        <v>6507549</v>
+        <v>6508823</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4335,11 +4330,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4366,10 +4356,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113399422</v>
+        <v>113399460</v>
       </c>
       <c r="B37" t="n">
-        <v>56781</v>
+        <v>95950</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4378,25 +4368,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4406,10 +4396,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>286408</v>
+        <v>286595</v>
       </c>
       <c r="R37" t="n">
-        <v>6507718</v>
+        <v>6508872</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4442,11 +4432,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4473,10 +4458,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113399437</v>
+        <v>113399408</v>
       </c>
       <c r="B38" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4489,16 +4474,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4513,10 +4498,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>286715</v>
+        <v>286479</v>
       </c>
       <c r="R38" t="n">
-        <v>6508776</v>
+        <v>6508372</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4553,7 +4538,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4580,7 +4565,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113399436</v>
+        <v>113399442</v>
       </c>
       <c r="B39" t="n">
         <v>56781</v>
@@ -4620,10 +4605,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>286684</v>
+        <v>286541</v>
       </c>
       <c r="R39" t="n">
-        <v>6508737</v>
+        <v>6508510</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4660,7 +4645,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4687,10 +4672,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113399448</v>
+        <v>113399438</v>
       </c>
       <c r="B40" t="n">
-        <v>91329</v>
+        <v>56781</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4703,21 +4688,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4727,10 +4712,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>286525</v>
+        <v>286835</v>
       </c>
       <c r="R40" t="n">
-        <v>6508258</v>
+        <v>6508956</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4767,7 +4752,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>9 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4794,10 +4779,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113399460</v>
+        <v>113399440</v>
       </c>
       <c r="B41" t="n">
-        <v>95950</v>
+        <v>56781</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4806,25 +4791,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4834,10 +4819,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>286595</v>
+        <v>286483</v>
       </c>
       <c r="R41" t="n">
-        <v>6508872</v>
+        <v>6508722</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4870,6 +4855,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4896,7 +4886,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113399440</v>
+        <v>113399418</v>
       </c>
       <c r="B42" t="n">
         <v>56781</v>
@@ -4936,10 +4926,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>286483</v>
+        <v>286273</v>
       </c>
       <c r="R42" t="n">
-        <v>6508722</v>
+        <v>6507549</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5003,7 +4993,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399439</v>
+        <v>113399427</v>
       </c>
       <c r="B43" t="n">
         <v>56781</v>
@@ -5043,10 +5033,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286834</v>
+        <v>286422</v>
       </c>
       <c r="R43" t="n">
-        <v>6508948</v>
+        <v>6508051</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5110,10 +5100,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399461</v>
+        <v>113399426</v>
       </c>
       <c r="B44" t="n">
-        <v>99570</v>
+        <v>56781</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5122,25 +5112,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5150,10 +5140,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>286239</v>
+        <v>286454</v>
       </c>
       <c r="R44" t="n">
-        <v>6507778</v>
+        <v>6508073</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5186,6 +5176,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5212,10 +5207,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113399412</v>
+        <v>113399429</v>
       </c>
       <c r="B45" t="n">
-        <v>95590</v>
+        <v>56781</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5224,25 +5219,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5252,10 +5247,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>286668</v>
+        <v>286485</v>
       </c>
       <c r="R45" t="n">
-        <v>6508839</v>
+        <v>6508336</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5288,6 +5283,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5314,10 +5314,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113399410</v>
+        <v>113399428</v>
       </c>
       <c r="B46" t="n">
-        <v>95590</v>
+        <v>56781</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5326,25 +5326,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>286724</v>
+        <v>286459</v>
       </c>
       <c r="R46" t="n">
-        <v>6508823</v>
+        <v>6508160</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5390,6 +5390,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5416,10 +5421,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113399438</v>
+        <v>113399456</v>
       </c>
       <c r="B47" t="n">
-        <v>56781</v>
+        <v>95950</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5428,25 +5433,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5456,10 +5461,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>286835</v>
+        <v>286522</v>
       </c>
       <c r="R47" t="n">
-        <v>6508956</v>
+        <v>6508764</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5492,11 +5497,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5523,7 +5523,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113399421</v>
+        <v>113399413</v>
       </c>
       <c r="B48" t="n">
         <v>56781</v>
@@ -5563,10 +5563,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>286411</v>
+        <v>286327</v>
       </c>
       <c r="R48" t="n">
-        <v>6507674</v>
+        <v>6508012</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5630,7 +5630,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113399429</v>
+        <v>113399425</v>
       </c>
       <c r="B49" t="n">
         <v>56781</v>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>286485</v>
+        <v>286469</v>
       </c>
       <c r="R49" t="n">
-        <v>6508336</v>
+        <v>6508059</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113399408</v>
+        <v>113399424</v>
       </c>
       <c r="B50" t="n">
-        <v>56765</v>
+        <v>56781</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5753,16 +5753,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>286479</v>
+        <v>286495</v>
       </c>
       <c r="R50" t="n">
-        <v>6508372</v>
+        <v>6508076</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Rnghack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>113354383</v>
       </c>
       <c r="B3" t="n">
-        <v>90056</v>
+        <v>90068</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113399449</v>
+        <v>113399438</v>
       </c>
       <c r="B4" t="n">
-        <v>91329</v>
+        <v>56782</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>286530</v>
+        <v>286835</v>
       </c>
       <c r="R4" t="n">
-        <v>6508258</v>
+        <v>6508956</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,6 +966,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113399419</v>
+        <v>113399437</v>
       </c>
       <c r="B5" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>286311</v>
+        <v>286715</v>
       </c>
       <c r="R5" t="n">
-        <v>6507585</v>
+        <v>6508776</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113399463</v>
+        <v>113399449</v>
       </c>
       <c r="B6" t="n">
-        <v>99570</v>
+        <v>91341</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>286229</v>
+        <v>286530</v>
       </c>
       <c r="R6" t="n">
-        <v>6507839</v>
+        <v>6508258</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1201,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113399448</v>
+        <v>113399408</v>
       </c>
       <c r="B7" t="n">
-        <v>91329</v>
+        <v>56766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,21 +1222,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>286525</v>
+        <v>286479</v>
       </c>
       <c r="R7" t="n">
-        <v>6508258</v>
+        <v>6508372</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1281,7 +1286,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>9 fruktkroppar</t>
+          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113399404</v>
+        <v>113399460</v>
       </c>
       <c r="B8" t="n">
-        <v>93755</v>
+        <v>95962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,21 +1329,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1348,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>286719</v>
+        <v>286595</v>
       </c>
       <c r="R8" t="n">
-        <v>6508879</v>
+        <v>6508872</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1410,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399433</v>
+        <v>113399434</v>
       </c>
       <c r="B9" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>286505</v>
+        <v>286601</v>
       </c>
       <c r="R9" t="n">
-        <v>6508433</v>
+        <v>6508623</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1517,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399439</v>
+        <v>113399463</v>
       </c>
       <c r="B10" t="n">
-        <v>56781</v>
+        <v>99582</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,25 +1534,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>286834</v>
+        <v>286229</v>
       </c>
       <c r="R10" t="n">
-        <v>6508948</v>
+        <v>6507839</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,11 +1598,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399455</v>
+        <v>113399411</v>
       </c>
       <c r="B11" t="n">
-        <v>95950</v>
+        <v>95602</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2606</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>286525</v>
+        <v>286712</v>
       </c>
       <c r="R11" t="n">
-        <v>6508767</v>
+        <v>6508906</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1726,10 +1726,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399420</v>
+        <v>113399418</v>
       </c>
       <c r="B12" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>286325</v>
+        <v>286273</v>
       </c>
       <c r="R12" t="n">
-        <v>6507609</v>
+        <v>6507549</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113399421</v>
+        <v>113399413</v>
       </c>
       <c r="B13" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>286411</v>
+        <v>286327</v>
       </c>
       <c r="R13" t="n">
-        <v>6507674</v>
+        <v>6508012</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113399443</v>
+        <v>113399461</v>
       </c>
       <c r="B14" t="n">
-        <v>56781</v>
+        <v>99582</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1952,25 +1952,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>286465</v>
+        <v>286239</v>
       </c>
       <c r="R14" t="n">
-        <v>6508688</v>
+        <v>6507778</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2016,11 +2016,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2047,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399409</v>
+        <v>113399422</v>
       </c>
       <c r="B15" t="n">
-        <v>56765</v>
+        <v>56782</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2063,16 +2058,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2087,10 +2082,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>286461</v>
+        <v>286408</v>
       </c>
       <c r="R15" t="n">
-        <v>6508704</v>
+        <v>6507718</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2127,7 +2122,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2154,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399411</v>
+        <v>113399426</v>
       </c>
       <c r="B16" t="n">
-        <v>95590</v>
+        <v>56782</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2166,25 +2161,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2189,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>286712</v>
+        <v>286454</v>
       </c>
       <c r="R16" t="n">
-        <v>6508906</v>
+        <v>6508073</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2230,6 +2225,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2256,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399412</v>
+        <v>113399431</v>
       </c>
       <c r="B17" t="n">
-        <v>95590</v>
+        <v>56782</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2268,25 +2268,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>286668</v>
+        <v>286459</v>
       </c>
       <c r="R17" t="n">
-        <v>6508839</v>
+        <v>6508392</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2332,6 +2332,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2361,7 +2366,7 @@
         <v>113399459</v>
       </c>
       <c r="B18" t="n">
-        <v>95950</v>
+        <v>95962</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2460,10 +2465,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399458</v>
+        <v>113399409</v>
       </c>
       <c r="B19" t="n">
-        <v>95950</v>
+        <v>56766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2472,25 +2477,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2606</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2500,10 +2505,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>286751</v>
+        <v>286461</v>
       </c>
       <c r="R19" t="n">
-        <v>6508904</v>
+        <v>6508704</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2536,6 +2541,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2562,10 +2572,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399461</v>
+        <v>113399427</v>
       </c>
       <c r="B20" t="n">
-        <v>99570</v>
+        <v>56782</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2574,25 +2584,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2602,10 +2612,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>286239</v>
+        <v>286422</v>
       </c>
       <c r="R20" t="n">
-        <v>6507778</v>
+        <v>6508051</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2638,6 +2648,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2664,10 +2679,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113399417</v>
+        <v>113399423</v>
       </c>
       <c r="B21" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2704,10 +2719,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>286266</v>
+        <v>286426</v>
       </c>
       <c r="R21" t="n">
-        <v>6507549</v>
+        <v>6507790</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2771,10 +2786,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113399464</v>
+        <v>113399455</v>
       </c>
       <c r="B22" t="n">
-        <v>94108</v>
+        <v>95962</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2787,21 +2802,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>2606</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2811,10 +2826,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>286444</v>
+        <v>286525</v>
       </c>
       <c r="R22" t="n">
-        <v>6508165</v>
+        <v>6508767</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2873,10 +2888,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113399434</v>
+        <v>113399464</v>
       </c>
       <c r="B23" t="n">
-        <v>56781</v>
+        <v>94120</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2885,25 +2900,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2913,10 +2928,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>286601</v>
+        <v>286444</v>
       </c>
       <c r="R23" t="n">
-        <v>6508623</v>
+        <v>6508165</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2949,11 +2964,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2980,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113399432</v>
+        <v>113399440</v>
       </c>
       <c r="B24" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3020,10 +3030,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>286495</v>
+        <v>286483</v>
       </c>
       <c r="R24" t="n">
-        <v>6508424</v>
+        <v>6508722</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3087,10 +3097,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113399405</v>
+        <v>113399428</v>
       </c>
       <c r="B25" t="n">
-        <v>93755</v>
+        <v>56782</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3099,25 +3109,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3127,10 +3137,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>286655</v>
+        <v>286459</v>
       </c>
       <c r="R25" t="n">
-        <v>6508854</v>
+        <v>6508160</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3163,6 +3173,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3189,10 +3204,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113399435</v>
+        <v>113399414</v>
       </c>
       <c r="B26" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3229,10 +3244,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>286667</v>
+        <v>286242</v>
       </c>
       <c r="R26" t="n">
-        <v>6508726</v>
+        <v>6507840</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3296,10 +3311,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113399423</v>
+        <v>113399417</v>
       </c>
       <c r="B27" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3336,10 +3351,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>286426</v>
+        <v>286266</v>
       </c>
       <c r="R27" t="n">
-        <v>6507790</v>
+        <v>6507549</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3403,10 +3418,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113399422</v>
+        <v>113399441</v>
       </c>
       <c r="B28" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3443,10 +3458,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>286408</v>
+        <v>286510</v>
       </c>
       <c r="R28" t="n">
-        <v>6507718</v>
+        <v>6508675</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3510,10 +3525,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113399457</v>
+        <v>113399439</v>
       </c>
       <c r="B29" t="n">
-        <v>95950</v>
+        <v>56782</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3522,25 +3537,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3550,10 +3565,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>286398</v>
+        <v>286834</v>
       </c>
       <c r="R29" t="n">
-        <v>6508131</v>
+        <v>6508948</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3586,6 +3601,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3612,10 +3632,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113399430</v>
+        <v>113399456</v>
       </c>
       <c r="B30" t="n">
-        <v>56781</v>
+        <v>95962</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3624,25 +3644,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3652,10 +3672,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>286476</v>
+        <v>286522</v>
       </c>
       <c r="R30" t="n">
-        <v>6508348</v>
+        <v>6508764</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3688,11 +3708,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3719,10 +3734,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113399441</v>
+        <v>113399420</v>
       </c>
       <c r="B31" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3759,10 +3774,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>286510</v>
+        <v>286325</v>
       </c>
       <c r="R31" t="n">
-        <v>6508675</v>
+        <v>6507609</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3826,10 +3841,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113399431</v>
+        <v>113399421</v>
       </c>
       <c r="B32" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3866,10 +3881,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>286459</v>
+        <v>286411</v>
       </c>
       <c r="R32" t="n">
-        <v>6508392</v>
+        <v>6507674</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3933,10 +3948,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113399437</v>
+        <v>113399430</v>
       </c>
       <c r="B33" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3973,10 +3988,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>286715</v>
+        <v>286476</v>
       </c>
       <c r="R33" t="n">
-        <v>6508776</v>
+        <v>6508348</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4040,10 +4055,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113399414</v>
+        <v>113399419</v>
       </c>
       <c r="B34" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4080,10 +4095,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>286242</v>
+        <v>286311</v>
       </c>
       <c r="R34" t="n">
-        <v>6507840</v>
+        <v>6507585</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4150,7 +4165,7 @@
         <v>113399436</v>
       </c>
       <c r="B35" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4254,10 +4269,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113399410</v>
+        <v>113399404</v>
       </c>
       <c r="B36" t="n">
-        <v>95590</v>
+        <v>93767</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4270,21 +4285,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4294,10 +4309,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>286724</v>
+        <v>286719</v>
       </c>
       <c r="R36" t="n">
-        <v>6508823</v>
+        <v>6508879</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4356,10 +4371,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113399460</v>
+        <v>113399457</v>
       </c>
       <c r="B37" t="n">
-        <v>95950</v>
+        <v>95962</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4396,10 +4411,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>286595</v>
+        <v>286398</v>
       </c>
       <c r="R37" t="n">
-        <v>6508872</v>
+        <v>6508131</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4458,10 +4473,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113399408</v>
+        <v>113399442</v>
       </c>
       <c r="B38" t="n">
-        <v>56765</v>
+        <v>56782</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4474,16 +4489,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4498,10 +4513,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>286479</v>
+        <v>286541</v>
       </c>
       <c r="R38" t="n">
-        <v>6508372</v>
+        <v>6508510</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4538,7 +4553,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rnghack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4565,10 +4580,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113399442</v>
+        <v>113399412</v>
       </c>
       <c r="B39" t="n">
-        <v>56781</v>
+        <v>95602</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4577,25 +4592,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4605,10 +4620,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>286541</v>
+        <v>286668</v>
       </c>
       <c r="R39" t="n">
-        <v>6508510</v>
+        <v>6508839</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4641,11 +4656,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4672,10 +4682,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113399438</v>
+        <v>113399448</v>
       </c>
       <c r="B40" t="n">
-        <v>56781</v>
+        <v>91341</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4688,21 +4698,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4712,10 +4722,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>286835</v>
+        <v>286525</v>
       </c>
       <c r="R40" t="n">
-        <v>6508956</v>
+        <v>6508258</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4752,7 +4762,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4779,10 +4789,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113399440</v>
+        <v>113399433</v>
       </c>
       <c r="B41" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4819,10 +4829,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>286483</v>
+        <v>286505</v>
       </c>
       <c r="R41" t="n">
-        <v>6508722</v>
+        <v>6508433</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4886,10 +4896,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113399418</v>
+        <v>113399443</v>
       </c>
       <c r="B42" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4926,10 +4936,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>286273</v>
+        <v>286465</v>
       </c>
       <c r="R42" t="n">
-        <v>6507549</v>
+        <v>6508688</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4966,7 +4976,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4993,10 +5003,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399427</v>
+        <v>113399425</v>
       </c>
       <c r="B43" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5033,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286422</v>
+        <v>286469</v>
       </c>
       <c r="R43" t="n">
-        <v>6508051</v>
+        <v>6508059</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5100,10 +5110,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399426</v>
+        <v>113399432</v>
       </c>
       <c r="B44" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5140,10 +5150,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>286454</v>
+        <v>286495</v>
       </c>
       <c r="R44" t="n">
-        <v>6508073</v>
+        <v>6508424</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5207,10 +5217,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113399429</v>
+        <v>113399435</v>
       </c>
       <c r="B45" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5247,10 +5257,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>286485</v>
+        <v>286667</v>
       </c>
       <c r="R45" t="n">
-        <v>6508336</v>
+        <v>6508726</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5314,10 +5324,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113399428</v>
+        <v>113399424</v>
       </c>
       <c r="B46" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5354,10 +5364,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>286459</v>
+        <v>286495</v>
       </c>
       <c r="R46" t="n">
-        <v>6508160</v>
+        <v>6508076</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5421,10 +5431,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113399456</v>
+        <v>113399458</v>
       </c>
       <c r="B47" t="n">
-        <v>95950</v>
+        <v>95962</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5461,10 +5471,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>286522</v>
+        <v>286751</v>
       </c>
       <c r="R47" t="n">
-        <v>6508764</v>
+        <v>6508904</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5523,10 +5533,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113399413</v>
+        <v>113399405</v>
       </c>
       <c r="B48" t="n">
-        <v>56781</v>
+        <v>93767</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5535,25 +5545,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5563,10 +5573,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>286327</v>
+        <v>286655</v>
       </c>
       <c r="R48" t="n">
-        <v>6508012</v>
+        <v>6508854</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5599,11 +5609,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5630,10 +5635,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113399425</v>
+        <v>113399410</v>
       </c>
       <c r="B49" t="n">
-        <v>56781</v>
+        <v>95602</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5642,25 +5647,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5670,10 +5675,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>286469</v>
+        <v>286724</v>
       </c>
       <c r="R49" t="n">
-        <v>6508059</v>
+        <v>6508823</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5706,11 +5711,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5737,10 +5737,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113399424</v>
+        <v>113399429</v>
       </c>
       <c r="B50" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>286495</v>
+        <v>286485</v>
       </c>
       <c r="R50" t="n">
-        <v>6508076</v>
+        <v>6508336</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -890,7 +890,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113399438</v>
+        <v>113399423</v>
       </c>
       <c r="B4" t="n">
         <v>56782</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>286835</v>
+        <v>286426</v>
       </c>
       <c r="R4" t="n">
-        <v>6508956</v>
+        <v>6507790</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113399437</v>
+        <v>113399410</v>
       </c>
       <c r="B5" t="n">
-        <v>56782</v>
+        <v>95602</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,25 +1009,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>286715</v>
+        <v>286724</v>
       </c>
       <c r="R5" t="n">
-        <v>6508776</v>
+        <v>6508823</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1073,11 +1073,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113399449</v>
+        <v>113399455</v>
       </c>
       <c r="B6" t="n">
-        <v>91341</v>
+        <v>95962</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>286530</v>
+        <v>286525</v>
       </c>
       <c r="R6" t="n">
-        <v>6508258</v>
+        <v>6508767</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1206,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113399408</v>
+        <v>113399456</v>
       </c>
       <c r="B7" t="n">
-        <v>56766</v>
+        <v>95962</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,25 +1213,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2606</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>286479</v>
+        <v>286522</v>
       </c>
       <c r="R7" t="n">
-        <v>6508372</v>
+        <v>6508764</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1282,11 +1277,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,10 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113399460</v>
+        <v>113399421</v>
       </c>
       <c r="B8" t="n">
-        <v>95962</v>
+        <v>56782</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,25 +1315,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1353,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>286595</v>
+        <v>286411</v>
       </c>
       <c r="R8" t="n">
-        <v>6508872</v>
+        <v>6507674</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,6 +1379,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,7 +1410,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399434</v>
+        <v>113399442</v>
       </c>
       <c r="B9" t="n">
         <v>56782</v>
@@ -1455,10 +1450,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>286601</v>
+        <v>286541</v>
       </c>
       <c r="R9" t="n">
-        <v>6508623</v>
+        <v>6508510</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1495,7 +1490,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399463</v>
+        <v>113399424</v>
       </c>
       <c r="B10" t="n">
-        <v>99582</v>
+        <v>56782</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1534,25 +1529,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>286229</v>
+        <v>286495</v>
       </c>
       <c r="R10" t="n">
-        <v>6507839</v>
+        <v>6508076</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,6 +1593,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399411</v>
+        <v>113399429</v>
       </c>
       <c r="B11" t="n">
-        <v>95602</v>
+        <v>56782</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1636,25 +1636,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>286712</v>
+        <v>286485</v>
       </c>
       <c r="R11" t="n">
-        <v>6508906</v>
+        <v>6508336</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,6 +1700,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1726,7 +1731,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399418</v>
+        <v>113399419</v>
       </c>
       <c r="B12" t="n">
         <v>56782</v>
@@ -1766,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>286273</v>
+        <v>286311</v>
       </c>
       <c r="R12" t="n">
-        <v>6507549</v>
+        <v>6507585</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1833,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113399413</v>
+        <v>113399409</v>
       </c>
       <c r="B13" t="n">
-        <v>56782</v>
+        <v>56766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1849,16 +1854,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1873,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>286327</v>
+        <v>286461</v>
       </c>
       <c r="R13" t="n">
-        <v>6508012</v>
+        <v>6508704</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1913,7 +1918,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399422</v>
+        <v>113399405</v>
       </c>
       <c r="B15" t="n">
-        <v>56782</v>
+        <v>93767</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2054,25 +2059,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2082,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>286408</v>
+        <v>286655</v>
       </c>
       <c r="R15" t="n">
-        <v>6507718</v>
+        <v>6508854</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2118,11 +2123,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2149,7 +2149,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399426</v>
+        <v>113399422</v>
       </c>
       <c r="B16" t="n">
         <v>56782</v>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>286454</v>
+        <v>286408</v>
       </c>
       <c r="R16" t="n">
-        <v>6508073</v>
+        <v>6507718</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2256,7 +2256,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399431</v>
+        <v>113399426</v>
       </c>
       <c r="B17" t="n">
         <v>56782</v>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>286459</v>
+        <v>286454</v>
       </c>
       <c r="R17" t="n">
-        <v>6508392</v>
+        <v>6508073</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2363,10 +2363,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399459</v>
+        <v>113399463</v>
       </c>
       <c r="B18" t="n">
-        <v>95962</v>
+        <v>99582</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2379,21 +2379,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2606</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>286600</v>
+        <v>286229</v>
       </c>
       <c r="R18" t="n">
-        <v>6508882</v>
+        <v>6507839</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399409</v>
+        <v>113399457</v>
       </c>
       <c r="B19" t="n">
-        <v>56766</v>
+        <v>95962</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2477,25 +2477,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2606</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>286461</v>
+        <v>286398</v>
       </c>
       <c r="R19" t="n">
-        <v>6508704</v>
+        <v>6508131</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2541,11 +2541,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2572,7 +2567,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399427</v>
+        <v>113399440</v>
       </c>
       <c r="B20" t="n">
         <v>56782</v>
@@ -2612,10 +2607,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>286422</v>
+        <v>286483</v>
       </c>
       <c r="R20" t="n">
-        <v>6508051</v>
+        <v>6508722</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2679,7 +2674,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113399423</v>
+        <v>113399441</v>
       </c>
       <c r="B21" t="n">
         <v>56782</v>
@@ -2719,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>286426</v>
+        <v>286510</v>
       </c>
       <c r="R21" t="n">
-        <v>6507790</v>
+        <v>6508675</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2786,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113399455</v>
+        <v>113399432</v>
       </c>
       <c r="B22" t="n">
-        <v>95962</v>
+        <v>56782</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2798,25 +2793,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2826,10 +2821,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>286525</v>
+        <v>286495</v>
       </c>
       <c r="R22" t="n">
-        <v>6508767</v>
+        <v>6508424</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2862,6 +2857,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2888,10 +2888,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113399464</v>
+        <v>113399413</v>
       </c>
       <c r="B23" t="n">
-        <v>94120</v>
+        <v>56782</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2900,25 +2900,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2928,10 +2928,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>286444</v>
+        <v>286327</v>
       </c>
       <c r="R23" t="n">
-        <v>6508165</v>
+        <v>6508012</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2964,6 +2964,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2990,10 +2995,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113399440</v>
+        <v>113399458</v>
       </c>
       <c r="B24" t="n">
-        <v>56782</v>
+        <v>95962</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3002,25 +3007,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3030,10 +3035,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>286483</v>
+        <v>286751</v>
       </c>
       <c r="R24" t="n">
-        <v>6508722</v>
+        <v>6508904</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3066,11 +3071,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3097,10 +3097,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113399428</v>
+        <v>113399408</v>
       </c>
       <c r="B25" t="n">
-        <v>56782</v>
+        <v>56766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3113,16 +3113,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>286459</v>
+        <v>286479</v>
       </c>
       <c r="R25" t="n">
-        <v>6508160</v>
+        <v>6508372</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3204,10 +3204,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113399414</v>
+        <v>113399404</v>
       </c>
       <c r="B26" t="n">
-        <v>56782</v>
+        <v>93767</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3216,25 +3216,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>286242</v>
+        <v>286719</v>
       </c>
       <c r="R26" t="n">
-        <v>6507840</v>
+        <v>6508879</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3280,11 +3280,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3311,7 +3306,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113399417</v>
+        <v>113399418</v>
       </c>
       <c r="B27" t="n">
         <v>56782</v>
@@ -3351,7 +3346,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>286266</v>
+        <v>286273</v>
       </c>
       <c r="R27" t="n">
         <v>6507549</v>
@@ -3418,7 +3413,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113399441</v>
+        <v>113399417</v>
       </c>
       <c r="B28" t="n">
         <v>56782</v>
@@ -3458,10 +3453,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>286510</v>
+        <v>286266</v>
       </c>
       <c r="R28" t="n">
-        <v>6508675</v>
+        <v>6507549</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3525,7 +3520,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113399439</v>
+        <v>113399436</v>
       </c>
       <c r="B29" t="n">
         <v>56782</v>
@@ -3565,10 +3560,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>286834</v>
+        <v>286684</v>
       </c>
       <c r="R29" t="n">
-        <v>6508948</v>
+        <v>6508737</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3632,10 +3627,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113399456</v>
+        <v>113399412</v>
       </c>
       <c r="B30" t="n">
-        <v>95962</v>
+        <v>95602</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3648,21 +3643,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2606</v>
+        <v>2569</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3672,10 +3667,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>286522</v>
+        <v>286668</v>
       </c>
       <c r="R30" t="n">
-        <v>6508764</v>
+        <v>6508839</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3734,10 +3729,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113399420</v>
+        <v>113399411</v>
       </c>
       <c r="B31" t="n">
-        <v>56782</v>
+        <v>95602</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3746,25 +3741,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3774,10 +3769,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>286325</v>
+        <v>286712</v>
       </c>
       <c r="R31" t="n">
-        <v>6507609</v>
+        <v>6508906</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3810,11 +3805,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3841,7 +3831,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113399421</v>
+        <v>113399420</v>
       </c>
       <c r="B32" t="n">
         <v>56782</v>
@@ -3881,10 +3871,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>286411</v>
+        <v>286325</v>
       </c>
       <c r="R32" t="n">
-        <v>6507674</v>
+        <v>6507609</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3948,7 +3938,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113399430</v>
+        <v>113399443</v>
       </c>
       <c r="B33" t="n">
         <v>56782</v>
@@ -3988,10 +3978,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>286476</v>
+        <v>286465</v>
       </c>
       <c r="R33" t="n">
-        <v>6508348</v>
+        <v>6508688</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4028,7 +4018,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4055,7 +4045,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113399419</v>
+        <v>113399428</v>
       </c>
       <c r="B34" t="n">
         <v>56782</v>
@@ -4095,10 +4085,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>286311</v>
+        <v>286459</v>
       </c>
       <c r="R34" t="n">
-        <v>6507585</v>
+        <v>6508160</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4162,7 +4152,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113399436</v>
+        <v>113399430</v>
       </c>
       <c r="B35" t="n">
         <v>56782</v>
@@ -4202,10 +4192,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>286684</v>
+        <v>286476</v>
       </c>
       <c r="R35" t="n">
-        <v>6508737</v>
+        <v>6508348</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4269,10 +4259,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113399404</v>
+        <v>113399439</v>
       </c>
       <c r="B36" t="n">
-        <v>93767</v>
+        <v>56782</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4281,25 +4271,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4309,10 +4299,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>286719</v>
+        <v>286834</v>
       </c>
       <c r="R36" t="n">
-        <v>6508879</v>
+        <v>6508948</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4345,6 +4335,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4371,10 +4366,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113399457</v>
+        <v>113399435</v>
       </c>
       <c r="B37" t="n">
-        <v>95962</v>
+        <v>56782</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4383,25 +4378,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4411,10 +4406,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>286398</v>
+        <v>286667</v>
       </c>
       <c r="R37" t="n">
-        <v>6508131</v>
+        <v>6508726</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4447,6 +4442,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4473,7 +4473,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113399442</v>
+        <v>113399437</v>
       </c>
       <c r="B38" t="n">
         <v>56782</v>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>286541</v>
+        <v>286715</v>
       </c>
       <c r="R38" t="n">
-        <v>6508510</v>
+        <v>6508776</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4580,10 +4580,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113399412</v>
+        <v>113399449</v>
       </c>
       <c r="B39" t="n">
-        <v>95602</v>
+        <v>91341</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4592,25 +4592,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2569</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>286668</v>
+        <v>286530</v>
       </c>
       <c r="R39" t="n">
-        <v>6508839</v>
+        <v>6508258</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4682,10 +4682,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113399448</v>
+        <v>113399460</v>
       </c>
       <c r="B40" t="n">
-        <v>91341</v>
+        <v>95962</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4694,25 +4694,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>2606</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4722,10 +4722,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>286525</v>
+        <v>286595</v>
       </c>
       <c r="R40" t="n">
-        <v>6508258</v>
+        <v>6508872</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4758,11 +4758,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4789,10 +4784,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113399433</v>
+        <v>113399459</v>
       </c>
       <c r="B41" t="n">
-        <v>56782</v>
+        <v>95962</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4801,25 +4796,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4829,10 +4824,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>286505</v>
+        <v>286600</v>
       </c>
       <c r="R41" t="n">
-        <v>6508433</v>
+        <v>6508882</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4865,11 +4860,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4896,10 +4886,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113399443</v>
+        <v>113399464</v>
       </c>
       <c r="B42" t="n">
-        <v>56782</v>
+        <v>94120</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4908,25 +4898,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4936,10 +4926,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>286465</v>
+        <v>286444</v>
       </c>
       <c r="R42" t="n">
-        <v>6508688</v>
+        <v>6508165</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4972,11 +4962,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5003,10 +4988,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399425</v>
+        <v>113399448</v>
       </c>
       <c r="B43" t="n">
-        <v>56782</v>
+        <v>91341</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5019,21 +5004,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5043,10 +5028,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286469</v>
+        <v>286525</v>
       </c>
       <c r="R43" t="n">
-        <v>6508059</v>
+        <v>6508258</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5083,7 +5068,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5110,7 +5095,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399432</v>
+        <v>113399431</v>
       </c>
       <c r="B44" t="n">
         <v>56782</v>
@@ -5150,10 +5135,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>286495</v>
+        <v>286459</v>
       </c>
       <c r="R44" t="n">
-        <v>6508424</v>
+        <v>6508392</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5217,7 +5202,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113399435</v>
+        <v>113399438</v>
       </c>
       <c r="B45" t="n">
         <v>56782</v>
@@ -5257,10 +5242,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>286667</v>
+        <v>286835</v>
       </c>
       <c r="R45" t="n">
-        <v>6508726</v>
+        <v>6508956</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5324,7 +5309,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113399424</v>
+        <v>113399425</v>
       </c>
       <c r="B46" t="n">
         <v>56782</v>
@@ -5364,10 +5349,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>286495</v>
+        <v>286469</v>
       </c>
       <c r="R46" t="n">
-        <v>6508076</v>
+        <v>6508059</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5431,10 +5416,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113399458</v>
+        <v>113399427</v>
       </c>
       <c r="B47" t="n">
-        <v>95962</v>
+        <v>56782</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5443,25 +5428,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5471,10 +5456,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>286751</v>
+        <v>286422</v>
       </c>
       <c r="R47" t="n">
-        <v>6508904</v>
+        <v>6508051</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5507,6 +5492,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5533,10 +5523,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113399405</v>
+        <v>113399434</v>
       </c>
       <c r="B48" t="n">
-        <v>93767</v>
+        <v>56782</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5545,25 +5535,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5573,10 +5563,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>286655</v>
+        <v>286601</v>
       </c>
       <c r="R48" t="n">
-        <v>6508854</v>
+        <v>6508623</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5609,6 +5599,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5635,10 +5630,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113399410</v>
+        <v>113399414</v>
       </c>
       <c r="B49" t="n">
-        <v>95602</v>
+        <v>56782</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5647,25 +5642,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5675,10 +5670,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>286724</v>
+        <v>286242</v>
       </c>
       <c r="R49" t="n">
-        <v>6508823</v>
+        <v>6507840</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5711,6 +5706,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5737,7 +5737,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113399429</v>
+        <v>113399433</v>
       </c>
       <c r="B50" t="n">
         <v>56782</v>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>286485</v>
+        <v>286505</v>
       </c>
       <c r="R50" t="n">
-        <v>6508336</v>
+        <v>6508433</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -1517,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399424</v>
+        <v>113399405</v>
       </c>
       <c r="B10" t="n">
-        <v>56782</v>
+        <v>93767</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,25 +1529,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>286495</v>
+        <v>286655</v>
       </c>
       <c r="R10" t="n">
-        <v>6508076</v>
+        <v>6508854</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,11 +1593,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,7 +1619,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399429</v>
+        <v>113399424</v>
       </c>
       <c r="B11" t="n">
         <v>56782</v>
@@ -1664,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>286485</v>
+        <v>286495</v>
       </c>
       <c r="R11" t="n">
-        <v>6508336</v>
+        <v>6508076</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1731,7 +1726,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399419</v>
+        <v>113399429</v>
       </c>
       <c r="B12" t="n">
         <v>56782</v>
@@ -1771,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>286311</v>
+        <v>286485</v>
       </c>
       <c r="R12" t="n">
-        <v>6507585</v>
+        <v>6508336</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1838,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113399409</v>
+        <v>113399419</v>
       </c>
       <c r="B13" t="n">
-        <v>56766</v>
+        <v>56782</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,16 +1849,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1878,10 +1873,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>286461</v>
+        <v>286311</v>
       </c>
       <c r="R13" t="n">
-        <v>6508704</v>
+        <v>6507585</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1918,7 +1913,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1945,10 +1940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113399461</v>
+        <v>113399409</v>
       </c>
       <c r="B14" t="n">
-        <v>99582</v>
+        <v>56766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,25 +1952,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>286239</v>
+        <v>286461</v>
       </c>
       <c r="R14" t="n">
-        <v>6507778</v>
+        <v>6508704</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2021,6 +2016,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2047,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399405</v>
+        <v>113399461</v>
       </c>
       <c r="B15" t="n">
-        <v>93767</v>
+        <v>99582</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2810</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>286655</v>
+        <v>286239</v>
       </c>
       <c r="R15" t="n">
-        <v>6508854</v>
+        <v>6507778</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>113354383</v>
       </c>
       <c r="B3" t="n">
-        <v>90068</v>
+        <v>90090</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113399423</v>
+        <v>113399461</v>
       </c>
       <c r="B4" t="n">
-        <v>56782</v>
+        <v>99604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -902,25 +902,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>286426</v>
+        <v>286239</v>
       </c>
       <c r="R4" t="n">
-        <v>6507790</v>
+        <v>6507778</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,11 +966,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113399410</v>
+        <v>113399441</v>
       </c>
       <c r="B5" t="n">
-        <v>95602</v>
+        <v>56782</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,25 +1004,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>286724</v>
+        <v>286510</v>
       </c>
       <c r="R5" t="n">
-        <v>6508823</v>
+        <v>6508675</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1073,6 +1068,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113399455</v>
+        <v>113399439</v>
       </c>
       <c r="B6" t="n">
-        <v>95962</v>
+        <v>56782</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>286525</v>
+        <v>286834</v>
       </c>
       <c r="R6" t="n">
-        <v>6508767</v>
+        <v>6508948</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1175,6 +1175,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113399456</v>
+        <v>113399411</v>
       </c>
       <c r="B7" t="n">
-        <v>95962</v>
+        <v>95624</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,21 +1222,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2606</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>286522</v>
+        <v>286712</v>
       </c>
       <c r="R7" t="n">
-        <v>6508764</v>
+        <v>6508906</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1303,7 +1308,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113399421</v>
+        <v>113399431</v>
       </c>
       <c r="B8" t="n">
         <v>56782</v>
@@ -1343,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>286411</v>
+        <v>286459</v>
       </c>
       <c r="R8" t="n">
-        <v>6507674</v>
+        <v>6508392</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1410,7 +1415,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399442</v>
+        <v>113399430</v>
       </c>
       <c r="B9" t="n">
         <v>56782</v>
@@ -1450,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>286541</v>
+        <v>286476</v>
       </c>
       <c r="R9" t="n">
-        <v>6508510</v>
+        <v>6508348</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1490,7 +1495,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1517,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399405</v>
+        <v>113399410</v>
       </c>
       <c r="B10" t="n">
-        <v>93767</v>
+        <v>95624</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1533,21 +1538,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>286655</v>
+        <v>286724</v>
       </c>
       <c r="R10" t="n">
-        <v>6508854</v>
+        <v>6508823</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1619,7 +1624,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399424</v>
+        <v>113399420</v>
       </c>
       <c r="B11" t="n">
         <v>56782</v>
@@ -1659,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>286495</v>
+        <v>286325</v>
       </c>
       <c r="R11" t="n">
-        <v>6508076</v>
+        <v>6507609</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1726,7 +1731,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399429</v>
+        <v>113399435</v>
       </c>
       <c r="B12" t="n">
         <v>56782</v>
@@ -1766,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>286485</v>
+        <v>286667</v>
       </c>
       <c r="R12" t="n">
-        <v>6508336</v>
+        <v>6508726</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1833,7 +1838,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113399419</v>
+        <v>113399422</v>
       </c>
       <c r="B13" t="n">
         <v>56782</v>
@@ -1873,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>286311</v>
+        <v>286408</v>
       </c>
       <c r="R13" t="n">
-        <v>6507585</v>
+        <v>6507718</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1940,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113399409</v>
+        <v>113399429</v>
       </c>
       <c r="B14" t="n">
-        <v>56766</v>
+        <v>56782</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1956,16 +1961,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1980,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>286461</v>
+        <v>286485</v>
       </c>
       <c r="R14" t="n">
-        <v>6508704</v>
+        <v>6508336</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2020,7 +2025,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2047,10 +2052,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399461</v>
+        <v>113399455</v>
       </c>
       <c r="B15" t="n">
-        <v>99582</v>
+        <v>95984</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2063,21 +2068,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>2606</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>286239</v>
+        <v>286525</v>
       </c>
       <c r="R15" t="n">
-        <v>6507778</v>
+        <v>6508767</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2149,7 +2154,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399422</v>
+        <v>113399413</v>
       </c>
       <c r="B16" t="n">
         <v>56782</v>
@@ -2189,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>286408</v>
+        <v>286327</v>
       </c>
       <c r="R16" t="n">
-        <v>6507718</v>
+        <v>6508012</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2256,10 +2261,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399426</v>
+        <v>113399448</v>
       </c>
       <c r="B17" t="n">
-        <v>56782</v>
+        <v>91363</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2272,21 +2277,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2296,10 +2301,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>286454</v>
+        <v>286525</v>
       </c>
       <c r="R17" t="n">
-        <v>6508073</v>
+        <v>6508258</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2336,7 +2341,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2363,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399463</v>
+        <v>113399449</v>
       </c>
       <c r="B18" t="n">
-        <v>99582</v>
+        <v>91363</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2375,25 +2380,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2408,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>286229</v>
+        <v>286530</v>
       </c>
       <c r="R18" t="n">
-        <v>6507839</v>
+        <v>6508258</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2465,10 +2470,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399457</v>
+        <v>113399418</v>
       </c>
       <c r="B19" t="n">
-        <v>95962</v>
+        <v>56782</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2477,25 +2482,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2505,10 +2510,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>286398</v>
+        <v>286273</v>
       </c>
       <c r="R19" t="n">
-        <v>6508131</v>
+        <v>6507549</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2541,6 +2546,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2567,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399440</v>
+        <v>113399405</v>
       </c>
       <c r="B20" t="n">
-        <v>56782</v>
+        <v>93789</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2579,25 +2589,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2607,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>286483</v>
+        <v>286655</v>
       </c>
       <c r="R20" t="n">
-        <v>6508722</v>
+        <v>6508854</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2643,11 +2653,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2674,10 +2679,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113399441</v>
+        <v>113399463</v>
       </c>
       <c r="B21" t="n">
-        <v>56782</v>
+        <v>99604</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2686,25 +2691,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2714,10 +2719,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>286510</v>
+        <v>286229</v>
       </c>
       <c r="R21" t="n">
-        <v>6508675</v>
+        <v>6507839</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2750,11 +2755,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2781,7 +2781,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113399432</v>
+        <v>113399442</v>
       </c>
       <c r="B22" t="n">
         <v>56782</v>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>286495</v>
+        <v>286541</v>
       </c>
       <c r="R22" t="n">
-        <v>6508424</v>
+        <v>6508510</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2888,7 +2888,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113399413</v>
+        <v>113399436</v>
       </c>
       <c r="B23" t="n">
         <v>56782</v>
@@ -2928,10 +2928,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>286327</v>
+        <v>286684</v>
       </c>
       <c r="R23" t="n">
-        <v>6508012</v>
+        <v>6508737</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113399458</v>
+        <v>113399419</v>
       </c>
       <c r="B24" t="n">
-        <v>95962</v>
+        <v>56782</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3007,25 +3007,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>286751</v>
+        <v>286311</v>
       </c>
       <c r="R24" t="n">
-        <v>6508904</v>
+        <v>6507585</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3071,6 +3071,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3097,10 +3102,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113399408</v>
+        <v>113399423</v>
       </c>
       <c r="B25" t="n">
-        <v>56766</v>
+        <v>56782</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3113,16 +3118,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3137,10 +3142,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>286479</v>
+        <v>286426</v>
       </c>
       <c r="R25" t="n">
-        <v>6508372</v>
+        <v>6507790</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3177,7 +3182,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rnghack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3204,10 +3209,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113399404</v>
+        <v>113399427</v>
       </c>
       <c r="B26" t="n">
-        <v>93767</v>
+        <v>56782</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3216,25 +3221,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3244,10 +3249,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>286719</v>
+        <v>286422</v>
       </c>
       <c r="R26" t="n">
-        <v>6508879</v>
+        <v>6508051</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3280,6 +3285,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3306,7 +3316,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113399418</v>
+        <v>113399426</v>
       </c>
       <c r="B27" t="n">
         <v>56782</v>
@@ -3346,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>286273</v>
+        <v>286454</v>
       </c>
       <c r="R27" t="n">
-        <v>6507549</v>
+        <v>6508073</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3413,7 +3423,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113399417</v>
+        <v>113399425</v>
       </c>
       <c r="B28" t="n">
         <v>56782</v>
@@ -3453,10 +3463,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>286266</v>
+        <v>286469</v>
       </c>
       <c r="R28" t="n">
-        <v>6507549</v>
+        <v>6508059</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3520,7 +3530,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113399436</v>
+        <v>113399434</v>
       </c>
       <c r="B29" t="n">
         <v>56782</v>
@@ -3560,10 +3570,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>286684</v>
+        <v>286601</v>
       </c>
       <c r="R29" t="n">
-        <v>6508737</v>
+        <v>6508623</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3627,10 +3637,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113399412</v>
+        <v>113399437</v>
       </c>
       <c r="B30" t="n">
-        <v>95602</v>
+        <v>56782</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3639,25 +3649,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3667,10 +3677,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>286668</v>
+        <v>286715</v>
       </c>
       <c r="R30" t="n">
-        <v>6508839</v>
+        <v>6508776</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3703,6 +3713,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3729,10 +3744,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113399411</v>
+        <v>113399440</v>
       </c>
       <c r="B31" t="n">
-        <v>95602</v>
+        <v>56782</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3741,25 +3756,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3769,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>286712</v>
+        <v>286483</v>
       </c>
       <c r="R31" t="n">
-        <v>6508906</v>
+        <v>6508722</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3805,6 +3820,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3831,7 +3851,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113399420</v>
+        <v>113399421</v>
       </c>
       <c r="B32" t="n">
         <v>56782</v>
@@ -3871,10 +3891,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>286325</v>
+        <v>286411</v>
       </c>
       <c r="R32" t="n">
-        <v>6507609</v>
+        <v>6507674</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3938,7 +3958,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113399443</v>
+        <v>113399417</v>
       </c>
       <c r="B33" t="n">
         <v>56782</v>
@@ -3978,10 +3998,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>286465</v>
+        <v>286266</v>
       </c>
       <c r="R33" t="n">
-        <v>6508688</v>
+        <v>6507549</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4018,7 +4038,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4045,10 +4065,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113399428</v>
+        <v>113399408</v>
       </c>
       <c r="B34" t="n">
-        <v>56782</v>
+        <v>56766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4061,16 +4081,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4085,10 +4105,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>286459</v>
+        <v>286479</v>
       </c>
       <c r="R34" t="n">
-        <v>6508160</v>
+        <v>6508372</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4125,7 +4145,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4152,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113399430</v>
+        <v>113399459</v>
       </c>
       <c r="B35" t="n">
-        <v>56782</v>
+        <v>95984</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4164,25 +4184,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4192,10 +4212,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>286476</v>
+        <v>286600</v>
       </c>
       <c r="R35" t="n">
-        <v>6508348</v>
+        <v>6508882</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4228,11 +4248,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4259,7 +4274,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113399439</v>
+        <v>113399433</v>
       </c>
       <c r="B36" t="n">
         <v>56782</v>
@@ -4299,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>286834</v>
+        <v>286505</v>
       </c>
       <c r="R36" t="n">
-        <v>6508948</v>
+        <v>6508433</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4366,10 +4381,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113399435</v>
+        <v>113399460</v>
       </c>
       <c r="B37" t="n">
-        <v>56782</v>
+        <v>95984</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4378,25 +4393,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4406,10 +4421,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>286667</v>
+        <v>286595</v>
       </c>
       <c r="R37" t="n">
-        <v>6508726</v>
+        <v>6508872</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4442,11 +4457,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4473,10 +4483,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113399437</v>
+        <v>113399456</v>
       </c>
       <c r="B38" t="n">
-        <v>56782</v>
+        <v>95984</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4485,25 +4495,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4513,10 +4523,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>286715</v>
+        <v>286522</v>
       </c>
       <c r="R38" t="n">
-        <v>6508776</v>
+        <v>6508764</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4549,11 +4559,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4580,10 +4585,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113399449</v>
+        <v>113399432</v>
       </c>
       <c r="B39" t="n">
-        <v>91341</v>
+        <v>56782</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4596,21 +4601,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4620,10 +4625,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>286530</v>
+        <v>286495</v>
       </c>
       <c r="R39" t="n">
-        <v>6508258</v>
+        <v>6508424</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4656,6 +4661,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4682,10 +4692,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113399460</v>
+        <v>113399443</v>
       </c>
       <c r="B40" t="n">
-        <v>95962</v>
+        <v>56782</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4694,25 +4704,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4722,10 +4732,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>286595</v>
+        <v>286465</v>
       </c>
       <c r="R40" t="n">
-        <v>6508872</v>
+        <v>6508688</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4758,6 +4768,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4784,10 +4799,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113399459</v>
+        <v>113399438</v>
       </c>
       <c r="B41" t="n">
-        <v>95962</v>
+        <v>56782</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4796,25 +4811,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4824,10 +4839,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>286600</v>
+        <v>286835</v>
       </c>
       <c r="R41" t="n">
-        <v>6508882</v>
+        <v>6508956</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4860,6 +4875,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4886,10 +4906,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113399464</v>
+        <v>113399458</v>
       </c>
       <c r="B42" t="n">
-        <v>94120</v>
+        <v>95984</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4902,21 +4922,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>2606</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4926,10 +4946,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>286444</v>
+        <v>286751</v>
       </c>
       <c r="R42" t="n">
-        <v>6508165</v>
+        <v>6508904</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4988,10 +5008,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399448</v>
+        <v>113399404</v>
       </c>
       <c r="B43" t="n">
-        <v>91341</v>
+        <v>93789</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5000,25 +5020,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>2810</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5028,10 +5048,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286525</v>
+        <v>286719</v>
       </c>
       <c r="R43" t="n">
-        <v>6508258</v>
+        <v>6508879</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5064,11 +5084,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5095,7 +5110,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399431</v>
+        <v>113399428</v>
       </c>
       <c r="B44" t="n">
         <v>56782</v>
@@ -5138,7 +5153,7 @@
         <v>286459</v>
       </c>
       <c r="R44" t="n">
-        <v>6508392</v>
+        <v>6508160</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5202,10 +5217,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113399438</v>
+        <v>113399464</v>
       </c>
       <c r="B45" t="n">
-        <v>56782</v>
+        <v>94142</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5214,25 +5229,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5242,10 +5257,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>286835</v>
+        <v>286444</v>
       </c>
       <c r="R45" t="n">
-        <v>6508956</v>
+        <v>6508165</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5278,11 +5293,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5309,10 +5319,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113399425</v>
+        <v>113399412</v>
       </c>
       <c r="B46" t="n">
-        <v>56782</v>
+        <v>95624</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5321,25 +5331,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5349,10 +5359,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>286469</v>
+        <v>286668</v>
       </c>
       <c r="R46" t="n">
-        <v>6508059</v>
+        <v>6508839</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5385,11 +5395,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5416,7 +5421,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113399427</v>
+        <v>113399414</v>
       </c>
       <c r="B47" t="n">
         <v>56782</v>
@@ -5456,10 +5461,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>286422</v>
+        <v>286242</v>
       </c>
       <c r="R47" t="n">
-        <v>6508051</v>
+        <v>6507840</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5523,7 +5528,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113399434</v>
+        <v>113399424</v>
       </c>
       <c r="B48" t="n">
         <v>56782</v>
@@ -5563,10 +5568,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>286601</v>
+        <v>286495</v>
       </c>
       <c r="R48" t="n">
-        <v>6508623</v>
+        <v>6508076</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5630,10 +5635,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113399414</v>
+        <v>113399457</v>
       </c>
       <c r="B49" t="n">
-        <v>56782</v>
+        <v>95984</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5642,25 +5647,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5670,10 +5675,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>286242</v>
+        <v>286398</v>
       </c>
       <c r="R49" t="n">
-        <v>6507840</v>
+        <v>6508131</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5706,11 +5711,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5737,10 +5737,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113399433</v>
+        <v>113399409</v>
       </c>
       <c r="B50" t="n">
-        <v>56782</v>
+        <v>56766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5753,16 +5753,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>286505</v>
+        <v>286461</v>
       </c>
       <c r="R50" t="n">
-        <v>6508433</v>
+        <v>6508704</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113399429</v>
+        <v>113399455</v>
       </c>
       <c r="B14" t="n">
-        <v>56782</v>
+        <v>95984</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,25 +1957,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>286485</v>
+        <v>286525</v>
       </c>
       <c r="R14" t="n">
-        <v>6508336</v>
+        <v>6508767</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2021,11 +2021,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2052,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399455</v>
+        <v>113399413</v>
       </c>
       <c r="B15" t="n">
-        <v>95984</v>
+        <v>56782</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2064,25 +2059,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2092,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>286525</v>
+        <v>286327</v>
       </c>
       <c r="R15" t="n">
-        <v>6508767</v>
+        <v>6508012</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2128,6 +2123,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2154,10 +2154,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399413</v>
+        <v>113399448</v>
       </c>
       <c r="B16" t="n">
-        <v>56782</v>
+        <v>91363</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2170,21 +2170,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>286327</v>
+        <v>286525</v>
       </c>
       <c r="R16" t="n">
-        <v>6508012</v>
+        <v>6508258</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2261,10 +2261,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399448</v>
+        <v>113399429</v>
       </c>
       <c r="B17" t="n">
-        <v>91363</v>
+        <v>56782</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,21 +2277,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>286525</v>
+        <v>286485</v>
       </c>
       <c r="R17" t="n">
-        <v>6508258</v>
+        <v>6508336</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>9 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2368,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399449</v>
+        <v>113399418</v>
       </c>
       <c r="B18" t="n">
-        <v>91363</v>
+        <v>56782</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2384,21 +2384,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>286530</v>
+        <v>286273</v>
       </c>
       <c r="R18" t="n">
-        <v>6508258</v>
+        <v>6507549</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2444,6 +2444,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2470,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399418</v>
+        <v>113399449</v>
       </c>
       <c r="B19" t="n">
-        <v>56782</v>
+        <v>91363</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2486,21 +2491,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2510,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>286273</v>
+        <v>286530</v>
       </c>
       <c r="R19" t="n">
-        <v>6507549</v>
+        <v>6508258</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2546,11 +2551,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -4585,7 +4585,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113399432</v>
+        <v>113399443</v>
       </c>
       <c r="B39" t="n">
         <v>56782</v>
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>286495</v>
+        <v>286465</v>
       </c>
       <c r="R39" t="n">
-        <v>6508424</v>
+        <v>6508688</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4692,7 +4692,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113399443</v>
+        <v>113399432</v>
       </c>
       <c r="B40" t="n">
         <v>56782</v>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>286465</v>
+        <v>286495</v>
       </c>
       <c r="R40" t="n">
-        <v>6508688</v>
+        <v>6508424</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>113354383</v>
       </c>
       <c r="B3" t="n">
-        <v>90090</v>
+        <v>90094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113399461</v>
+        <v>113399441</v>
       </c>
       <c r="B4" t="n">
-        <v>99604</v>
+        <v>56785</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -902,25 +902,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>286239</v>
+        <v>286510</v>
       </c>
       <c r="R4" t="n">
-        <v>6507778</v>
+        <v>6508675</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,6 +966,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113399441</v>
+        <v>113399432</v>
       </c>
       <c r="B5" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>286510</v>
+        <v>286495</v>
       </c>
       <c r="R5" t="n">
-        <v>6508675</v>
+        <v>6508424</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113399439</v>
+        <v>113399438</v>
       </c>
       <c r="B6" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>286834</v>
+        <v>286835</v>
       </c>
       <c r="R6" t="n">
-        <v>6508948</v>
+        <v>6508956</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1206,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113399411</v>
+        <v>113399414</v>
       </c>
       <c r="B7" t="n">
-        <v>95624</v>
+        <v>56785</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,25 +1223,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>286712</v>
+        <v>286242</v>
       </c>
       <c r="R7" t="n">
-        <v>6508906</v>
+        <v>6507840</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1282,6 +1287,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113399431</v>
+        <v>113399405</v>
       </c>
       <c r="B8" t="n">
-        <v>56782</v>
+        <v>93793</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1320,25 +1330,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1348,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>286459</v>
+        <v>286655</v>
       </c>
       <c r="R8" t="n">
-        <v>6508392</v>
+        <v>6508854</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1384,11 +1394,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399430</v>
+        <v>113399410</v>
       </c>
       <c r="B9" t="n">
-        <v>56782</v>
+        <v>95628</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1427,25 +1432,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>286476</v>
+        <v>286724</v>
       </c>
       <c r="R9" t="n">
-        <v>6508348</v>
+        <v>6508823</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,11 +1496,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399410</v>
+        <v>113399433</v>
       </c>
       <c r="B10" t="n">
-        <v>95624</v>
+        <v>56785</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1534,25 +1534,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>286724</v>
+        <v>286505</v>
       </c>
       <c r="R10" t="n">
-        <v>6508823</v>
+        <v>6508433</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,6 +1598,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399420</v>
+        <v>113399459</v>
       </c>
       <c r="B11" t="n">
-        <v>56782</v>
+        <v>95988</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1636,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>286325</v>
+        <v>286600</v>
       </c>
       <c r="R11" t="n">
-        <v>6507609</v>
+        <v>6508882</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,11 +1705,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1731,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399435</v>
+        <v>113399404</v>
       </c>
       <c r="B12" t="n">
-        <v>56782</v>
+        <v>93793</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1743,25 +1743,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>286667</v>
+        <v>286719</v>
       </c>
       <c r="R12" t="n">
-        <v>6508726</v>
+        <v>6508879</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1807,11 +1807,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113399422</v>
+        <v>113399418</v>
       </c>
       <c r="B13" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1878,10 +1873,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>286408</v>
+        <v>286273</v>
       </c>
       <c r="R13" t="n">
-        <v>6507718</v>
+        <v>6507549</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1945,10 +1940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113399455</v>
+        <v>113399443</v>
       </c>
       <c r="B14" t="n">
-        <v>95984</v>
+        <v>56785</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,25 +1952,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>286525</v>
+        <v>286465</v>
       </c>
       <c r="R14" t="n">
-        <v>6508767</v>
+        <v>6508688</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2021,6 +2016,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2047,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399413</v>
+        <v>113399461</v>
       </c>
       <c r="B15" t="n">
-        <v>56782</v>
+        <v>99608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2059,25 +2059,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>286327</v>
+        <v>286239</v>
       </c>
       <c r="R15" t="n">
-        <v>6508012</v>
+        <v>6507778</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2123,11 +2123,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2154,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399448</v>
+        <v>113399458</v>
       </c>
       <c r="B16" t="n">
-        <v>91363</v>
+        <v>95988</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2166,25 +2161,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>2606</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2189,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>286525</v>
+        <v>286751</v>
       </c>
       <c r="R16" t="n">
-        <v>6508258</v>
+        <v>6508904</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2230,11 +2225,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2261,10 +2251,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399429</v>
+        <v>113399431</v>
       </c>
       <c r="B17" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,10 +2291,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>286485</v>
+        <v>286459</v>
       </c>
       <c r="R17" t="n">
-        <v>6508336</v>
+        <v>6508392</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2368,10 +2358,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399418</v>
+        <v>113399434</v>
       </c>
       <c r="B18" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2408,10 +2398,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>286273</v>
+        <v>286601</v>
       </c>
       <c r="R18" t="n">
-        <v>6507549</v>
+        <v>6508623</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2475,10 +2465,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399449</v>
+        <v>113399429</v>
       </c>
       <c r="B19" t="n">
-        <v>91363</v>
+        <v>56785</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,21 +2481,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2515,10 +2505,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>286530</v>
+        <v>286485</v>
       </c>
       <c r="R19" t="n">
-        <v>6508258</v>
+        <v>6508336</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2551,6 +2541,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2577,10 +2572,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399405</v>
+        <v>113399449</v>
       </c>
       <c r="B20" t="n">
-        <v>93789</v>
+        <v>91367</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2589,25 +2584,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2810</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2617,10 +2612,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>286655</v>
+        <v>286530</v>
       </c>
       <c r="R20" t="n">
-        <v>6508854</v>
+        <v>6508258</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2679,10 +2674,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113399463</v>
+        <v>113399411</v>
       </c>
       <c r="B21" t="n">
-        <v>99604</v>
+        <v>95628</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2695,21 +2690,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>2569</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2719,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>286229</v>
+        <v>286712</v>
       </c>
       <c r="R21" t="n">
-        <v>6507839</v>
+        <v>6508906</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2781,10 +2776,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113399442</v>
+        <v>113399437</v>
       </c>
       <c r="B22" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>286541</v>
+        <v>286715</v>
       </c>
       <c r="R22" t="n">
-        <v>6508510</v>
+        <v>6508776</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2861,7 +2856,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2888,10 +2883,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113399436</v>
+        <v>113399408</v>
       </c>
       <c r="B23" t="n">
-        <v>56782</v>
+        <v>56769</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2904,16 +2899,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2928,10 +2923,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>286684</v>
+        <v>286479</v>
       </c>
       <c r="R23" t="n">
-        <v>6508737</v>
+        <v>6508372</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2968,7 +2963,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2995,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113399419</v>
+        <v>113399409</v>
       </c>
       <c r="B24" t="n">
-        <v>56782</v>
+        <v>56769</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3011,16 +3006,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3035,10 +3030,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>286311</v>
+        <v>286461</v>
       </c>
       <c r="R24" t="n">
-        <v>6507585</v>
+        <v>6508704</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3075,7 +3070,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3102,10 +3097,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113399423</v>
+        <v>113399436</v>
       </c>
       <c r="B25" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3142,10 +3137,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>286426</v>
+        <v>286684</v>
       </c>
       <c r="R25" t="n">
-        <v>6507790</v>
+        <v>6508737</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3209,10 +3204,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113399427</v>
+        <v>113399425</v>
       </c>
       <c r="B26" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3249,10 +3244,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>286422</v>
+        <v>286469</v>
       </c>
       <c r="R26" t="n">
-        <v>6508051</v>
+        <v>6508059</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3316,10 +3311,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113399426</v>
+        <v>113399420</v>
       </c>
       <c r="B27" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3356,10 +3351,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>286454</v>
+        <v>286325</v>
       </c>
       <c r="R27" t="n">
-        <v>6508073</v>
+        <v>6507609</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3423,10 +3418,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113399425</v>
+        <v>113399439</v>
       </c>
       <c r="B28" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3463,10 +3458,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>286469</v>
+        <v>286834</v>
       </c>
       <c r="R28" t="n">
-        <v>6508059</v>
+        <v>6508948</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3530,10 +3525,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113399434</v>
+        <v>113399419</v>
       </c>
       <c r="B29" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3570,10 +3565,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>286601</v>
+        <v>286311</v>
       </c>
       <c r="R29" t="n">
-        <v>6508623</v>
+        <v>6507585</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3637,10 +3632,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113399437</v>
+        <v>113399428</v>
       </c>
       <c r="B30" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3677,10 +3672,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>286715</v>
+        <v>286459</v>
       </c>
       <c r="R30" t="n">
-        <v>6508776</v>
+        <v>6508160</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3744,10 +3739,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113399440</v>
+        <v>113399413</v>
       </c>
       <c r="B31" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3784,10 +3779,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>286483</v>
+        <v>286327</v>
       </c>
       <c r="R31" t="n">
-        <v>6508722</v>
+        <v>6508012</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3851,10 +3846,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113399421</v>
+        <v>113399464</v>
       </c>
       <c r="B32" t="n">
-        <v>56782</v>
+        <v>94146</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3863,25 +3858,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3891,10 +3886,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>286411</v>
+        <v>286444</v>
       </c>
       <c r="R32" t="n">
-        <v>6507674</v>
+        <v>6508165</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3927,11 +3922,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3958,10 +3948,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113399417</v>
+        <v>113399455</v>
       </c>
       <c r="B33" t="n">
-        <v>56782</v>
+        <v>95988</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3970,25 +3960,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3998,10 +3988,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>286266</v>
+        <v>286525</v>
       </c>
       <c r="R33" t="n">
-        <v>6507549</v>
+        <v>6508767</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4034,11 +4024,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4065,10 +4050,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113399408</v>
+        <v>113399460</v>
       </c>
       <c r="B34" t="n">
-        <v>56766</v>
+        <v>95988</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4077,25 +4062,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2606</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4105,10 +4090,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>286479</v>
+        <v>286595</v>
       </c>
       <c r="R34" t="n">
-        <v>6508372</v>
+        <v>6508872</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4141,11 +4126,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4172,10 +4152,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113399459</v>
+        <v>113399440</v>
       </c>
       <c r="B35" t="n">
-        <v>95984</v>
+        <v>56785</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4184,25 +4164,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4212,10 +4192,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>286600</v>
+        <v>286483</v>
       </c>
       <c r="R35" t="n">
-        <v>6508882</v>
+        <v>6508722</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4248,6 +4228,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4274,10 +4259,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113399433</v>
+        <v>113399426</v>
       </c>
       <c r="B36" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4314,10 +4299,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>286505</v>
+        <v>286454</v>
       </c>
       <c r="R36" t="n">
-        <v>6508433</v>
+        <v>6508073</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4381,10 +4366,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113399460</v>
+        <v>113399417</v>
       </c>
       <c r="B37" t="n">
-        <v>95984</v>
+        <v>56785</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4393,25 +4378,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4421,10 +4406,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>286595</v>
+        <v>286266</v>
       </c>
       <c r="R37" t="n">
-        <v>6508872</v>
+        <v>6507549</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4457,6 +4442,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4483,10 +4473,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113399456</v>
+        <v>113399442</v>
       </c>
       <c r="B38" t="n">
-        <v>95984</v>
+        <v>56785</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4495,25 +4485,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4523,10 +4513,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>286522</v>
+        <v>286541</v>
       </c>
       <c r="R38" t="n">
-        <v>6508764</v>
+        <v>6508510</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4559,6 +4549,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4585,10 +4580,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113399443</v>
+        <v>113399448</v>
       </c>
       <c r="B39" t="n">
-        <v>56782</v>
+        <v>91367</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4601,21 +4596,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4625,10 +4620,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>286465</v>
+        <v>286525</v>
       </c>
       <c r="R39" t="n">
-        <v>6508688</v>
+        <v>6508258</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4665,7 +4660,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4692,10 +4687,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113399432</v>
+        <v>113399456</v>
       </c>
       <c r="B40" t="n">
-        <v>56782</v>
+        <v>95988</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4704,25 +4699,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4732,10 +4727,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>286495</v>
+        <v>286522</v>
       </c>
       <c r="R40" t="n">
-        <v>6508424</v>
+        <v>6508764</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4768,11 +4763,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4799,10 +4789,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113399438</v>
+        <v>113399427</v>
       </c>
       <c r="B41" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4839,10 +4829,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>286835</v>
+        <v>286422</v>
       </c>
       <c r="R41" t="n">
-        <v>6508956</v>
+        <v>6508051</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4906,10 +4896,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113399458</v>
+        <v>113399421</v>
       </c>
       <c r="B42" t="n">
-        <v>95984</v>
+        <v>56785</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4918,25 +4908,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4946,10 +4936,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>286751</v>
+        <v>286411</v>
       </c>
       <c r="R42" t="n">
-        <v>6508904</v>
+        <v>6507674</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4982,6 +4972,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5008,10 +5003,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399404</v>
+        <v>113399424</v>
       </c>
       <c r="B43" t="n">
-        <v>93789</v>
+        <v>56785</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5020,25 +5015,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5048,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286719</v>
+        <v>286495</v>
       </c>
       <c r="R43" t="n">
-        <v>6508879</v>
+        <v>6508076</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5084,6 +5079,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5110,10 +5110,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399428</v>
+        <v>113399457</v>
       </c>
       <c r="B44" t="n">
-        <v>56782</v>
+        <v>95988</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5122,25 +5122,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>286459</v>
+        <v>286398</v>
       </c>
       <c r="R44" t="n">
-        <v>6508160</v>
+        <v>6508131</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5186,11 +5186,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5217,10 +5212,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113399464</v>
+        <v>113399422</v>
       </c>
       <c r="B45" t="n">
-        <v>94142</v>
+        <v>56785</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5229,25 +5224,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5257,10 +5252,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>286444</v>
+        <v>286408</v>
       </c>
       <c r="R45" t="n">
-        <v>6508165</v>
+        <v>6507718</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5293,6 +5288,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5319,10 +5319,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113399412</v>
+        <v>113399435</v>
       </c>
       <c r="B46" t="n">
-        <v>95624</v>
+        <v>56785</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5331,25 +5331,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>286668</v>
+        <v>286667</v>
       </c>
       <c r="R46" t="n">
-        <v>6508839</v>
+        <v>6508726</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5395,6 +5395,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5421,10 +5426,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113399414</v>
+        <v>113399423</v>
       </c>
       <c r="B47" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5461,10 +5466,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>286242</v>
+        <v>286426</v>
       </c>
       <c r="R47" t="n">
-        <v>6507840</v>
+        <v>6507790</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5528,10 +5533,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113399424</v>
+        <v>113399412</v>
       </c>
       <c r="B48" t="n">
-        <v>56782</v>
+        <v>95628</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5540,25 +5545,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5568,10 +5573,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>286495</v>
+        <v>286668</v>
       </c>
       <c r="R48" t="n">
-        <v>6508076</v>
+        <v>6508839</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5604,11 +5609,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5635,10 +5635,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113399457</v>
+        <v>113399430</v>
       </c>
       <c r="B49" t="n">
-        <v>95984</v>
+        <v>56785</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5647,25 +5647,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>286398</v>
+        <v>286476</v>
       </c>
       <c r="R49" t="n">
-        <v>6508131</v>
+        <v>6508348</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5711,6 +5711,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5737,10 +5742,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113399409</v>
+        <v>113399463</v>
       </c>
       <c r="B50" t="n">
-        <v>56766</v>
+        <v>99608</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5749,25 +5754,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5777,10 +5782,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>286461</v>
+        <v>286229</v>
       </c>
       <c r="R50" t="n">
-        <v>6508704</v>
+        <v>6507839</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5813,11 +5818,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -1211,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113399414</v>
+        <v>113399405</v>
       </c>
       <c r="B7" t="n">
-        <v>56785</v>
+        <v>93793</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,25 +1223,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>286242</v>
+        <v>286655</v>
       </c>
       <c r="R7" t="n">
-        <v>6507840</v>
+        <v>6508854</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,11 +1287,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113399405</v>
+        <v>113399410</v>
       </c>
       <c r="B8" t="n">
-        <v>93793</v>
+        <v>95628</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1334,21 +1329,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1358,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>286655</v>
+        <v>286724</v>
       </c>
       <c r="R8" t="n">
-        <v>6508854</v>
+        <v>6508823</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1420,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399410</v>
+        <v>113399414</v>
       </c>
       <c r="B9" t="n">
-        <v>95628</v>
+        <v>56785</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,25 +1427,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>286724</v>
+        <v>286242</v>
       </c>
       <c r="R9" t="n">
-        <v>6508823</v>
+        <v>6507840</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,6 +1491,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2149,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399458</v>
+        <v>113399431</v>
       </c>
       <c r="B16" t="n">
-        <v>95988</v>
+        <v>56785</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,25 +2161,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>286751</v>
+        <v>286459</v>
       </c>
       <c r="R16" t="n">
-        <v>6508904</v>
+        <v>6508392</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2225,6 +2225,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2251,7 +2256,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399431</v>
+        <v>113399434</v>
       </c>
       <c r="B17" t="n">
         <v>56785</v>
@@ -2291,10 +2296,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>286459</v>
+        <v>286601</v>
       </c>
       <c r="R17" t="n">
-        <v>6508392</v>
+        <v>6508623</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2358,10 +2363,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399434</v>
+        <v>113399458</v>
       </c>
       <c r="B18" t="n">
-        <v>56785</v>
+        <v>95988</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2370,25 +2375,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2398,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>286601</v>
+        <v>286751</v>
       </c>
       <c r="R18" t="n">
-        <v>6508623</v>
+        <v>6508904</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2434,11 +2439,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2883,7 +2883,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113399408</v>
+        <v>113399409</v>
       </c>
       <c r="B23" t="n">
         <v>56769</v>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>286479</v>
+        <v>286461</v>
       </c>
       <c r="R23" t="n">
-        <v>6508372</v>
+        <v>6508704</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rnghack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2990,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113399409</v>
+        <v>113399419</v>
       </c>
       <c r="B24" t="n">
-        <v>56769</v>
+        <v>56785</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3006,16 +3006,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>286461</v>
+        <v>286311</v>
       </c>
       <c r="R24" t="n">
-        <v>6508704</v>
+        <v>6507585</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3097,10 +3097,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113399436</v>
+        <v>113399408</v>
       </c>
       <c r="B25" t="n">
-        <v>56785</v>
+        <v>56769</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3113,16 +3113,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>286684</v>
+        <v>286479</v>
       </c>
       <c r="R25" t="n">
-        <v>6508737</v>
+        <v>6508372</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3204,7 +3204,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113399425</v>
+        <v>113399436</v>
       </c>
       <c r="B26" t="n">
         <v>56785</v>
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>286469</v>
+        <v>286684</v>
       </c>
       <c r="R26" t="n">
-        <v>6508059</v>
+        <v>6508737</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3311,7 +3311,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113399420</v>
+        <v>113399425</v>
       </c>
       <c r="B27" t="n">
         <v>56785</v>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>286325</v>
+        <v>286469</v>
       </c>
       <c r="R27" t="n">
-        <v>6507609</v>
+        <v>6508059</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113399439</v>
+        <v>113399420</v>
       </c>
       <c r="B28" t="n">
         <v>56785</v>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>286834</v>
+        <v>286325</v>
       </c>
       <c r="R28" t="n">
-        <v>6508948</v>
+        <v>6507609</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3525,7 +3525,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113399419</v>
+        <v>113399439</v>
       </c>
       <c r="B29" t="n">
         <v>56785</v>
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>286311</v>
+        <v>286834</v>
       </c>
       <c r="R29" t="n">
-        <v>6507585</v>
+        <v>6508948</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4580,10 +4580,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113399448</v>
+        <v>113399456</v>
       </c>
       <c r="B39" t="n">
-        <v>91367</v>
+        <v>95988</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4592,25 +4592,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>2606</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>286525</v>
+        <v>286522</v>
       </c>
       <c r="R39" t="n">
-        <v>6508258</v>
+        <v>6508764</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4656,11 +4656,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4687,10 +4682,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113399456</v>
+        <v>113399427</v>
       </c>
       <c r="B40" t="n">
-        <v>95988</v>
+        <v>56785</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4699,25 +4694,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4727,10 +4722,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>286522</v>
+        <v>286422</v>
       </c>
       <c r="R40" t="n">
-        <v>6508764</v>
+        <v>6508051</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4763,6 +4758,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4789,7 +4789,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113399427</v>
+        <v>113399424</v>
       </c>
       <c r="B41" t="n">
         <v>56785</v>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>286422</v>
+        <v>286495</v>
       </c>
       <c r="R41" t="n">
-        <v>6508051</v>
+        <v>6508076</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5003,10 +5003,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399424</v>
+        <v>113399448</v>
       </c>
       <c r="B43" t="n">
-        <v>56785</v>
+        <v>91367</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5019,21 +5019,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286495</v>
+        <v>286525</v>
       </c>
       <c r="R43" t="n">
-        <v>6508076</v>
+        <v>6508258</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -890,7 +890,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113399441</v>
+        <v>113399419</v>
       </c>
       <c r="B4" t="n">
         <v>56785</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>286510</v>
+        <v>286311</v>
       </c>
       <c r="R4" t="n">
-        <v>6508675</v>
+        <v>6507585</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -997,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113399432</v>
+        <v>113399436</v>
       </c>
       <c r="B5" t="n">
         <v>56785</v>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>286495</v>
+        <v>286684</v>
       </c>
       <c r="R5" t="n">
-        <v>6508424</v>
+        <v>6508737</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113399438</v>
+        <v>113399417</v>
       </c>
       <c r="B6" t="n">
         <v>56785</v>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>286835</v>
+        <v>286266</v>
       </c>
       <c r="R6" t="n">
-        <v>6508956</v>
+        <v>6507549</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113399405</v>
+        <v>113399414</v>
       </c>
       <c r="B7" t="n">
-        <v>93793</v>
+        <v>56785</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,25 +1223,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>286655</v>
+        <v>286242</v>
       </c>
       <c r="R7" t="n">
-        <v>6508854</v>
+        <v>6507840</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,6 +1287,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113399410</v>
+        <v>113399413</v>
       </c>
       <c r="B8" t="n">
-        <v>95628</v>
+        <v>56785</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,25 +1330,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1353,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>286724</v>
+        <v>286327</v>
       </c>
       <c r="R8" t="n">
-        <v>6508823</v>
+        <v>6508012</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,6 +1394,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399414</v>
+        <v>113399463</v>
       </c>
       <c r="B9" t="n">
-        <v>56785</v>
+        <v>99608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1427,25 +1437,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>286242</v>
+        <v>286229</v>
       </c>
       <c r="R9" t="n">
-        <v>6507840</v>
+        <v>6507839</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,11 +1501,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399433</v>
+        <v>113399422</v>
       </c>
       <c r="B10" t="n">
         <v>56785</v>
@@ -1562,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>286505</v>
+        <v>286408</v>
       </c>
       <c r="R10" t="n">
-        <v>6508433</v>
+        <v>6507718</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1629,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399459</v>
+        <v>113399433</v>
       </c>
       <c r="B11" t="n">
-        <v>95988</v>
+        <v>56785</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>286600</v>
+        <v>286505</v>
       </c>
       <c r="R11" t="n">
-        <v>6508882</v>
+        <v>6508433</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1705,6 +1710,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1731,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399404</v>
+        <v>113399455</v>
       </c>
       <c r="B12" t="n">
-        <v>93793</v>
+        <v>95988</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,21 +1757,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1771,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>286719</v>
+        <v>286525</v>
       </c>
       <c r="R12" t="n">
-        <v>6508879</v>
+        <v>6508767</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1833,7 +1843,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113399418</v>
+        <v>113399432</v>
       </c>
       <c r="B13" t="n">
         <v>56785</v>
@@ -1873,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>286273</v>
+        <v>286495</v>
       </c>
       <c r="R13" t="n">
-        <v>6507549</v>
+        <v>6508424</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1940,10 +1950,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113399443</v>
+        <v>113399405</v>
       </c>
       <c r="B14" t="n">
-        <v>56785</v>
+        <v>93793</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1952,25 +1962,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1980,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>286465</v>
+        <v>286655</v>
       </c>
       <c r="R14" t="n">
-        <v>6508688</v>
+        <v>6508854</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2016,11 +2026,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2047,10 +2052,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399461</v>
+        <v>113399464</v>
       </c>
       <c r="B15" t="n">
-        <v>99608</v>
+        <v>94146</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2063,21 +2068,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>286239</v>
+        <v>286444</v>
       </c>
       <c r="R15" t="n">
-        <v>6507778</v>
+        <v>6508165</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2149,10 +2154,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399431</v>
+        <v>113399457</v>
       </c>
       <c r="B16" t="n">
-        <v>56785</v>
+        <v>95988</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,25 +2166,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2189,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>286459</v>
+        <v>286398</v>
       </c>
       <c r="R16" t="n">
-        <v>6508392</v>
+        <v>6508131</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2225,11 +2230,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2256,7 +2256,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399434</v>
+        <v>113399440</v>
       </c>
       <c r="B17" t="n">
         <v>56785</v>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>286601</v>
+        <v>286483</v>
       </c>
       <c r="R17" t="n">
-        <v>6508623</v>
+        <v>6508722</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2363,10 +2363,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399458</v>
+        <v>113399448</v>
       </c>
       <c r="B18" t="n">
-        <v>95988</v>
+        <v>91367</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2375,25 +2375,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2606</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>286751</v>
+        <v>286525</v>
       </c>
       <c r="R18" t="n">
-        <v>6508904</v>
+        <v>6508258</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2439,6 +2439,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2465,7 +2470,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399429</v>
+        <v>113399428</v>
       </c>
       <c r="B19" t="n">
         <v>56785</v>
@@ -2505,10 +2510,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>286485</v>
+        <v>286459</v>
       </c>
       <c r="R19" t="n">
-        <v>6508336</v>
+        <v>6508160</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2572,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399449</v>
+        <v>113399418</v>
       </c>
       <c r="B20" t="n">
-        <v>91367</v>
+        <v>56785</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2588,21 +2593,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2612,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>286530</v>
+        <v>286273</v>
       </c>
       <c r="R20" t="n">
-        <v>6508258</v>
+        <v>6507549</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2648,6 +2653,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2674,10 +2684,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113399411</v>
+        <v>113399424</v>
       </c>
       <c r="B21" t="n">
-        <v>95628</v>
+        <v>56785</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2686,25 +2696,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2714,10 +2724,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>286712</v>
+        <v>286495</v>
       </c>
       <c r="R21" t="n">
-        <v>6508906</v>
+        <v>6508076</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2750,6 +2760,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2776,7 +2791,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113399437</v>
+        <v>113399434</v>
       </c>
       <c r="B22" t="n">
         <v>56785</v>
@@ -2816,10 +2831,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>286715</v>
+        <v>286601</v>
       </c>
       <c r="R22" t="n">
-        <v>6508776</v>
+        <v>6508623</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2883,10 +2898,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113399409</v>
+        <v>113399430</v>
       </c>
       <c r="B23" t="n">
-        <v>56769</v>
+        <v>56785</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2899,16 +2914,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2923,10 +2938,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>286461</v>
+        <v>286476</v>
       </c>
       <c r="R23" t="n">
-        <v>6508704</v>
+        <v>6508348</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2963,7 +2978,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2990,10 +3005,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113399419</v>
+        <v>113399404</v>
       </c>
       <c r="B24" t="n">
-        <v>56785</v>
+        <v>93793</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3002,25 +3017,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3030,10 +3045,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>286311</v>
+        <v>286719</v>
       </c>
       <c r="R24" t="n">
-        <v>6507585</v>
+        <v>6508879</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3066,11 +3081,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3097,10 +3107,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113399408</v>
+        <v>113399442</v>
       </c>
       <c r="B25" t="n">
-        <v>56769</v>
+        <v>56785</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3113,16 +3123,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3137,10 +3147,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>286479</v>
+        <v>286541</v>
       </c>
       <c r="R25" t="n">
-        <v>6508372</v>
+        <v>6508510</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3177,7 +3187,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rnghack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3204,10 +3214,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113399436</v>
+        <v>113399449</v>
       </c>
       <c r="B26" t="n">
-        <v>56785</v>
+        <v>91367</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3220,21 +3230,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3244,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>286684</v>
+        <v>286530</v>
       </c>
       <c r="R26" t="n">
-        <v>6508737</v>
+        <v>6508258</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3280,11 +3290,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3311,7 +3316,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113399425</v>
+        <v>113399435</v>
       </c>
       <c r="B27" t="n">
         <v>56785</v>
@@ -3351,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>286469</v>
+        <v>286667</v>
       </c>
       <c r="R27" t="n">
-        <v>6508059</v>
+        <v>6508726</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3418,10 +3423,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113399420</v>
+        <v>113399461</v>
       </c>
       <c r="B28" t="n">
-        <v>56785</v>
+        <v>99608</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3430,25 +3435,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3458,10 +3463,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>286325</v>
+        <v>286239</v>
       </c>
       <c r="R28" t="n">
-        <v>6507609</v>
+        <v>6507778</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3494,11 +3499,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3525,10 +3525,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113399439</v>
+        <v>113399410</v>
       </c>
       <c r="B29" t="n">
-        <v>56785</v>
+        <v>95628</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3537,25 +3537,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>286834</v>
+        <v>286724</v>
       </c>
       <c r="R29" t="n">
-        <v>6508948</v>
+        <v>6508823</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3601,11 +3601,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3632,10 +3627,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113399428</v>
+        <v>113399459</v>
       </c>
       <c r="B30" t="n">
-        <v>56785</v>
+        <v>95988</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3644,25 +3639,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3672,10 +3667,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>286459</v>
+        <v>286600</v>
       </c>
       <c r="R30" t="n">
-        <v>6508160</v>
+        <v>6508882</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3708,11 +3703,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3739,10 +3729,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113399413</v>
+        <v>113399456</v>
       </c>
       <c r="B31" t="n">
-        <v>56785</v>
+        <v>95988</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3751,25 +3741,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3779,10 +3769,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>286327</v>
+        <v>286522</v>
       </c>
       <c r="R31" t="n">
-        <v>6508012</v>
+        <v>6508764</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3815,11 +3805,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3846,10 +3831,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113399464</v>
+        <v>113399421</v>
       </c>
       <c r="B32" t="n">
-        <v>94146</v>
+        <v>56785</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3858,25 +3843,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3886,10 +3871,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>286444</v>
+        <v>286411</v>
       </c>
       <c r="R32" t="n">
-        <v>6508165</v>
+        <v>6507674</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3922,6 +3907,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3948,10 +3938,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113399455</v>
+        <v>113399431</v>
       </c>
       <c r="B33" t="n">
-        <v>95988</v>
+        <v>56785</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3960,25 +3950,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3988,10 +3978,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>286525</v>
+        <v>286459</v>
       </c>
       <c r="R33" t="n">
-        <v>6508767</v>
+        <v>6508392</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4024,6 +4014,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4050,10 +4045,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113399460</v>
+        <v>113399438</v>
       </c>
       <c r="B34" t="n">
-        <v>95988</v>
+        <v>56785</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4062,25 +4057,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4090,10 +4085,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>286595</v>
+        <v>286835</v>
       </c>
       <c r="R34" t="n">
-        <v>6508872</v>
+        <v>6508956</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4126,6 +4121,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4152,10 +4152,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113399440</v>
+        <v>113399460</v>
       </c>
       <c r="B35" t="n">
-        <v>56785</v>
+        <v>95988</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4164,25 +4164,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>286483</v>
+        <v>286595</v>
       </c>
       <c r="R35" t="n">
-        <v>6508722</v>
+        <v>6508872</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4228,11 +4228,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4259,10 +4254,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113399426</v>
+        <v>113399408</v>
       </c>
       <c r="B36" t="n">
-        <v>56785</v>
+        <v>56769</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4275,16 +4270,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4299,10 +4294,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>286454</v>
+        <v>286479</v>
       </c>
       <c r="R36" t="n">
-        <v>6508073</v>
+        <v>6508372</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4339,7 +4334,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4366,7 +4361,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113399417</v>
+        <v>113399425</v>
       </c>
       <c r="B37" t="n">
         <v>56785</v>
@@ -4406,10 +4401,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>286266</v>
+        <v>286469</v>
       </c>
       <c r="R37" t="n">
-        <v>6507549</v>
+        <v>6508059</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4473,10 +4468,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113399442</v>
+        <v>113399458</v>
       </c>
       <c r="B38" t="n">
-        <v>56785</v>
+        <v>95988</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4485,25 +4480,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4513,10 +4508,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>286541</v>
+        <v>286751</v>
       </c>
       <c r="R38" t="n">
-        <v>6508510</v>
+        <v>6508904</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4549,11 +4544,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4580,10 +4570,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113399456</v>
+        <v>113399411</v>
       </c>
       <c r="B39" t="n">
-        <v>95988</v>
+        <v>95628</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4596,21 +4586,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2606</v>
+        <v>2569</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4620,10 +4610,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>286522</v>
+        <v>286712</v>
       </c>
       <c r="R39" t="n">
-        <v>6508764</v>
+        <v>6508906</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4682,7 +4672,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113399427</v>
+        <v>113399426</v>
       </c>
       <c r="B40" t="n">
         <v>56785</v>
@@ -4722,10 +4712,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>286422</v>
+        <v>286454</v>
       </c>
       <c r="R40" t="n">
-        <v>6508051</v>
+        <v>6508073</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4789,7 +4779,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113399424</v>
+        <v>113399441</v>
       </c>
       <c r="B41" t="n">
         <v>56785</v>
@@ -4829,10 +4819,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>286495</v>
+        <v>286510</v>
       </c>
       <c r="R41" t="n">
-        <v>6508076</v>
+        <v>6508675</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4896,7 +4886,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113399421</v>
+        <v>113399423</v>
       </c>
       <c r="B42" t="n">
         <v>56785</v>
@@ -4936,10 +4926,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>286411</v>
+        <v>286426</v>
       </c>
       <c r="R42" t="n">
-        <v>6507674</v>
+        <v>6507790</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5003,10 +4993,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399448</v>
+        <v>113399427</v>
       </c>
       <c r="B43" t="n">
-        <v>91367</v>
+        <v>56785</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5019,21 +5009,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5043,10 +5033,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286525</v>
+        <v>286422</v>
       </c>
       <c r="R43" t="n">
-        <v>6508258</v>
+        <v>6508051</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5083,7 +5073,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>9 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5110,10 +5100,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399457</v>
+        <v>113399429</v>
       </c>
       <c r="B44" t="n">
-        <v>95988</v>
+        <v>56785</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5122,25 +5112,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5150,10 +5140,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>286398</v>
+        <v>286485</v>
       </c>
       <c r="R44" t="n">
-        <v>6508131</v>
+        <v>6508336</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5186,6 +5176,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5212,7 +5207,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113399422</v>
+        <v>113399439</v>
       </c>
       <c r="B45" t="n">
         <v>56785</v>
@@ -5252,10 +5247,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>286408</v>
+        <v>286834</v>
       </c>
       <c r="R45" t="n">
-        <v>6507718</v>
+        <v>6508948</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5319,7 +5314,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113399435</v>
+        <v>113399443</v>
       </c>
       <c r="B46" t="n">
         <v>56785</v>
@@ -5359,10 +5354,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>286667</v>
+        <v>286465</v>
       </c>
       <c r="R46" t="n">
-        <v>6508726</v>
+        <v>6508688</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5399,7 +5394,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5426,7 +5421,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113399423</v>
+        <v>113399420</v>
       </c>
       <c r="B47" t="n">
         <v>56785</v>
@@ -5466,10 +5461,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>286426</v>
+        <v>286325</v>
       </c>
       <c r="R47" t="n">
-        <v>6507790</v>
+        <v>6507609</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5533,10 +5528,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113399412</v>
+        <v>113399409</v>
       </c>
       <c r="B48" t="n">
-        <v>95628</v>
+        <v>56769</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5545,25 +5540,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2569</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5573,10 +5568,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>286668</v>
+        <v>286461</v>
       </c>
       <c r="R48" t="n">
-        <v>6508839</v>
+        <v>6508704</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5609,6 +5604,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5635,7 +5635,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113399430</v>
+        <v>113399437</v>
       </c>
       <c r="B49" t="n">
         <v>56785</v>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>286476</v>
+        <v>286715</v>
       </c>
       <c r="R49" t="n">
-        <v>6508348</v>
+        <v>6508776</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5742,10 +5742,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113399463</v>
+        <v>113399412</v>
       </c>
       <c r="B50" t="n">
-        <v>99608</v>
+        <v>95628</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5758,21 +5758,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>2569</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5782,10 +5782,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>286229</v>
+        <v>286668</v>
       </c>
       <c r="R50" t="n">
-        <v>6507839</v>
+        <v>6508839</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>113354383</v>
       </c>
       <c r="B3" t="n">
-        <v>90094</v>
+        <v>90100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113399419</v>
+        <v>113399430</v>
       </c>
       <c r="B4" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>286311</v>
+        <v>286476</v>
       </c>
       <c r="R4" t="n">
-        <v>6507585</v>
+        <v>6508348</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113399436</v>
+        <v>113399422</v>
       </c>
       <c r="B5" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>286684</v>
+        <v>286408</v>
       </c>
       <c r="R5" t="n">
-        <v>6508737</v>
+        <v>6507718</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113399417</v>
+        <v>113399409</v>
       </c>
       <c r="B6" t="n">
-        <v>56785</v>
+        <v>56773</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>286266</v>
+        <v>286461</v>
       </c>
       <c r="R6" t="n">
-        <v>6507549</v>
+        <v>6508704</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113399414</v>
+        <v>113399457</v>
       </c>
       <c r="B7" t="n">
-        <v>56785</v>
+        <v>95994</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,25 +1223,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>286242</v>
+        <v>286398</v>
       </c>
       <c r="R7" t="n">
-        <v>6507840</v>
+        <v>6508131</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,11 +1287,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113399413</v>
+        <v>113399441</v>
       </c>
       <c r="B8" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>286327</v>
+        <v>286510</v>
       </c>
       <c r="R8" t="n">
-        <v>6508012</v>
+        <v>6508675</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1425,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399463</v>
+        <v>113399438</v>
       </c>
       <c r="B9" t="n">
-        <v>99608</v>
+        <v>56789</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,25 +1432,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1465,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>286229</v>
+        <v>286835</v>
       </c>
       <c r="R9" t="n">
-        <v>6507839</v>
+        <v>6508956</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1501,6 +1496,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399422</v>
+        <v>113399428</v>
       </c>
       <c r="B10" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>286408</v>
+        <v>286459</v>
       </c>
       <c r="R10" t="n">
-        <v>6507718</v>
+        <v>6508160</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399433</v>
+        <v>113399420</v>
       </c>
       <c r="B11" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>286505</v>
+        <v>286325</v>
       </c>
       <c r="R11" t="n">
-        <v>6508433</v>
+        <v>6507609</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399455</v>
+        <v>113399437</v>
       </c>
       <c r="B12" t="n">
-        <v>95988</v>
+        <v>56789</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,25 +1753,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>286525</v>
+        <v>286715</v>
       </c>
       <c r="R12" t="n">
-        <v>6508767</v>
+        <v>6508776</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1817,6 +1817,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113399432</v>
+        <v>113399411</v>
       </c>
       <c r="B13" t="n">
-        <v>56785</v>
+        <v>95634</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,25 +1860,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1888,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>286495</v>
+        <v>286712</v>
       </c>
       <c r="R13" t="n">
-        <v>6508424</v>
+        <v>6508906</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1919,11 +1924,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1950,10 +1950,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113399405</v>
+        <v>113399435</v>
       </c>
       <c r="B14" t="n">
-        <v>93793</v>
+        <v>56789</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1962,25 +1962,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>286655</v>
+        <v>286667</v>
       </c>
       <c r="R14" t="n">
-        <v>6508854</v>
+        <v>6508726</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2026,6 +2026,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2052,10 +2057,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399464</v>
+        <v>113399419</v>
       </c>
       <c r="B15" t="n">
-        <v>94146</v>
+        <v>56789</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2064,25 +2069,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2092,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>286444</v>
+        <v>286311</v>
       </c>
       <c r="R15" t="n">
-        <v>6508165</v>
+        <v>6507585</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2128,6 +2133,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2154,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399457</v>
+        <v>113399426</v>
       </c>
       <c r="B16" t="n">
-        <v>95988</v>
+        <v>56789</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2166,25 +2176,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>286398</v>
+        <v>286454</v>
       </c>
       <c r="R16" t="n">
-        <v>6508131</v>
+        <v>6508073</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2230,6 +2240,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2256,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399440</v>
+        <v>113399455</v>
       </c>
       <c r="B17" t="n">
-        <v>56785</v>
+        <v>95994</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2268,25 +2283,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2296,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>286483</v>
+        <v>286525</v>
       </c>
       <c r="R17" t="n">
-        <v>6508722</v>
+        <v>6508767</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2332,11 +2347,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2363,10 +2373,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399448</v>
+        <v>113399431</v>
       </c>
       <c r="B18" t="n">
-        <v>91367</v>
+        <v>56789</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2379,21 +2389,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>286525</v>
+        <v>286459</v>
       </c>
       <c r="R18" t="n">
-        <v>6508258</v>
+        <v>6508392</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2443,7 +2453,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>9 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2470,10 +2480,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399428</v>
+        <v>113399414</v>
       </c>
       <c r="B19" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>286459</v>
+        <v>286242</v>
       </c>
       <c r="R19" t="n">
-        <v>6508160</v>
+        <v>6507840</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2577,10 +2587,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399418</v>
+        <v>113399461</v>
       </c>
       <c r="B20" t="n">
-        <v>56785</v>
+        <v>99614</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2589,25 +2599,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2617,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>286273</v>
+        <v>286239</v>
       </c>
       <c r="R20" t="n">
-        <v>6507549</v>
+        <v>6507778</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2653,11 +2663,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2684,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113399424</v>
+        <v>113399421</v>
       </c>
       <c r="B21" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>286495</v>
+        <v>286411</v>
       </c>
       <c r="R21" t="n">
-        <v>6508076</v>
+        <v>6507674</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2791,10 +2796,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113399434</v>
+        <v>113399443</v>
       </c>
       <c r="B22" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,10 +2836,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>286601</v>
+        <v>286465</v>
       </c>
       <c r="R22" t="n">
-        <v>6508623</v>
+        <v>6508688</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2871,7 +2876,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2898,10 +2903,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113399430</v>
+        <v>113399429</v>
       </c>
       <c r="B23" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2938,10 +2943,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>286476</v>
+        <v>286485</v>
       </c>
       <c r="R23" t="n">
-        <v>6508348</v>
+        <v>6508336</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3005,10 +3010,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113399404</v>
+        <v>113399408</v>
       </c>
       <c r="B24" t="n">
-        <v>93793</v>
+        <v>56773</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3017,25 +3022,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2810</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3045,10 +3050,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>286719</v>
+        <v>286479</v>
       </c>
       <c r="R24" t="n">
-        <v>6508879</v>
+        <v>6508372</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3081,6 +3086,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3107,10 +3117,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113399442</v>
+        <v>113399433</v>
       </c>
       <c r="B25" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3147,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>286541</v>
+        <v>286505</v>
       </c>
       <c r="R25" t="n">
-        <v>6508510</v>
+        <v>6508433</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3187,7 +3197,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3214,10 +3224,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113399449</v>
+        <v>113399404</v>
       </c>
       <c r="B26" t="n">
-        <v>91367</v>
+        <v>93799</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3226,25 +3236,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>2810</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3254,10 +3264,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>286530</v>
+        <v>286719</v>
       </c>
       <c r="R26" t="n">
-        <v>6508258</v>
+        <v>6508879</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3316,10 +3326,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113399435</v>
+        <v>113399448</v>
       </c>
       <c r="B27" t="n">
-        <v>56785</v>
+        <v>91373</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3332,21 +3342,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3356,10 +3366,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>286667</v>
+        <v>286525</v>
       </c>
       <c r="R27" t="n">
-        <v>6508726</v>
+        <v>6508258</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3396,7 +3406,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3423,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113399461</v>
+        <v>113399442</v>
       </c>
       <c r="B28" t="n">
-        <v>99608</v>
+        <v>56789</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3435,25 +3445,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3463,10 +3473,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>286239</v>
+        <v>286541</v>
       </c>
       <c r="R28" t="n">
-        <v>6507778</v>
+        <v>6508510</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3499,6 +3509,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3528,7 +3543,7 @@
         <v>113399410</v>
       </c>
       <c r="B29" t="n">
-        <v>95628</v>
+        <v>95634</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3627,10 +3642,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113399459</v>
+        <v>113399458</v>
       </c>
       <c r="B30" t="n">
-        <v>95988</v>
+        <v>95994</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3667,10 +3682,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>286600</v>
+        <v>286751</v>
       </c>
       <c r="R30" t="n">
-        <v>6508882</v>
+        <v>6508904</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3729,10 +3744,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113399456</v>
+        <v>113399434</v>
       </c>
       <c r="B31" t="n">
-        <v>95988</v>
+        <v>56789</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3741,25 +3756,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3769,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>286522</v>
+        <v>286601</v>
       </c>
       <c r="R31" t="n">
-        <v>6508764</v>
+        <v>6508623</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3805,6 +3820,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3831,10 +3851,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113399421</v>
+        <v>113399423</v>
       </c>
       <c r="B32" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3871,10 +3891,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>286411</v>
+        <v>286426</v>
       </c>
       <c r="R32" t="n">
-        <v>6507674</v>
+        <v>6507790</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3938,10 +3958,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113399431</v>
+        <v>113399436</v>
       </c>
       <c r="B33" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3978,10 +3998,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>286459</v>
+        <v>286684</v>
       </c>
       <c r="R33" t="n">
-        <v>6508392</v>
+        <v>6508737</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4045,10 +4065,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113399438</v>
+        <v>113399418</v>
       </c>
       <c r="B34" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4085,10 +4105,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>286835</v>
+        <v>286273</v>
       </c>
       <c r="R34" t="n">
-        <v>6508956</v>
+        <v>6507549</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4152,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113399460</v>
+        <v>113399463</v>
       </c>
       <c r="B35" t="n">
-        <v>95988</v>
+        <v>99614</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4168,21 +4188,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2606</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4192,10 +4212,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>286595</v>
+        <v>286229</v>
       </c>
       <c r="R35" t="n">
-        <v>6508872</v>
+        <v>6507839</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4254,10 +4274,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113399408</v>
+        <v>113399412</v>
       </c>
       <c r="B36" t="n">
-        <v>56769</v>
+        <v>95634</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4266,25 +4286,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>2569</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4294,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>286479</v>
+        <v>286668</v>
       </c>
       <c r="R36" t="n">
-        <v>6508372</v>
+        <v>6508839</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4330,11 +4350,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4361,10 +4376,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113399425</v>
+        <v>113399440</v>
       </c>
       <c r="B37" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4401,10 +4416,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>286469</v>
+        <v>286483</v>
       </c>
       <c r="R37" t="n">
-        <v>6508059</v>
+        <v>6508722</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4468,10 +4483,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113399458</v>
+        <v>113399425</v>
       </c>
       <c r="B38" t="n">
-        <v>95988</v>
+        <v>56789</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4480,25 +4495,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4508,10 +4523,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>286751</v>
+        <v>286469</v>
       </c>
       <c r="R38" t="n">
-        <v>6508904</v>
+        <v>6508059</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4544,6 +4559,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4570,10 +4590,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113399411</v>
+        <v>113399424</v>
       </c>
       <c r="B39" t="n">
-        <v>95628</v>
+        <v>56789</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4582,25 +4602,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4610,10 +4630,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>286712</v>
+        <v>286495</v>
       </c>
       <c r="R39" t="n">
-        <v>6508906</v>
+        <v>6508076</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4646,6 +4666,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4672,10 +4697,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113399426</v>
+        <v>113399432</v>
       </c>
       <c r="B40" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4712,10 +4737,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>286454</v>
+        <v>286495</v>
       </c>
       <c r="R40" t="n">
-        <v>6508073</v>
+        <v>6508424</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4779,10 +4804,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113399441</v>
+        <v>113399413</v>
       </c>
       <c r="B41" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4819,10 +4844,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>286510</v>
+        <v>286327</v>
       </c>
       <c r="R41" t="n">
-        <v>6508675</v>
+        <v>6508012</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4886,10 +4911,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113399423</v>
+        <v>113399456</v>
       </c>
       <c r="B42" t="n">
-        <v>56785</v>
+        <v>95994</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4898,25 +4923,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4926,10 +4951,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>286426</v>
+        <v>286522</v>
       </c>
       <c r="R42" t="n">
-        <v>6507790</v>
+        <v>6508764</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4962,11 +4987,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4993,10 +5013,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399427</v>
+        <v>113399459</v>
       </c>
       <c r="B43" t="n">
-        <v>56785</v>
+        <v>95994</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5005,25 +5025,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5033,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286422</v>
+        <v>286600</v>
       </c>
       <c r="R43" t="n">
-        <v>6508051</v>
+        <v>6508882</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5069,11 +5089,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5100,10 +5115,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399429</v>
+        <v>113399449</v>
       </c>
       <c r="B44" t="n">
-        <v>56785</v>
+        <v>91373</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5116,21 +5131,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5140,10 +5155,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>286485</v>
+        <v>286530</v>
       </c>
       <c r="R44" t="n">
-        <v>6508336</v>
+        <v>6508258</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5176,11 +5191,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5207,10 +5217,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113399439</v>
+        <v>113399405</v>
       </c>
       <c r="B45" t="n">
-        <v>56785</v>
+        <v>93799</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5219,25 +5229,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5247,10 +5257,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>286834</v>
+        <v>286655</v>
       </c>
       <c r="R45" t="n">
-        <v>6508948</v>
+        <v>6508854</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5283,11 +5293,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5314,10 +5319,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113399443</v>
+        <v>113399427</v>
       </c>
       <c r="B46" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5354,10 +5359,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>286465</v>
+        <v>286422</v>
       </c>
       <c r="R46" t="n">
-        <v>6508688</v>
+        <v>6508051</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5394,7 +5399,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5421,10 +5426,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113399420</v>
+        <v>113399417</v>
       </c>
       <c r="B47" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5461,10 +5466,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>286325</v>
+        <v>286266</v>
       </c>
       <c r="R47" t="n">
-        <v>6507609</v>
+        <v>6507549</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5528,10 +5533,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113399409</v>
+        <v>113399439</v>
       </c>
       <c r="B48" t="n">
-        <v>56769</v>
+        <v>56789</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5544,16 +5549,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5568,10 +5573,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>286461</v>
+        <v>286834</v>
       </c>
       <c r="R48" t="n">
-        <v>6508704</v>
+        <v>6508948</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5608,7 +5613,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5635,10 +5640,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113399437</v>
+        <v>113399460</v>
       </c>
       <c r="B49" t="n">
-        <v>56785</v>
+        <v>95994</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5647,25 +5652,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5675,10 +5680,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>286715</v>
+        <v>286595</v>
       </c>
       <c r="R49" t="n">
-        <v>6508776</v>
+        <v>6508872</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5711,11 +5716,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5742,10 +5742,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113399412</v>
+        <v>113399464</v>
       </c>
       <c r="B50" t="n">
-        <v>95628</v>
+        <v>94152</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5758,21 +5758,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5782,10 +5782,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>286668</v>
+        <v>286444</v>
       </c>
       <c r="R50" t="n">
-        <v>6508839</v>
+        <v>6508165</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -890,7 +890,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113399430</v>
+        <v>113399426</v>
       </c>
       <c r="B4" t="n">
         <v>56789</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>286476</v>
+        <v>286454</v>
       </c>
       <c r="R4" t="n">
-        <v>6508348</v>
+        <v>6508073</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -997,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113399422</v>
+        <v>113399423</v>
       </c>
       <c r="B5" t="n">
         <v>56789</v>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>286408</v>
+        <v>286426</v>
       </c>
       <c r="R5" t="n">
-        <v>6507718</v>
+        <v>6507790</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113399409</v>
+        <v>113399449</v>
       </c>
       <c r="B6" t="n">
-        <v>56773</v>
+        <v>91373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>286461</v>
+        <v>286530</v>
       </c>
       <c r="R6" t="n">
-        <v>6508704</v>
+        <v>6508258</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1180,11 +1180,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113399457</v>
+        <v>113399418</v>
       </c>
       <c r="B7" t="n">
-        <v>95994</v>
+        <v>56789</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,25 +1218,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>286398</v>
+        <v>286273</v>
       </c>
       <c r="R7" t="n">
-        <v>6508131</v>
+        <v>6507549</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,6 +1282,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113399441</v>
+        <v>113399456</v>
       </c>
       <c r="B8" t="n">
-        <v>56789</v>
+        <v>95994</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,25 +1325,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>286510</v>
+        <v>286522</v>
       </c>
       <c r="R8" t="n">
-        <v>6508675</v>
+        <v>6508764</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,11 +1389,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399438</v>
+        <v>113399461</v>
       </c>
       <c r="B9" t="n">
-        <v>56789</v>
+        <v>99614</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,25 +1427,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>286835</v>
+        <v>286239</v>
       </c>
       <c r="R9" t="n">
-        <v>6508956</v>
+        <v>6507778</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,11 +1491,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,7 +1517,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399428</v>
+        <v>113399443</v>
       </c>
       <c r="B10" t="n">
         <v>56789</v>
@@ -1567,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>286459</v>
+        <v>286465</v>
       </c>
       <c r="R10" t="n">
-        <v>6508160</v>
+        <v>6508688</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1607,7 +1597,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,7 +1624,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399420</v>
+        <v>113399430</v>
       </c>
       <c r="B11" t="n">
         <v>56789</v>
@@ -1674,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>286325</v>
+        <v>286476</v>
       </c>
       <c r="R11" t="n">
-        <v>6507609</v>
+        <v>6508348</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1741,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399437</v>
+        <v>113399457</v>
       </c>
       <c r="B12" t="n">
-        <v>56789</v>
+        <v>95994</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,25 +1743,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>286715</v>
+        <v>286398</v>
       </c>
       <c r="R12" t="n">
-        <v>6508776</v>
+        <v>6508131</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1817,11 +1807,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113399411</v>
+        <v>113399421</v>
       </c>
       <c r="B13" t="n">
-        <v>95634</v>
+        <v>56789</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1860,25 +1845,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1888,10 +1873,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>286712</v>
+        <v>286411</v>
       </c>
       <c r="R13" t="n">
-        <v>6508906</v>
+        <v>6507674</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1924,6 +1909,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1950,7 +1940,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113399435</v>
+        <v>113399438</v>
       </c>
       <c r="B14" t="n">
         <v>56789</v>
@@ -1990,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>286667</v>
+        <v>286835</v>
       </c>
       <c r="R14" t="n">
-        <v>6508726</v>
+        <v>6508956</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2057,7 +2047,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399419</v>
+        <v>113399425</v>
       </c>
       <c r="B15" t="n">
         <v>56789</v>
@@ -2097,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>286311</v>
+        <v>286469</v>
       </c>
       <c r="R15" t="n">
-        <v>6507585</v>
+        <v>6508059</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2164,10 +2154,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399426</v>
+        <v>113399460</v>
       </c>
       <c r="B16" t="n">
-        <v>56789</v>
+        <v>95994</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,25 +2166,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>286454</v>
+        <v>286595</v>
       </c>
       <c r="R16" t="n">
-        <v>6508073</v>
+        <v>6508872</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2240,11 +2230,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2271,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399455</v>
+        <v>113399440</v>
       </c>
       <c r="B17" t="n">
-        <v>95994</v>
+        <v>56789</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,25 +2268,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2296,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>286525</v>
+        <v>286483</v>
       </c>
       <c r="R17" t="n">
-        <v>6508767</v>
+        <v>6508722</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2347,6 +2332,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2373,10 +2363,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399431</v>
+        <v>113399405</v>
       </c>
       <c r="B18" t="n">
-        <v>56789</v>
+        <v>93799</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,25 +2375,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2413,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>286459</v>
+        <v>286655</v>
       </c>
       <c r="R18" t="n">
-        <v>6508392</v>
+        <v>6508854</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2449,11 +2439,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2480,7 +2465,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399414</v>
+        <v>113399417</v>
       </c>
       <c r="B19" t="n">
         <v>56789</v>
@@ -2520,10 +2505,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>286242</v>
+        <v>286266</v>
       </c>
       <c r="R19" t="n">
-        <v>6507840</v>
+        <v>6507549</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2587,7 +2572,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399461</v>
+        <v>113399463</v>
       </c>
       <c r="B20" t="n">
         <v>99614</v>
@@ -2627,10 +2612,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>286239</v>
+        <v>286229</v>
       </c>
       <c r="R20" t="n">
-        <v>6507778</v>
+        <v>6507839</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2689,10 +2674,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113399421</v>
+        <v>113399410</v>
       </c>
       <c r="B21" t="n">
-        <v>56789</v>
+        <v>95634</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2686,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>286411</v>
+        <v>286724</v>
       </c>
       <c r="R21" t="n">
-        <v>6507674</v>
+        <v>6508823</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2765,11 +2750,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2796,7 +2776,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113399443</v>
+        <v>113399424</v>
       </c>
       <c r="B22" t="n">
         <v>56789</v>
@@ -2836,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>286465</v>
+        <v>286495</v>
       </c>
       <c r="R22" t="n">
-        <v>6508688</v>
+        <v>6508076</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2876,7 +2856,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2903,10 +2883,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113399429</v>
+        <v>113399412</v>
       </c>
       <c r="B23" t="n">
-        <v>56789</v>
+        <v>95634</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2915,25 +2895,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2943,10 +2923,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>286485</v>
+        <v>286668</v>
       </c>
       <c r="R23" t="n">
-        <v>6508336</v>
+        <v>6508839</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2979,11 +2959,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3010,10 +2985,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113399408</v>
+        <v>113399439</v>
       </c>
       <c r="B24" t="n">
-        <v>56773</v>
+        <v>56789</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3026,16 +3001,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3050,10 +3025,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>286479</v>
+        <v>286834</v>
       </c>
       <c r="R24" t="n">
-        <v>6508372</v>
+        <v>6508948</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3090,7 +3065,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rnghack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3117,7 +3092,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113399433</v>
+        <v>113399437</v>
       </c>
       <c r="B25" t="n">
         <v>56789</v>
@@ -3157,10 +3132,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>286505</v>
+        <v>286715</v>
       </c>
       <c r="R25" t="n">
-        <v>6508433</v>
+        <v>6508776</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3224,10 +3199,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113399404</v>
+        <v>113399432</v>
       </c>
       <c r="B26" t="n">
-        <v>93799</v>
+        <v>56789</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3236,25 +3211,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3264,10 +3239,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>286719</v>
+        <v>286495</v>
       </c>
       <c r="R26" t="n">
-        <v>6508879</v>
+        <v>6508424</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3300,6 +3275,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3326,10 +3306,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113399448</v>
+        <v>113399435</v>
       </c>
       <c r="B27" t="n">
-        <v>91373</v>
+        <v>56789</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3342,21 +3322,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3366,10 +3346,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>286525</v>
+        <v>286667</v>
       </c>
       <c r="R27" t="n">
-        <v>6508258</v>
+        <v>6508726</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3406,7 +3386,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>9 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3433,7 +3413,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113399442</v>
+        <v>113399419</v>
       </c>
       <c r="B28" t="n">
         <v>56789</v>
@@ -3473,10 +3453,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>286541</v>
+        <v>286311</v>
       </c>
       <c r="R28" t="n">
-        <v>6508510</v>
+        <v>6507585</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3513,7 +3493,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3540,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113399410</v>
+        <v>113399459</v>
       </c>
       <c r="B29" t="n">
-        <v>95634</v>
+        <v>95994</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3556,21 +3536,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2569</v>
+        <v>2606</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3580,10 +3560,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>286724</v>
+        <v>286600</v>
       </c>
       <c r="R29" t="n">
-        <v>6508823</v>
+        <v>6508882</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3642,10 +3622,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113399458</v>
+        <v>113399428</v>
       </c>
       <c r="B30" t="n">
-        <v>95994</v>
+        <v>56789</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3654,25 +3634,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3682,10 +3662,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>286751</v>
+        <v>286459</v>
       </c>
       <c r="R30" t="n">
-        <v>6508904</v>
+        <v>6508160</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3718,6 +3698,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3744,10 +3729,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113399434</v>
+        <v>113399455</v>
       </c>
       <c r="B31" t="n">
-        <v>56789</v>
+        <v>95994</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3756,25 +3741,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3784,10 +3769,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>286601</v>
+        <v>286525</v>
       </c>
       <c r="R31" t="n">
-        <v>6508623</v>
+        <v>6508767</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3820,11 +3805,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3851,7 +3831,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113399423</v>
+        <v>113399441</v>
       </c>
       <c r="B32" t="n">
         <v>56789</v>
@@ -3891,10 +3871,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>286426</v>
+        <v>286510</v>
       </c>
       <c r="R32" t="n">
-        <v>6507790</v>
+        <v>6508675</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3958,10 +3938,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113399436</v>
+        <v>113399408</v>
       </c>
       <c r="B33" t="n">
-        <v>56789</v>
+        <v>56773</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3974,16 +3954,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3998,10 +3978,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>286684</v>
+        <v>286479</v>
       </c>
       <c r="R33" t="n">
-        <v>6508737</v>
+        <v>6508372</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4038,7 +4018,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4065,7 +4045,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113399418</v>
+        <v>113399422</v>
       </c>
       <c r="B34" t="n">
         <v>56789</v>
@@ -4105,10 +4085,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>286273</v>
+        <v>286408</v>
       </c>
       <c r="R34" t="n">
-        <v>6507549</v>
+        <v>6507718</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4172,10 +4152,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113399463</v>
+        <v>113399420</v>
       </c>
       <c r="B35" t="n">
-        <v>99614</v>
+        <v>56789</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4184,25 +4164,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4212,10 +4192,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>286229</v>
+        <v>286325</v>
       </c>
       <c r="R35" t="n">
-        <v>6507839</v>
+        <v>6507609</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4248,6 +4228,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4274,10 +4259,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113399412</v>
+        <v>113399448</v>
       </c>
       <c r="B36" t="n">
-        <v>95634</v>
+        <v>91373</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4286,25 +4271,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2569</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4314,10 +4299,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>286668</v>
+        <v>286525</v>
       </c>
       <c r="R36" t="n">
-        <v>6508839</v>
+        <v>6508258</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4350,6 +4335,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4376,10 +4366,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113399440</v>
+        <v>113399464</v>
       </c>
       <c r="B37" t="n">
-        <v>56789</v>
+        <v>94152</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4388,25 +4378,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4416,10 +4406,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>286483</v>
+        <v>286444</v>
       </c>
       <c r="R37" t="n">
-        <v>6508722</v>
+        <v>6508165</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4452,11 +4442,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4483,10 +4468,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113399425</v>
+        <v>113399411</v>
       </c>
       <c r="B38" t="n">
-        <v>56789</v>
+        <v>95634</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4495,25 +4480,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4523,10 +4508,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>286469</v>
+        <v>286712</v>
       </c>
       <c r="R38" t="n">
-        <v>6508059</v>
+        <v>6508906</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4559,11 +4544,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4590,7 +4570,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113399424</v>
+        <v>113399436</v>
       </c>
       <c r="B39" t="n">
         <v>56789</v>
@@ -4630,10 +4610,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>286495</v>
+        <v>286684</v>
       </c>
       <c r="R39" t="n">
-        <v>6508076</v>
+        <v>6508737</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4697,7 +4677,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113399432</v>
+        <v>113399442</v>
       </c>
       <c r="B40" t="n">
         <v>56789</v>
@@ -4737,10 +4717,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>286495</v>
+        <v>286541</v>
       </c>
       <c r="R40" t="n">
-        <v>6508424</v>
+        <v>6508510</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4777,7 +4757,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4804,10 +4784,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113399413</v>
+        <v>113399458</v>
       </c>
       <c r="B41" t="n">
-        <v>56789</v>
+        <v>95994</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4816,25 +4796,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4844,10 +4824,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>286327</v>
+        <v>286751</v>
       </c>
       <c r="R41" t="n">
-        <v>6508012</v>
+        <v>6508904</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4880,11 +4860,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4911,10 +4886,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113399456</v>
+        <v>113399409</v>
       </c>
       <c r="B42" t="n">
-        <v>95994</v>
+        <v>56773</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4923,25 +4898,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2606</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4951,10 +4926,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>286522</v>
+        <v>286461</v>
       </c>
       <c r="R42" t="n">
-        <v>6508764</v>
+        <v>6508704</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4987,6 +4962,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5013,10 +4993,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399459</v>
+        <v>113399404</v>
       </c>
       <c r="B43" t="n">
-        <v>95994</v>
+        <v>93799</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5029,21 +5009,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5053,10 +5033,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286600</v>
+        <v>286719</v>
       </c>
       <c r="R43" t="n">
-        <v>6508882</v>
+        <v>6508879</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5115,10 +5095,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399449</v>
+        <v>113399427</v>
       </c>
       <c r="B44" t="n">
-        <v>91373</v>
+        <v>56789</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5131,21 +5111,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5155,10 +5135,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>286530</v>
+        <v>286422</v>
       </c>
       <c r="R44" t="n">
-        <v>6508258</v>
+        <v>6508051</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5191,6 +5171,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5217,10 +5202,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113399405</v>
+        <v>113399431</v>
       </c>
       <c r="B45" t="n">
-        <v>93799</v>
+        <v>56789</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5229,25 +5214,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5257,10 +5242,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>286655</v>
+        <v>286459</v>
       </c>
       <c r="R45" t="n">
-        <v>6508854</v>
+        <v>6508392</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5293,6 +5278,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5319,7 +5309,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113399427</v>
+        <v>113399434</v>
       </c>
       <c r="B46" t="n">
         <v>56789</v>
@@ -5359,10 +5349,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>286422</v>
+        <v>286601</v>
       </c>
       <c r="R46" t="n">
-        <v>6508051</v>
+        <v>6508623</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5426,7 +5416,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113399417</v>
+        <v>113399414</v>
       </c>
       <c r="B47" t="n">
         <v>56789</v>
@@ -5466,10 +5456,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>286266</v>
+        <v>286242</v>
       </c>
       <c r="R47" t="n">
-        <v>6507549</v>
+        <v>6507840</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5533,7 +5523,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113399439</v>
+        <v>113399433</v>
       </c>
       <c r="B48" t="n">
         <v>56789</v>
@@ -5573,10 +5563,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>286834</v>
+        <v>286505</v>
       </c>
       <c r="R48" t="n">
-        <v>6508948</v>
+        <v>6508433</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5640,10 +5630,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113399460</v>
+        <v>113399413</v>
       </c>
       <c r="B49" t="n">
-        <v>95994</v>
+        <v>56789</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5652,25 +5642,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5680,10 +5670,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>286595</v>
+        <v>286327</v>
       </c>
       <c r="R49" t="n">
-        <v>6508872</v>
+        <v>6508012</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5716,6 +5706,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5742,10 +5737,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113399464</v>
+        <v>113399429</v>
       </c>
       <c r="B50" t="n">
-        <v>94152</v>
+        <v>56789</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5754,25 +5749,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5782,10 +5777,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>286444</v>
+        <v>286485</v>
       </c>
       <c r="R50" t="n">
-        <v>6508165</v>
+        <v>6508336</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5818,6 +5813,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>113354383</v>
       </c>
       <c r="B3" t="n">
-        <v>90100</v>
+        <v>90107</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113399426</v>
+        <v>113399410</v>
       </c>
       <c r="B4" t="n">
-        <v>56789</v>
+        <v>95641</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -902,25 +902,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>286454</v>
+        <v>286724</v>
       </c>
       <c r="R4" t="n">
-        <v>6508073</v>
+        <v>6508823</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,11 +966,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113399423</v>
+        <v>113399429</v>
       </c>
       <c r="B5" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>286426</v>
+        <v>286485</v>
       </c>
       <c r="R5" t="n">
-        <v>6507790</v>
+        <v>6508336</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113399449</v>
+        <v>113399422</v>
       </c>
       <c r="B6" t="n">
-        <v>91373</v>
+        <v>56796</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>286530</v>
+        <v>286408</v>
       </c>
       <c r="R6" t="n">
-        <v>6508258</v>
+        <v>6507718</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1180,6 +1175,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113399418</v>
+        <v>113399417</v>
       </c>
       <c r="B7" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>286273</v>
+        <v>286266</v>
       </c>
       <c r="R7" t="n">
         <v>6507549</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113399456</v>
+        <v>113399431</v>
       </c>
       <c r="B8" t="n">
-        <v>95994</v>
+        <v>56796</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,25 +1325,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>286522</v>
+        <v>286459</v>
       </c>
       <c r="R8" t="n">
-        <v>6508764</v>
+        <v>6508392</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,6 +1389,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399461</v>
+        <v>113399432</v>
       </c>
       <c r="B9" t="n">
-        <v>99614</v>
+        <v>56796</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1427,25 +1432,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>286239</v>
+        <v>286495</v>
       </c>
       <c r="R9" t="n">
-        <v>6507778</v>
+        <v>6508424</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,6 +1496,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1517,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399443</v>
+        <v>113399455</v>
       </c>
       <c r="B10" t="n">
-        <v>56789</v>
+        <v>96001</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,25 +1539,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>286465</v>
+        <v>286525</v>
       </c>
       <c r="R10" t="n">
-        <v>6508688</v>
+        <v>6508767</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,11 +1603,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399430</v>
+        <v>113399412</v>
       </c>
       <c r="B11" t="n">
-        <v>56789</v>
+        <v>95641</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1636,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>286476</v>
+        <v>286668</v>
       </c>
       <c r="R11" t="n">
-        <v>6508348</v>
+        <v>6508839</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,11 +1705,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1731,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399457</v>
+        <v>113399463</v>
       </c>
       <c r="B12" t="n">
-        <v>95994</v>
+        <v>99621</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,21 +1747,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2606</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>286398</v>
+        <v>286229</v>
       </c>
       <c r="R12" t="n">
-        <v>6508131</v>
+        <v>6507839</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113399421</v>
+        <v>113399448</v>
       </c>
       <c r="B13" t="n">
-        <v>56789</v>
+        <v>91380</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1849,21 +1849,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>286411</v>
+        <v>286525</v>
       </c>
       <c r="R13" t="n">
-        <v>6507674</v>
+        <v>6508258</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1940,10 +1940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113399438</v>
+        <v>113399440</v>
       </c>
       <c r="B14" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>286835</v>
+        <v>286483</v>
       </c>
       <c r="R14" t="n">
-        <v>6508956</v>
+        <v>6508722</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399425</v>
+        <v>113399449</v>
       </c>
       <c r="B15" t="n">
-        <v>56789</v>
+        <v>91380</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>286469</v>
+        <v>286530</v>
       </c>
       <c r="R15" t="n">
-        <v>6508059</v>
+        <v>6508258</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2123,11 +2123,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2154,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399460</v>
+        <v>113399438</v>
       </c>
       <c r="B16" t="n">
-        <v>95994</v>
+        <v>56796</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2166,25 +2161,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2189,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>286595</v>
+        <v>286835</v>
       </c>
       <c r="R16" t="n">
-        <v>6508872</v>
+        <v>6508956</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2230,6 +2225,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2256,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399440</v>
+        <v>113399435</v>
       </c>
       <c r="B17" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>286483</v>
+        <v>286667</v>
       </c>
       <c r="R17" t="n">
-        <v>6508722</v>
+        <v>6508726</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2363,10 +2363,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399405</v>
+        <v>113399441</v>
       </c>
       <c r="B18" t="n">
-        <v>93799</v>
+        <v>56796</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2375,25 +2375,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>286655</v>
+        <v>286510</v>
       </c>
       <c r="R18" t="n">
-        <v>6508854</v>
+        <v>6508675</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2439,6 +2439,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2465,10 +2470,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399417</v>
+        <v>113399437</v>
       </c>
       <c r="B19" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,10 +2510,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>286266</v>
+        <v>286715</v>
       </c>
       <c r="R19" t="n">
-        <v>6507549</v>
+        <v>6508776</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2572,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399463</v>
+        <v>113399421</v>
       </c>
       <c r="B20" t="n">
-        <v>99614</v>
+        <v>56796</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2584,25 +2589,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2612,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>286229</v>
+        <v>286411</v>
       </c>
       <c r="R20" t="n">
-        <v>6507839</v>
+        <v>6507674</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2648,6 +2653,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2674,10 +2684,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113399410</v>
+        <v>113399443</v>
       </c>
       <c r="B21" t="n">
-        <v>95634</v>
+        <v>56796</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2686,25 +2696,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2714,10 +2724,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>286724</v>
+        <v>286465</v>
       </c>
       <c r="R21" t="n">
-        <v>6508823</v>
+        <v>6508688</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2750,6 +2760,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2776,10 +2791,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113399424</v>
+        <v>113399458</v>
       </c>
       <c r="B22" t="n">
-        <v>56789</v>
+        <v>96001</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2788,25 +2803,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2816,10 +2831,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>286495</v>
+        <v>286751</v>
       </c>
       <c r="R22" t="n">
-        <v>6508076</v>
+        <v>6508904</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2852,11 +2867,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2883,10 +2893,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113399412</v>
+        <v>113399428</v>
       </c>
       <c r="B23" t="n">
-        <v>95634</v>
+        <v>56796</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2895,25 +2905,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2923,10 +2933,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>286668</v>
+        <v>286459</v>
       </c>
       <c r="R23" t="n">
-        <v>6508839</v>
+        <v>6508160</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2959,6 +2969,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2985,10 +3000,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113399439</v>
+        <v>113399418</v>
       </c>
       <c r="B24" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3025,10 +3040,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>286834</v>
+        <v>286273</v>
       </c>
       <c r="R24" t="n">
-        <v>6508948</v>
+        <v>6507549</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3092,10 +3107,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113399437</v>
+        <v>113399424</v>
       </c>
       <c r="B25" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,10 +3147,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>286715</v>
+        <v>286495</v>
       </c>
       <c r="R25" t="n">
-        <v>6508776</v>
+        <v>6508076</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3199,10 +3214,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113399432</v>
+        <v>113399413</v>
       </c>
       <c r="B26" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3239,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>286495</v>
+        <v>286327</v>
       </c>
       <c r="R26" t="n">
-        <v>6508424</v>
+        <v>6508012</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3306,10 +3321,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113399435</v>
+        <v>113399430</v>
       </c>
       <c r="B27" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3346,10 +3361,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>286667</v>
+        <v>286476</v>
       </c>
       <c r="R27" t="n">
-        <v>6508726</v>
+        <v>6508348</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3413,10 +3428,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113399419</v>
+        <v>113399461</v>
       </c>
       <c r="B28" t="n">
-        <v>56789</v>
+        <v>99621</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3425,25 +3440,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3453,10 +3468,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>286311</v>
+        <v>286239</v>
       </c>
       <c r="R28" t="n">
-        <v>6507585</v>
+        <v>6507778</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3489,11 +3504,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3523,7 +3533,7 @@
         <v>113399459</v>
       </c>
       <c r="B29" t="n">
-        <v>95994</v>
+        <v>96001</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3622,10 +3632,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113399428</v>
+        <v>113399408</v>
       </c>
       <c r="B30" t="n">
-        <v>56789</v>
+        <v>56780</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3638,16 +3648,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3662,10 +3672,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>286459</v>
+        <v>286479</v>
       </c>
       <c r="R30" t="n">
-        <v>6508160</v>
+        <v>6508372</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3702,7 +3712,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3729,10 +3739,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113399455</v>
+        <v>113399419</v>
       </c>
       <c r="B31" t="n">
-        <v>95994</v>
+        <v>56796</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3741,25 +3751,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3769,10 +3779,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>286525</v>
+        <v>286311</v>
       </c>
       <c r="R31" t="n">
-        <v>6508767</v>
+        <v>6507585</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3805,6 +3815,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3831,10 +3846,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113399441</v>
+        <v>113399405</v>
       </c>
       <c r="B32" t="n">
-        <v>56789</v>
+        <v>93806</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3843,25 +3858,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3871,10 +3886,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>286510</v>
+        <v>286655</v>
       </c>
       <c r="R32" t="n">
-        <v>6508675</v>
+        <v>6508854</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3907,11 +3922,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3938,10 +3948,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113399408</v>
+        <v>113399414</v>
       </c>
       <c r="B33" t="n">
-        <v>56773</v>
+        <v>56796</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3954,16 +3964,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3978,10 +3988,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>286479</v>
+        <v>286242</v>
       </c>
       <c r="R33" t="n">
-        <v>6508372</v>
+        <v>6507840</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4018,7 +4028,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rnghack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4045,10 +4055,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113399422</v>
+        <v>113399426</v>
       </c>
       <c r="B34" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4085,10 +4095,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>286408</v>
+        <v>286454</v>
       </c>
       <c r="R34" t="n">
-        <v>6507718</v>
+        <v>6508073</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4152,10 +4162,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113399420</v>
+        <v>113399433</v>
       </c>
       <c r="B35" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4192,10 +4202,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>286325</v>
+        <v>286505</v>
       </c>
       <c r="R35" t="n">
-        <v>6507609</v>
+        <v>6508433</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4259,10 +4269,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113399448</v>
+        <v>113399434</v>
       </c>
       <c r="B36" t="n">
-        <v>91373</v>
+        <v>56796</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4275,21 +4285,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4299,10 +4309,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>286525</v>
+        <v>286601</v>
       </c>
       <c r="R36" t="n">
-        <v>6508258</v>
+        <v>6508623</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4339,7 +4349,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>9 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4366,10 +4376,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113399464</v>
+        <v>113399423</v>
       </c>
       <c r="B37" t="n">
-        <v>94152</v>
+        <v>56796</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4378,25 +4388,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4406,10 +4416,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>286444</v>
+        <v>286426</v>
       </c>
       <c r="R37" t="n">
-        <v>6508165</v>
+        <v>6507790</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4442,6 +4452,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4468,10 +4483,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113399411</v>
+        <v>113399456</v>
       </c>
       <c r="B38" t="n">
-        <v>95634</v>
+        <v>96001</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4484,21 +4499,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2569</v>
+        <v>2606</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4508,10 +4523,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>286712</v>
+        <v>286522</v>
       </c>
       <c r="R38" t="n">
-        <v>6508906</v>
+        <v>6508764</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4570,10 +4585,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113399436</v>
+        <v>113399404</v>
       </c>
       <c r="B39" t="n">
-        <v>56789</v>
+        <v>93806</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4582,25 +4597,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4610,10 +4625,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>286684</v>
+        <v>286719</v>
       </c>
       <c r="R39" t="n">
-        <v>6508737</v>
+        <v>6508879</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4646,11 +4661,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4677,10 +4687,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113399442</v>
+        <v>113399439</v>
       </c>
       <c r="B40" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4717,10 +4727,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>286541</v>
+        <v>286834</v>
       </c>
       <c r="R40" t="n">
-        <v>6508510</v>
+        <v>6508948</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4757,7 +4767,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4784,10 +4794,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113399458</v>
+        <v>113399464</v>
       </c>
       <c r="B41" t="n">
-        <v>95994</v>
+        <v>94159</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4800,21 +4810,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2606</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4824,10 +4834,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>286751</v>
+        <v>286444</v>
       </c>
       <c r="R41" t="n">
-        <v>6508904</v>
+        <v>6508165</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4889,7 +4899,7 @@
         <v>113399409</v>
       </c>
       <c r="B42" t="n">
-        <v>56773</v>
+        <v>56780</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4993,10 +5003,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399404</v>
+        <v>113399427</v>
       </c>
       <c r="B43" t="n">
-        <v>93799</v>
+        <v>56796</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5005,25 +5015,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5033,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286719</v>
+        <v>286422</v>
       </c>
       <c r="R43" t="n">
-        <v>6508879</v>
+        <v>6508051</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5069,6 +5079,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5095,10 +5110,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399427</v>
+        <v>113399420</v>
       </c>
       <c r="B44" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5135,10 +5150,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>286422</v>
+        <v>286325</v>
       </c>
       <c r="R44" t="n">
-        <v>6508051</v>
+        <v>6507609</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5202,10 +5217,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113399431</v>
+        <v>113399442</v>
       </c>
       <c r="B45" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5242,10 +5257,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>286459</v>
+        <v>286541</v>
       </c>
       <c r="R45" t="n">
-        <v>6508392</v>
+        <v>6508510</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5282,7 +5297,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5309,10 +5324,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113399434</v>
+        <v>113399460</v>
       </c>
       <c r="B46" t="n">
-        <v>56789</v>
+        <v>96001</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5321,25 +5336,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5349,10 +5364,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>286601</v>
+        <v>286595</v>
       </c>
       <c r="R46" t="n">
-        <v>6508623</v>
+        <v>6508872</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5385,11 +5400,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5416,10 +5426,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113399414</v>
+        <v>113399457</v>
       </c>
       <c r="B47" t="n">
-        <v>56789</v>
+        <v>96001</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5428,25 +5438,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5456,10 +5466,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>286242</v>
+        <v>286398</v>
       </c>
       <c r="R47" t="n">
-        <v>6507840</v>
+        <v>6508131</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5492,11 +5502,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5523,10 +5528,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113399433</v>
+        <v>113399411</v>
       </c>
       <c r="B48" t="n">
-        <v>56789</v>
+        <v>95641</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5535,25 +5540,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5563,10 +5568,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>286505</v>
+        <v>286712</v>
       </c>
       <c r="R48" t="n">
-        <v>6508433</v>
+        <v>6508906</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5599,11 +5604,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5630,10 +5630,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113399413</v>
+        <v>113399436</v>
       </c>
       <c r="B49" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>286327</v>
+        <v>286684</v>
       </c>
       <c r="R49" t="n">
-        <v>6508012</v>
+        <v>6508737</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113399429</v>
+        <v>113399425</v>
       </c>
       <c r="B50" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>286485</v>
+        <v>286469</v>
       </c>
       <c r="R50" t="n">
-        <v>6508336</v>
+        <v>6508059</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113399410</v>
+        <v>113399429</v>
       </c>
       <c r="B4" t="n">
-        <v>95641</v>
+        <v>56796</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -902,25 +902,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>286724</v>
+        <v>286485</v>
       </c>
       <c r="R4" t="n">
-        <v>6508823</v>
+        <v>6508336</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,6 +966,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113399429</v>
+        <v>113399422</v>
       </c>
       <c r="B5" t="n">
         <v>56796</v>
@@ -1032,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>286485</v>
+        <v>286408</v>
       </c>
       <c r="R5" t="n">
-        <v>6508336</v>
+        <v>6507718</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113399422</v>
+        <v>113399410</v>
       </c>
       <c r="B6" t="n">
-        <v>56796</v>
+        <v>95641</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>286408</v>
+        <v>286724</v>
       </c>
       <c r="R6" t="n">
-        <v>6507718</v>
+        <v>6508823</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1175,11 +1180,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,7 +1206,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113399417</v>
+        <v>113399431</v>
       </c>
       <c r="B7" t="n">
         <v>56796</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>286266</v>
+        <v>286459</v>
       </c>
       <c r="R7" t="n">
-        <v>6507549</v>
+        <v>6508392</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113399431</v>
+        <v>113399417</v>
       </c>
       <c r="B8" t="n">
         <v>56796</v>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>286459</v>
+        <v>286266</v>
       </c>
       <c r="R8" t="n">
-        <v>6508392</v>
+        <v>6507549</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -4483,10 +4483,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113399456</v>
+        <v>113399404</v>
       </c>
       <c r="B38" t="n">
-        <v>96001</v>
+        <v>93806</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4499,21 +4499,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>286522</v>
+        <v>286719</v>
       </c>
       <c r="R38" t="n">
-        <v>6508764</v>
+        <v>6508879</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4585,10 +4585,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113399404</v>
+        <v>113399456</v>
       </c>
       <c r="B39" t="n">
-        <v>93806</v>
+        <v>96001</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4601,21 +4601,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>286719</v>
+        <v>286522</v>
       </c>
       <c r="R39" t="n">
-        <v>6508879</v>
+        <v>6508764</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113399409</v>
+        <v>113399427</v>
       </c>
       <c r="B42" t="n">
-        <v>56780</v>
+        <v>56796</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4912,16 +4912,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>286461</v>
+        <v>286422</v>
       </c>
       <c r="R42" t="n">
-        <v>6508704</v>
+        <v>6508051</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5003,7 +5003,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399427</v>
+        <v>113399420</v>
       </c>
       <c r="B43" t="n">
         <v>56796</v>
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286422</v>
+        <v>286325</v>
       </c>
       <c r="R43" t="n">
-        <v>6508051</v>
+        <v>6507609</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5110,7 +5110,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399420</v>
+        <v>113399442</v>
       </c>
       <c r="B44" t="n">
         <v>56796</v>
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>286325</v>
+        <v>286541</v>
       </c>
       <c r="R44" t="n">
-        <v>6507609</v>
+        <v>6508510</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5217,10 +5217,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113399442</v>
+        <v>113399409</v>
       </c>
       <c r="B45" t="n">
-        <v>56796</v>
+        <v>56780</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5233,16 +5233,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>286541</v>
+        <v>286461</v>
       </c>
       <c r="R45" t="n">
-        <v>6508510</v>
+        <v>6508704</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5324,7 +5324,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113399460</v>
+        <v>113399457</v>
       </c>
       <c r="B46" t="n">
         <v>96001</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>286595</v>
+        <v>286398</v>
       </c>
       <c r="R46" t="n">
-        <v>6508872</v>
+        <v>6508131</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5426,10 +5426,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113399457</v>
+        <v>113399411</v>
       </c>
       <c r="B47" t="n">
-        <v>96001</v>
+        <v>95641</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5442,21 +5442,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2606</v>
+        <v>2569</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5466,10 +5466,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>286398</v>
+        <v>286712</v>
       </c>
       <c r="R47" t="n">
-        <v>6508131</v>
+        <v>6508906</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5528,10 +5528,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113399411</v>
+        <v>113399436</v>
       </c>
       <c r="B48" t="n">
-        <v>95641</v>
+        <v>56796</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5540,25 +5540,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5568,10 +5568,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>286712</v>
+        <v>286684</v>
       </c>
       <c r="R48" t="n">
-        <v>6508906</v>
+        <v>6508737</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5604,6 +5604,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5630,7 +5635,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113399436</v>
+        <v>113399425</v>
       </c>
       <c r="B49" t="n">
         <v>56796</v>
@@ -5670,10 +5675,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>286684</v>
+        <v>286469</v>
       </c>
       <c r="R49" t="n">
-        <v>6508737</v>
+        <v>6508059</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5737,10 +5742,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113399425</v>
+        <v>113399460</v>
       </c>
       <c r="B50" t="n">
-        <v>56796</v>
+        <v>96001</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5749,25 +5754,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5777,10 +5782,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>286469</v>
+        <v>286595</v>
       </c>
       <c r="R50" t="n">
-        <v>6508059</v>
+        <v>6508872</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5813,11 +5818,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -4483,10 +4483,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113399404</v>
+        <v>113399456</v>
       </c>
       <c r="B38" t="n">
-        <v>93806</v>
+        <v>96001</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4499,21 +4499,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>286719</v>
+        <v>286522</v>
       </c>
       <c r="R38" t="n">
-        <v>6508879</v>
+        <v>6508764</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4585,10 +4585,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113399456</v>
+        <v>113399404</v>
       </c>
       <c r="B39" t="n">
-        <v>96001</v>
+        <v>93806</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4601,21 +4601,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>286522</v>
+        <v>286719</v>
       </c>
       <c r="R39" t="n">
-        <v>6508764</v>
+        <v>6508879</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113399427</v>
+        <v>113399409</v>
       </c>
       <c r="B42" t="n">
-        <v>56796</v>
+        <v>56780</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4912,16 +4912,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>286422</v>
+        <v>286461</v>
       </c>
       <c r="R42" t="n">
-        <v>6508051</v>
+        <v>6508704</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5003,7 +5003,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399420</v>
+        <v>113399427</v>
       </c>
       <c r="B43" t="n">
         <v>56796</v>
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286325</v>
+        <v>286422</v>
       </c>
       <c r="R43" t="n">
-        <v>6507609</v>
+        <v>6508051</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5110,7 +5110,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399442</v>
+        <v>113399420</v>
       </c>
       <c r="B44" t="n">
         <v>56796</v>
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>286541</v>
+        <v>286325</v>
       </c>
       <c r="R44" t="n">
-        <v>6508510</v>
+        <v>6507609</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5217,10 +5217,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113399409</v>
+        <v>113399442</v>
       </c>
       <c r="B45" t="n">
-        <v>56780</v>
+        <v>56796</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5233,16 +5233,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>286461</v>
+        <v>286541</v>
       </c>
       <c r="R45" t="n">
-        <v>6508704</v>
+        <v>6508510</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5324,7 +5324,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113399457</v>
+        <v>113399460</v>
       </c>
       <c r="B46" t="n">
         <v>96001</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>286398</v>
+        <v>286595</v>
       </c>
       <c r="R46" t="n">
-        <v>6508131</v>
+        <v>6508872</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5426,10 +5426,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113399411</v>
+        <v>113399457</v>
       </c>
       <c r="B47" t="n">
-        <v>95641</v>
+        <v>96001</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5442,21 +5442,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2569</v>
+        <v>2606</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5466,10 +5466,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>286712</v>
+        <v>286398</v>
       </c>
       <c r="R47" t="n">
-        <v>6508906</v>
+        <v>6508131</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5528,10 +5528,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113399436</v>
+        <v>113399411</v>
       </c>
       <c r="B48" t="n">
-        <v>56796</v>
+        <v>95641</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5540,25 +5540,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5568,10 +5568,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>286684</v>
+        <v>286712</v>
       </c>
       <c r="R48" t="n">
-        <v>6508737</v>
+        <v>6508906</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5604,11 +5604,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5635,7 +5630,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113399425</v>
+        <v>113399436</v>
       </c>
       <c r="B49" t="n">
         <v>56796</v>
@@ -5675,10 +5670,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>286469</v>
+        <v>286684</v>
       </c>
       <c r="R49" t="n">
-        <v>6508059</v>
+        <v>6508737</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5742,10 +5737,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113399460</v>
+        <v>113399425</v>
       </c>
       <c r="B50" t="n">
-        <v>96001</v>
+        <v>56796</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5754,25 +5749,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5782,10 +5777,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>286595</v>
+        <v>286469</v>
       </c>
       <c r="R50" t="n">
-        <v>6508872</v>
+        <v>6508059</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5818,6 +5813,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -1833,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113399448</v>
+        <v>113399440</v>
       </c>
       <c r="B13" t="n">
-        <v>91380</v>
+        <v>56796</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1849,21 +1849,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>286525</v>
+        <v>286483</v>
       </c>
       <c r="R13" t="n">
-        <v>6508258</v>
+        <v>6508722</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>9 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1940,10 +1940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113399440</v>
+        <v>113399448</v>
       </c>
       <c r="B14" t="n">
-        <v>56796</v>
+        <v>91380</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>286483</v>
+        <v>286525</v>
       </c>
       <c r="R14" t="n">
-        <v>6508722</v>
+        <v>6508258</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -4896,10 +4896,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113399409</v>
+        <v>113399427</v>
       </c>
       <c r="B42" t="n">
-        <v>56780</v>
+        <v>56796</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4912,16 +4912,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>286461</v>
+        <v>286422</v>
       </c>
       <c r="R42" t="n">
-        <v>6508704</v>
+        <v>6508051</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5003,7 +5003,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399427</v>
+        <v>113399420</v>
       </c>
       <c r="B43" t="n">
         <v>56796</v>
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286422</v>
+        <v>286325</v>
       </c>
       <c r="R43" t="n">
-        <v>6508051</v>
+        <v>6507609</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5110,7 +5110,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399420</v>
+        <v>113399442</v>
       </c>
       <c r="B44" t="n">
         <v>56796</v>
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>286325</v>
+        <v>286541</v>
       </c>
       <c r="R44" t="n">
-        <v>6507609</v>
+        <v>6508510</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5217,10 +5217,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113399442</v>
+        <v>113399409</v>
       </c>
       <c r="B45" t="n">
-        <v>56796</v>
+        <v>56780</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5233,16 +5233,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>286541</v>
+        <v>286461</v>
       </c>
       <c r="R45" t="n">
-        <v>6508510</v>
+        <v>6508704</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>113354383</v>
       </c>
       <c r="B3" t="n">
-        <v>90107</v>
+        <v>90110</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113399429</v>
+        <v>113399413</v>
       </c>
       <c r="B4" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>286485</v>
+        <v>286327</v>
       </c>
       <c r="R4" t="n">
-        <v>6508336</v>
+        <v>6508012</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113399422</v>
+        <v>113399449</v>
       </c>
       <c r="B5" t="n">
-        <v>56796</v>
+        <v>91385</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>286408</v>
+        <v>286530</v>
       </c>
       <c r="R5" t="n">
-        <v>6507718</v>
+        <v>6508258</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1073,11 +1073,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113399410</v>
+        <v>113399414</v>
       </c>
       <c r="B6" t="n">
-        <v>95641</v>
+        <v>56798</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>286724</v>
+        <v>286242</v>
       </c>
       <c r="R6" t="n">
-        <v>6508823</v>
+        <v>6507840</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1180,6 +1175,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113399431</v>
+        <v>113399425</v>
       </c>
       <c r="B7" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>286459</v>
+        <v>286469</v>
       </c>
       <c r="R7" t="n">
-        <v>6508392</v>
+        <v>6508059</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113399417</v>
+        <v>113399419</v>
       </c>
       <c r="B8" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>286266</v>
+        <v>286311</v>
       </c>
       <c r="R8" t="n">
-        <v>6507549</v>
+        <v>6507585</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1420,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399432</v>
+        <v>113399411</v>
       </c>
       <c r="B9" t="n">
-        <v>56796</v>
+        <v>95646</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,25 +1432,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>286495</v>
+        <v>286712</v>
       </c>
       <c r="R9" t="n">
-        <v>6508424</v>
+        <v>6508906</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,11 +1496,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399455</v>
+        <v>113399431</v>
       </c>
       <c r="B10" t="n">
-        <v>96001</v>
+        <v>56798</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,25 +1534,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>286525</v>
+        <v>286459</v>
       </c>
       <c r="R10" t="n">
-        <v>6508767</v>
+        <v>6508392</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1603,6 +1598,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399412</v>
+        <v>113399430</v>
       </c>
       <c r="B11" t="n">
-        <v>95641</v>
+        <v>56798</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>286668</v>
+        <v>286476</v>
       </c>
       <c r="R11" t="n">
-        <v>6508839</v>
+        <v>6508348</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1705,6 +1705,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1731,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399463</v>
+        <v>113399426</v>
       </c>
       <c r="B12" t="n">
-        <v>99621</v>
+        <v>56798</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1743,25 +1748,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1771,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>286229</v>
+        <v>286454</v>
       </c>
       <c r="R12" t="n">
-        <v>6507839</v>
+        <v>6508073</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1807,6 +1812,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1833,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113399440</v>
+        <v>113399443</v>
       </c>
       <c r="B13" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>286483</v>
+        <v>286465</v>
       </c>
       <c r="R13" t="n">
-        <v>6508722</v>
+        <v>6508688</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1913,7 +1923,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1940,10 +1950,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113399448</v>
+        <v>113399442</v>
       </c>
       <c r="B14" t="n">
-        <v>91380</v>
+        <v>56798</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1956,21 +1966,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1980,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>286525</v>
+        <v>286541</v>
       </c>
       <c r="R14" t="n">
-        <v>6508258</v>
+        <v>6508510</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2020,7 +2030,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>9 fruktkroppar</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2047,10 +2057,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399449</v>
+        <v>113399457</v>
       </c>
       <c r="B15" t="n">
-        <v>91380</v>
+        <v>96006</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2059,25 +2069,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>2606</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>286530</v>
+        <v>286398</v>
       </c>
       <c r="R15" t="n">
-        <v>6508258</v>
+        <v>6508131</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2149,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399438</v>
+        <v>113399420</v>
       </c>
       <c r="B16" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2189,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>286835</v>
+        <v>286325</v>
       </c>
       <c r="R16" t="n">
-        <v>6508956</v>
+        <v>6507609</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2256,10 +2266,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399435</v>
+        <v>113399460</v>
       </c>
       <c r="B17" t="n">
-        <v>56796</v>
+        <v>96006</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2268,25 +2278,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2296,10 +2306,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>286667</v>
+        <v>286595</v>
       </c>
       <c r="R17" t="n">
-        <v>6508726</v>
+        <v>6508872</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2332,11 +2342,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2363,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399441</v>
+        <v>113399440</v>
       </c>
       <c r="B18" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,10 +2408,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>286510</v>
+        <v>286483</v>
       </c>
       <c r="R18" t="n">
-        <v>6508675</v>
+        <v>6508722</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2470,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399437</v>
+        <v>113399439</v>
       </c>
       <c r="B19" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>286715</v>
+        <v>286834</v>
       </c>
       <c r="R19" t="n">
-        <v>6508776</v>
+        <v>6508948</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2577,10 +2582,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399421</v>
+        <v>113399409</v>
       </c>
       <c r="B20" t="n">
-        <v>56796</v>
+        <v>56782</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2593,16 +2598,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2617,10 +2622,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>286411</v>
+        <v>286461</v>
       </c>
       <c r="R20" t="n">
-        <v>6507674</v>
+        <v>6508704</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2657,7 +2662,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2684,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113399443</v>
+        <v>113399456</v>
       </c>
       <c r="B21" t="n">
-        <v>56796</v>
+        <v>96006</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2696,25 +2701,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2724,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>286465</v>
+        <v>286522</v>
       </c>
       <c r="R21" t="n">
-        <v>6508688</v>
+        <v>6508764</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2760,11 +2765,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2791,10 +2791,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113399458</v>
+        <v>113399461</v>
       </c>
       <c r="B22" t="n">
-        <v>96001</v>
+        <v>99626</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,21 +2807,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2606</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>286751</v>
+        <v>286239</v>
       </c>
       <c r="R22" t="n">
-        <v>6508904</v>
+        <v>6507778</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2893,10 +2893,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113399428</v>
+        <v>113399417</v>
       </c>
       <c r="B23" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>286459</v>
+        <v>286266</v>
       </c>
       <c r="R23" t="n">
-        <v>6508160</v>
+        <v>6507549</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3003,7 +3003,7 @@
         <v>113399418</v>
       </c>
       <c r="B24" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113399424</v>
+        <v>113399434</v>
       </c>
       <c r="B25" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3147,10 +3147,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>286495</v>
+        <v>286601</v>
       </c>
       <c r="R25" t="n">
-        <v>6508076</v>
+        <v>6508623</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113399413</v>
+        <v>113399423</v>
       </c>
       <c r="B26" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>286327</v>
+        <v>286426</v>
       </c>
       <c r="R26" t="n">
-        <v>6508012</v>
+        <v>6507790</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3321,10 +3321,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113399430</v>
+        <v>113399404</v>
       </c>
       <c r="B27" t="n">
-        <v>56796</v>
+        <v>93811</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3333,25 +3333,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>286476</v>
+        <v>286719</v>
       </c>
       <c r="R27" t="n">
-        <v>6508348</v>
+        <v>6508879</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3397,11 +3397,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3428,10 +3423,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113399461</v>
+        <v>113399410</v>
       </c>
       <c r="B28" t="n">
-        <v>99621</v>
+        <v>95646</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3444,21 +3439,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>2569</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3468,10 +3463,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>286239</v>
+        <v>286724</v>
       </c>
       <c r="R28" t="n">
-        <v>6507778</v>
+        <v>6508823</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3530,10 +3525,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113399459</v>
+        <v>113399448</v>
       </c>
       <c r="B29" t="n">
-        <v>96001</v>
+        <v>91385</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3542,25 +3537,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2606</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3570,10 +3565,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>286600</v>
+        <v>286525</v>
       </c>
       <c r="R29" t="n">
-        <v>6508882</v>
+        <v>6508258</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3606,6 +3601,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3635,7 +3635,7 @@
         <v>113399408</v>
       </c>
       <c r="B30" t="n">
-        <v>56780</v>
+        <v>56782</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3739,10 +3739,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113399419</v>
+        <v>113399441</v>
       </c>
       <c r="B31" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3779,10 +3779,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>286311</v>
+        <v>286510</v>
       </c>
       <c r="R31" t="n">
-        <v>6507585</v>
+        <v>6508675</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113399405</v>
+        <v>113399436</v>
       </c>
       <c r="B32" t="n">
-        <v>93806</v>
+        <v>56798</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3858,25 +3858,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>286655</v>
+        <v>286684</v>
       </c>
       <c r="R32" t="n">
-        <v>6508854</v>
+        <v>6508737</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3922,6 +3922,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3948,10 +3953,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113399414</v>
+        <v>113399421</v>
       </c>
       <c r="B33" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3988,10 +3993,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>286242</v>
+        <v>286411</v>
       </c>
       <c r="R33" t="n">
-        <v>6507840</v>
+        <v>6507674</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4055,10 +4060,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113399426</v>
+        <v>113399459</v>
       </c>
       <c r="B34" t="n">
-        <v>56796</v>
+        <v>96006</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4067,25 +4072,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4095,10 +4100,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>286454</v>
+        <v>286600</v>
       </c>
       <c r="R34" t="n">
-        <v>6508073</v>
+        <v>6508882</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4131,11 +4136,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4162,10 +4162,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113399433</v>
+        <v>113399424</v>
       </c>
       <c r="B35" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>286505</v>
+        <v>286495</v>
       </c>
       <c r="R35" t="n">
-        <v>6508433</v>
+        <v>6508076</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113399434</v>
+        <v>113399458</v>
       </c>
       <c r="B36" t="n">
-        <v>56796</v>
+        <v>96006</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>286601</v>
+        <v>286751</v>
       </c>
       <c r="R36" t="n">
-        <v>6508623</v>
+        <v>6508904</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4345,11 +4345,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4376,10 +4371,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113399423</v>
+        <v>113399422</v>
       </c>
       <c r="B37" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4416,10 +4411,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>286426</v>
+        <v>286408</v>
       </c>
       <c r="R37" t="n">
-        <v>6507790</v>
+        <v>6507718</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4483,10 +4478,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113399456</v>
+        <v>113399435</v>
       </c>
       <c r="B38" t="n">
-        <v>96001</v>
+        <v>56798</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4495,25 +4490,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4523,10 +4518,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>286522</v>
+        <v>286667</v>
       </c>
       <c r="R38" t="n">
-        <v>6508764</v>
+        <v>6508726</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4559,6 +4554,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4585,10 +4585,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113399404</v>
+        <v>113399464</v>
       </c>
       <c r="B39" t="n">
-        <v>93806</v>
+        <v>94164</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4601,21 +4601,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>286719</v>
+        <v>286444</v>
       </c>
       <c r="R39" t="n">
-        <v>6508879</v>
+        <v>6508165</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4687,10 +4687,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113399439</v>
+        <v>113399405</v>
       </c>
       <c r="B40" t="n">
-        <v>56796</v>
+        <v>93811</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4699,25 +4699,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>286834</v>
+        <v>286655</v>
       </c>
       <c r="R40" t="n">
-        <v>6508948</v>
+        <v>6508854</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4763,11 +4763,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4794,10 +4789,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113399464</v>
+        <v>113399412</v>
       </c>
       <c r="B41" t="n">
-        <v>94159</v>
+        <v>95646</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4810,21 +4805,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4834,10 +4829,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>286444</v>
+        <v>286668</v>
       </c>
       <c r="R41" t="n">
-        <v>6508165</v>
+        <v>6508839</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4896,10 +4891,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113399427</v>
+        <v>113399438</v>
       </c>
       <c r="B42" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4936,10 +4931,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>286422</v>
+        <v>286835</v>
       </c>
       <c r="R42" t="n">
-        <v>6508051</v>
+        <v>6508956</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5003,10 +4998,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399420</v>
+        <v>113399428</v>
       </c>
       <c r="B43" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5043,10 +5038,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286325</v>
+        <v>286459</v>
       </c>
       <c r="R43" t="n">
-        <v>6507609</v>
+        <v>6508160</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5110,10 +5105,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399442</v>
+        <v>113399437</v>
       </c>
       <c r="B44" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5150,10 +5145,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>286541</v>
+        <v>286715</v>
       </c>
       <c r="R44" t="n">
-        <v>6508510</v>
+        <v>6508776</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5190,7 +5185,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5217,10 +5212,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113399409</v>
+        <v>113399427</v>
       </c>
       <c r="B45" t="n">
-        <v>56780</v>
+        <v>56798</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5233,16 +5228,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5257,10 +5252,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>286461</v>
+        <v>286422</v>
       </c>
       <c r="R45" t="n">
-        <v>6508704</v>
+        <v>6508051</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5297,7 +5292,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5324,10 +5319,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113399460</v>
+        <v>113399433</v>
       </c>
       <c r="B46" t="n">
-        <v>96001</v>
+        <v>56798</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5336,25 +5331,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5364,10 +5359,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>286595</v>
+        <v>286505</v>
       </c>
       <c r="R46" t="n">
-        <v>6508872</v>
+        <v>6508433</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5400,6 +5395,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5426,10 +5426,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113399457</v>
+        <v>113399432</v>
       </c>
       <c r="B47" t="n">
-        <v>96001</v>
+        <v>56798</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5438,25 +5438,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5466,10 +5466,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>286398</v>
+        <v>286495</v>
       </c>
       <c r="R47" t="n">
-        <v>6508131</v>
+        <v>6508424</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5502,6 +5502,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5528,10 +5533,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113399411</v>
+        <v>113399429</v>
       </c>
       <c r="B48" t="n">
-        <v>95641</v>
+        <v>56798</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5540,25 +5545,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5568,10 +5573,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>286712</v>
+        <v>286485</v>
       </c>
       <c r="R48" t="n">
-        <v>6508906</v>
+        <v>6508336</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5604,6 +5609,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5630,10 +5640,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113399436</v>
+        <v>113399455</v>
       </c>
       <c r="B49" t="n">
-        <v>56796</v>
+        <v>96006</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5642,25 +5652,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5670,10 +5680,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>286684</v>
+        <v>286525</v>
       </c>
       <c r="R49" t="n">
-        <v>6508737</v>
+        <v>6508767</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5706,11 +5716,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5737,10 +5742,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113399425</v>
+        <v>113399463</v>
       </c>
       <c r="B50" t="n">
-        <v>56796</v>
+        <v>99626</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5749,25 +5754,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5777,10 +5782,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>286469</v>
+        <v>286229</v>
       </c>
       <c r="R50" t="n">
-        <v>6508059</v>
+        <v>6507839</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5813,11 +5818,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -1420,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399411</v>
+        <v>113399431</v>
       </c>
       <c r="B9" t="n">
-        <v>95646</v>
+        <v>56798</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,25 +1432,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>286712</v>
+        <v>286459</v>
       </c>
       <c r="R9" t="n">
-        <v>6508906</v>
+        <v>6508392</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,6 +1496,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399431</v>
+        <v>113399411</v>
       </c>
       <c r="B10" t="n">
-        <v>56798</v>
+        <v>95646</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1534,25 +1539,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>286459</v>
+        <v>286712</v>
       </c>
       <c r="R10" t="n">
-        <v>6508392</v>
+        <v>6508906</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,11 +1603,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -3214,10 +3214,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113399423</v>
+        <v>113399404</v>
       </c>
       <c r="B26" t="n">
-        <v>56798</v>
+        <v>93811</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3226,25 +3226,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>286426</v>
+        <v>286719</v>
       </c>
       <c r="R26" t="n">
-        <v>6507790</v>
+        <v>6508879</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3290,11 +3290,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3321,10 +3316,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113399404</v>
+        <v>113399423</v>
       </c>
       <c r="B27" t="n">
-        <v>93811</v>
+        <v>56798</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3333,25 +3328,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3361,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>286719</v>
+        <v>286426</v>
       </c>
       <c r="R27" t="n">
-        <v>6508879</v>
+        <v>6507790</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3397,6 +3392,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3423,10 +3423,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113399410</v>
+        <v>113399441</v>
       </c>
       <c r="B28" t="n">
-        <v>95646</v>
+        <v>56798</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3435,25 +3435,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>286724</v>
+        <v>286510</v>
       </c>
       <c r="R28" t="n">
-        <v>6508823</v>
+        <v>6508675</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3499,6 +3499,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3525,10 +3530,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113399448</v>
+        <v>113399436</v>
       </c>
       <c r="B29" t="n">
-        <v>91385</v>
+        <v>56798</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3541,21 +3546,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3565,10 +3570,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>286525</v>
+        <v>286684</v>
       </c>
       <c r="R29" t="n">
-        <v>6508258</v>
+        <v>6508737</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3605,7 +3610,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>9 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3632,10 +3637,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113399408</v>
+        <v>113399421</v>
       </c>
       <c r="B30" t="n">
-        <v>56782</v>
+        <v>56798</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3648,16 +3653,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3672,10 +3677,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>286479</v>
+        <v>286411</v>
       </c>
       <c r="R30" t="n">
-        <v>6508372</v>
+        <v>6507674</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3712,7 +3717,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rnghack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3739,10 +3744,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113399441</v>
+        <v>113399410</v>
       </c>
       <c r="B31" t="n">
-        <v>56798</v>
+        <v>95646</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3751,25 +3756,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3779,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>286510</v>
+        <v>286724</v>
       </c>
       <c r="R31" t="n">
-        <v>6508675</v>
+        <v>6508823</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3815,11 +3820,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3846,10 +3846,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113399436</v>
+        <v>113399408</v>
       </c>
       <c r="B32" t="n">
-        <v>56798</v>
+        <v>56782</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3862,16 +3862,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>286684</v>
+        <v>286479</v>
       </c>
       <c r="R32" t="n">
-        <v>6508737</v>
+        <v>6508372</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3953,10 +3953,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113399421</v>
+        <v>113399448</v>
       </c>
       <c r="B33" t="n">
-        <v>56798</v>
+        <v>91385</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3969,21 +3969,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>286411</v>
+        <v>286525</v>
       </c>
       <c r="R33" t="n">
-        <v>6507674</v>
+        <v>6508258</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4162,10 +4162,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113399424</v>
+        <v>113399458</v>
       </c>
       <c r="B35" t="n">
-        <v>56798</v>
+        <v>96006</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4174,25 +4174,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>286495</v>
+        <v>286751</v>
       </c>
       <c r="R35" t="n">
-        <v>6508076</v>
+        <v>6508904</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4238,11 +4238,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4269,10 +4264,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113399458</v>
+        <v>113399424</v>
       </c>
       <c r="B36" t="n">
-        <v>96006</v>
+        <v>56798</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4281,25 +4276,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4309,10 +4304,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>286751</v>
+        <v>286495</v>
       </c>
       <c r="R36" t="n">
-        <v>6508904</v>
+        <v>6508076</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4345,6 +4340,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>113354383</v>
       </c>
       <c r="B3" t="n">
-        <v>90110</v>
+        <v>90141</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113399413</v>
+        <v>113399428</v>
       </c>
       <c r="B4" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>286327</v>
+        <v>286459</v>
       </c>
       <c r="R4" t="n">
-        <v>6508012</v>
+        <v>6508160</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113399449</v>
+        <v>113399422</v>
       </c>
       <c r="B5" t="n">
-        <v>91385</v>
+        <v>56826</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>286530</v>
+        <v>286408</v>
       </c>
       <c r="R5" t="n">
-        <v>6508258</v>
+        <v>6507718</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1073,6 +1073,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113399414</v>
+        <v>113399405</v>
       </c>
       <c r="B6" t="n">
-        <v>56798</v>
+        <v>93839</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>286242</v>
+        <v>286655</v>
       </c>
       <c r="R6" t="n">
-        <v>6507840</v>
+        <v>6508854</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1175,11 +1180,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113399425</v>
+        <v>113399455</v>
       </c>
       <c r="B7" t="n">
-        <v>56798</v>
+        <v>96034</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,25 +1218,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>286469</v>
+        <v>286525</v>
       </c>
       <c r="R7" t="n">
-        <v>6508059</v>
+        <v>6508767</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1282,11 +1282,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,10 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113399419</v>
+        <v>113399443</v>
       </c>
       <c r="B8" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>286311</v>
+        <v>286465</v>
       </c>
       <c r="R8" t="n">
-        <v>6507585</v>
+        <v>6508688</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1393,7 +1388,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399431</v>
+        <v>113399434</v>
       </c>
       <c r="B9" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>286459</v>
+        <v>286601</v>
       </c>
       <c r="R9" t="n">
-        <v>6508392</v>
+        <v>6508623</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1527,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399411</v>
+        <v>113399420</v>
       </c>
       <c r="B10" t="n">
-        <v>95646</v>
+        <v>56826</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,25 +1534,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>286712</v>
+        <v>286325</v>
       </c>
       <c r="R10" t="n">
-        <v>6508906</v>
+        <v>6507609</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1603,6 +1598,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399430</v>
+        <v>113399425</v>
       </c>
       <c r="B11" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>286476</v>
+        <v>286469</v>
       </c>
       <c r="R11" t="n">
-        <v>6508348</v>
+        <v>6508059</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399426</v>
+        <v>113399463</v>
       </c>
       <c r="B12" t="n">
-        <v>56798</v>
+        <v>99655</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1748,25 +1748,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>286454</v>
+        <v>286229</v>
       </c>
       <c r="R12" t="n">
-        <v>6508073</v>
+        <v>6507839</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1812,11 +1812,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113399443</v>
+        <v>113399457</v>
       </c>
       <c r="B13" t="n">
-        <v>56798</v>
+        <v>96034</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,25 +1850,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>286465</v>
+        <v>286398</v>
       </c>
       <c r="R13" t="n">
-        <v>6508688</v>
+        <v>6508131</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1919,11 +1914,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1950,10 +1940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113399442</v>
+        <v>113399408</v>
       </c>
       <c r="B14" t="n">
-        <v>56798</v>
+        <v>56810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,16 +1956,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1990,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>286541</v>
+        <v>286479</v>
       </c>
       <c r="R14" t="n">
-        <v>6508510</v>
+        <v>6508372</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2030,7 +2020,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2057,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399457</v>
+        <v>113399448</v>
       </c>
       <c r="B15" t="n">
-        <v>96006</v>
+        <v>91413</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,25 +2059,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2606</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2097,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>286398</v>
+        <v>286525</v>
       </c>
       <c r="R15" t="n">
-        <v>6508131</v>
+        <v>6508258</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2133,6 +2123,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2159,10 +2154,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399420</v>
+        <v>113399440</v>
       </c>
       <c r="B16" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>286325</v>
+        <v>286483</v>
       </c>
       <c r="R16" t="n">
-        <v>6507609</v>
+        <v>6508722</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2266,10 +2261,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399460</v>
+        <v>113399437</v>
       </c>
       <c r="B17" t="n">
-        <v>96006</v>
+        <v>56826</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2278,25 +2273,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2306,10 +2301,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>286595</v>
+        <v>286715</v>
       </c>
       <c r="R17" t="n">
-        <v>6508872</v>
+        <v>6508776</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2342,6 +2337,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2368,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399440</v>
+        <v>113399432</v>
       </c>
       <c r="B18" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>286483</v>
+        <v>286495</v>
       </c>
       <c r="R18" t="n">
-        <v>6508722</v>
+        <v>6508424</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2475,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399439</v>
+        <v>113399442</v>
       </c>
       <c r="B19" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>286834</v>
+        <v>286541</v>
       </c>
       <c r="R19" t="n">
-        <v>6508948</v>
+        <v>6508510</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2582,10 +2582,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399409</v>
+        <v>113399426</v>
       </c>
       <c r="B20" t="n">
-        <v>56782</v>
+        <v>56826</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2598,16 +2598,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>286461</v>
+        <v>286454</v>
       </c>
       <c r="R20" t="n">
-        <v>6508704</v>
+        <v>6508073</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2692,7 +2692,7 @@
         <v>113399456</v>
       </c>
       <c r="B21" t="n">
-        <v>96006</v>
+        <v>96034</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2791,10 +2791,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113399461</v>
+        <v>113399435</v>
       </c>
       <c r="B22" t="n">
-        <v>99626</v>
+        <v>56826</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2803,25 +2803,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>286239</v>
+        <v>286667</v>
       </c>
       <c r="R22" t="n">
-        <v>6507778</v>
+        <v>6508726</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2867,6 +2867,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2893,10 +2898,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113399417</v>
+        <v>113399423</v>
       </c>
       <c r="B23" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2933,10 +2938,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>286266</v>
+        <v>286426</v>
       </c>
       <c r="R23" t="n">
-        <v>6507549</v>
+        <v>6507790</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3000,10 +3005,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113399418</v>
+        <v>113399427</v>
       </c>
       <c r="B24" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3040,10 +3045,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>286273</v>
+        <v>286422</v>
       </c>
       <c r="R24" t="n">
-        <v>6507549</v>
+        <v>6508051</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3107,10 +3112,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113399434</v>
+        <v>113399409</v>
       </c>
       <c r="B25" t="n">
-        <v>56798</v>
+        <v>56810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3123,16 +3128,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3147,10 +3152,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>286601</v>
+        <v>286461</v>
       </c>
       <c r="R25" t="n">
-        <v>6508623</v>
+        <v>6508704</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3187,7 +3192,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3214,10 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113399404</v>
+        <v>113399414</v>
       </c>
       <c r="B26" t="n">
-        <v>93811</v>
+        <v>56826</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3226,25 +3231,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3254,10 +3259,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>286719</v>
+        <v>286242</v>
       </c>
       <c r="R26" t="n">
-        <v>6508879</v>
+        <v>6507840</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3290,6 +3295,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3316,10 +3326,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113399423</v>
+        <v>113399404</v>
       </c>
       <c r="B27" t="n">
-        <v>56798</v>
+        <v>93839</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3328,25 +3338,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3356,10 +3366,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>286426</v>
+        <v>286719</v>
       </c>
       <c r="R27" t="n">
-        <v>6507790</v>
+        <v>6508879</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3392,11 +3402,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3423,10 +3428,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113399441</v>
+        <v>113399430</v>
       </c>
       <c r="B28" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3463,10 +3468,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>286510</v>
+        <v>286476</v>
       </c>
       <c r="R28" t="n">
-        <v>6508675</v>
+        <v>6508348</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3530,10 +3535,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113399436</v>
+        <v>113399421</v>
       </c>
       <c r="B29" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3570,10 +3575,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>286684</v>
+        <v>286411</v>
       </c>
       <c r="R29" t="n">
-        <v>6508737</v>
+        <v>6507674</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3637,10 +3642,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113399421</v>
+        <v>113399461</v>
       </c>
       <c r="B30" t="n">
-        <v>56798</v>
+        <v>99655</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3649,25 +3654,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3677,10 +3682,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>286411</v>
+        <v>286239</v>
       </c>
       <c r="R30" t="n">
-        <v>6507674</v>
+        <v>6507778</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3713,11 +3718,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3744,10 +3744,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113399410</v>
+        <v>113399459</v>
       </c>
       <c r="B31" t="n">
-        <v>95646</v>
+        <v>96034</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3760,21 +3760,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2569</v>
+        <v>2606</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>286724</v>
+        <v>286600</v>
       </c>
       <c r="R31" t="n">
-        <v>6508823</v>
+        <v>6508882</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113399408</v>
+        <v>113399412</v>
       </c>
       <c r="B32" t="n">
-        <v>56782</v>
+        <v>95674</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3858,25 +3858,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>2569</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>286479</v>
+        <v>286668</v>
       </c>
       <c r="R32" t="n">
-        <v>6508372</v>
+        <v>6508839</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3922,11 +3922,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3953,10 +3948,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113399448</v>
+        <v>113399441</v>
       </c>
       <c r="B33" t="n">
-        <v>91385</v>
+        <v>56826</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3969,21 +3964,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3993,10 +3988,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>286525</v>
+        <v>286510</v>
       </c>
       <c r="R33" t="n">
-        <v>6508258</v>
+        <v>6508675</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4033,7 +4028,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>9 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4060,10 +4055,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113399459</v>
+        <v>113399417</v>
       </c>
       <c r="B34" t="n">
-        <v>96006</v>
+        <v>56826</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4072,25 +4067,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4100,10 +4095,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>286600</v>
+        <v>286266</v>
       </c>
       <c r="R34" t="n">
-        <v>6508882</v>
+        <v>6507549</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4136,6 +4131,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4162,10 +4162,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113399458</v>
+        <v>113399418</v>
       </c>
       <c r="B35" t="n">
-        <v>96006</v>
+        <v>56826</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4174,25 +4174,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>286751</v>
+        <v>286273</v>
       </c>
       <c r="R35" t="n">
-        <v>6508904</v>
+        <v>6507549</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4238,6 +4238,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4264,10 +4269,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113399424</v>
+        <v>113399458</v>
       </c>
       <c r="B36" t="n">
-        <v>56798</v>
+        <v>96034</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4276,25 +4281,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4304,10 +4309,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>286495</v>
+        <v>286751</v>
       </c>
       <c r="R36" t="n">
-        <v>6508076</v>
+        <v>6508904</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4340,11 +4345,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4371,10 +4371,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113399422</v>
+        <v>113399464</v>
       </c>
       <c r="B37" t="n">
-        <v>56798</v>
+        <v>94192</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4383,25 +4383,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>286408</v>
+        <v>286444</v>
       </c>
       <c r="R37" t="n">
-        <v>6507718</v>
+        <v>6508165</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4447,11 +4447,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4478,10 +4473,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113399435</v>
+        <v>113399439</v>
       </c>
       <c r="B38" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4518,10 +4513,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>286667</v>
+        <v>286834</v>
       </c>
       <c r="R38" t="n">
-        <v>6508726</v>
+        <v>6508948</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4585,10 +4580,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113399464</v>
+        <v>113399410</v>
       </c>
       <c r="B39" t="n">
-        <v>94164</v>
+        <v>95674</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4601,21 +4596,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4625,10 +4620,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>286444</v>
+        <v>286724</v>
       </c>
       <c r="R39" t="n">
-        <v>6508165</v>
+        <v>6508823</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4687,10 +4682,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113399405</v>
+        <v>113399436</v>
       </c>
       <c r="B40" t="n">
-        <v>93811</v>
+        <v>56826</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4699,25 +4694,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4727,10 +4722,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>286655</v>
+        <v>286684</v>
       </c>
       <c r="R40" t="n">
-        <v>6508854</v>
+        <v>6508737</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4763,6 +4758,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4789,10 +4789,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113399412</v>
+        <v>113399419</v>
       </c>
       <c r="B41" t="n">
-        <v>95646</v>
+        <v>56826</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4801,25 +4801,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>286668</v>
+        <v>286311</v>
       </c>
       <c r="R41" t="n">
-        <v>6508839</v>
+        <v>6507585</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4865,6 +4865,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4891,10 +4896,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113399438</v>
+        <v>113399433</v>
       </c>
       <c r="B42" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4931,10 +4936,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>286835</v>
+        <v>286505</v>
       </c>
       <c r="R42" t="n">
-        <v>6508956</v>
+        <v>6508433</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4998,10 +5003,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399428</v>
+        <v>113399460</v>
       </c>
       <c r="B43" t="n">
-        <v>56798</v>
+        <v>96034</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5010,25 +5015,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5038,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286459</v>
+        <v>286595</v>
       </c>
       <c r="R43" t="n">
-        <v>6508160</v>
+        <v>6508872</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5074,11 +5079,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5105,10 +5105,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399437</v>
+        <v>113399424</v>
       </c>
       <c r="B44" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>286715</v>
+        <v>286495</v>
       </c>
       <c r="R44" t="n">
-        <v>6508776</v>
+        <v>6508076</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5212,10 +5212,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113399427</v>
+        <v>113399429</v>
       </c>
       <c r="B45" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5252,10 +5252,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>286422</v>
+        <v>286485</v>
       </c>
       <c r="R45" t="n">
-        <v>6508051</v>
+        <v>6508336</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5319,10 +5319,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113399433</v>
+        <v>113399411</v>
       </c>
       <c r="B46" t="n">
-        <v>56798</v>
+        <v>95674</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5331,25 +5331,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>286505</v>
+        <v>286712</v>
       </c>
       <c r="R46" t="n">
-        <v>6508433</v>
+        <v>6508906</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5395,11 +5395,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5426,10 +5421,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113399432</v>
+        <v>113399413</v>
       </c>
       <c r="B47" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5466,10 +5461,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>286495</v>
+        <v>286327</v>
       </c>
       <c r="R47" t="n">
-        <v>6508424</v>
+        <v>6508012</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5533,10 +5528,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113399429</v>
+        <v>113399449</v>
       </c>
       <c r="B48" t="n">
-        <v>56798</v>
+        <v>91413</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5549,21 +5544,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5573,10 +5568,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>286485</v>
+        <v>286530</v>
       </c>
       <c r="R48" t="n">
-        <v>6508336</v>
+        <v>6508258</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5609,11 +5604,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5640,10 +5630,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113399455</v>
+        <v>113399438</v>
       </c>
       <c r="B49" t="n">
-        <v>96006</v>
+        <v>56826</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5652,25 +5642,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5680,10 +5670,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>286525</v>
+        <v>286835</v>
       </c>
       <c r="R49" t="n">
-        <v>6508767</v>
+        <v>6508956</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5716,6 +5706,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5742,10 +5737,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113399463</v>
+        <v>113399431</v>
       </c>
       <c r="B50" t="n">
-        <v>99626</v>
+        <v>56826</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5754,25 +5749,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5782,10 +5777,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>286229</v>
+        <v>286459</v>
       </c>
       <c r="R50" t="n">
-        <v>6507839</v>
+        <v>6508392</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5818,6 +5813,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113399455</v>
+        <v>113399443</v>
       </c>
       <c r="B7" t="n">
-        <v>96034</v>
+        <v>56826</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,25 +1218,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>286525</v>
+        <v>286465</v>
       </c>
       <c r="R7" t="n">
-        <v>6508767</v>
+        <v>6508688</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1282,6 +1282,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,7 +1313,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113399443</v>
+        <v>113399434</v>
       </c>
       <c r="B8" t="n">
         <v>56826</v>
@@ -1348,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>286465</v>
+        <v>286601</v>
       </c>
       <c r="R8" t="n">
-        <v>6508688</v>
+        <v>6508623</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1388,7 +1393,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,7 +1420,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399434</v>
+        <v>113399420</v>
       </c>
       <c r="B9" t="n">
         <v>56826</v>
@@ -1455,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>286601</v>
+        <v>286325</v>
       </c>
       <c r="R9" t="n">
-        <v>6508623</v>
+        <v>6507609</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1522,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399420</v>
+        <v>113399463</v>
       </c>
       <c r="B10" t="n">
-        <v>56826</v>
+        <v>99655</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1534,25 +1539,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>286325</v>
+        <v>286229</v>
       </c>
       <c r="R10" t="n">
-        <v>6507609</v>
+        <v>6507839</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,11 +1603,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399463</v>
+        <v>113399455</v>
       </c>
       <c r="B12" t="n">
-        <v>99655</v>
+        <v>96034</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,21 +1752,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>2606</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>286229</v>
+        <v>286525</v>
       </c>
       <c r="R12" t="n">
-        <v>6507839</v>
+        <v>6508767</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1838,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113399457</v>
+        <v>113399408</v>
       </c>
       <c r="B13" t="n">
-        <v>96034</v>
+        <v>56810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1850,25 +1850,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2606</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>286398</v>
+        <v>286479</v>
       </c>
       <c r="R13" t="n">
-        <v>6508131</v>
+        <v>6508372</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1914,6 +1914,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1940,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113399408</v>
+        <v>113399457</v>
       </c>
       <c r="B14" t="n">
-        <v>56810</v>
+        <v>96034</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1952,25 +1957,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2606</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1980,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>286479</v>
+        <v>286398</v>
       </c>
       <c r="R14" t="n">
-        <v>6508372</v>
+        <v>6508131</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2016,11 +2021,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3219,10 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113399414</v>
+        <v>113399461</v>
       </c>
       <c r="B26" t="n">
-        <v>56826</v>
+        <v>99655</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3231,25 +3231,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>286242</v>
+        <v>286239</v>
       </c>
       <c r="R26" t="n">
-        <v>6507840</v>
+        <v>6507778</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3295,11 +3295,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3326,10 +3321,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113399404</v>
+        <v>113399430</v>
       </c>
       <c r="B27" t="n">
-        <v>93839</v>
+        <v>56826</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3338,25 +3333,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3366,10 +3361,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>286719</v>
+        <v>286476</v>
       </c>
       <c r="R27" t="n">
-        <v>6508879</v>
+        <v>6508348</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3402,6 +3397,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3428,7 +3428,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113399430</v>
+        <v>113399421</v>
       </c>
       <c r="B28" t="n">
         <v>56826</v>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>286476</v>
+        <v>286411</v>
       </c>
       <c r="R28" t="n">
-        <v>6508348</v>
+        <v>6507674</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3535,7 +3535,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113399421</v>
+        <v>113399414</v>
       </c>
       <c r="B29" t="n">
         <v>56826</v>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>286411</v>
+        <v>286242</v>
       </c>
       <c r="R29" t="n">
-        <v>6507674</v>
+        <v>6507840</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113399461</v>
+        <v>113399404</v>
       </c>
       <c r="B30" t="n">
-        <v>99655</v>
+        <v>93839</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3658,21 +3658,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>2810</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>286239</v>
+        <v>286719</v>
       </c>
       <c r="R30" t="n">
-        <v>6507778</v>
+        <v>6508879</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -5003,10 +5003,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399460</v>
+        <v>113399424</v>
       </c>
       <c r="B43" t="n">
-        <v>96034</v>
+        <v>56826</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5015,25 +5015,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286595</v>
+        <v>286495</v>
       </c>
       <c r="R43" t="n">
-        <v>6508872</v>
+        <v>6508076</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5079,6 +5079,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5105,7 +5110,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399424</v>
+        <v>113399429</v>
       </c>
       <c r="B44" t="n">
         <v>56826</v>
@@ -5145,10 +5150,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>286495</v>
+        <v>286485</v>
       </c>
       <c r="R44" t="n">
-        <v>6508076</v>
+        <v>6508336</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5212,10 +5217,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113399429</v>
+        <v>113399460</v>
       </c>
       <c r="B45" t="n">
-        <v>56826</v>
+        <v>96034</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5224,25 +5229,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5252,10 +5257,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>286485</v>
+        <v>286595</v>
       </c>
       <c r="R45" t="n">
-        <v>6508336</v>
+        <v>6508872</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5288,11 +5293,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5319,10 +5319,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113399411</v>
+        <v>113399413</v>
       </c>
       <c r="B46" t="n">
-        <v>95674</v>
+        <v>56826</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5331,25 +5331,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>286712</v>
+        <v>286327</v>
       </c>
       <c r="R46" t="n">
-        <v>6508906</v>
+        <v>6508012</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5395,6 +5395,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5421,7 +5426,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113399413</v>
+        <v>113399438</v>
       </c>
       <c r="B47" t="n">
         <v>56826</v>
@@ -5461,10 +5466,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>286327</v>
+        <v>286835</v>
       </c>
       <c r="R47" t="n">
-        <v>6508012</v>
+        <v>6508956</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5528,10 +5533,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113399449</v>
+        <v>113399431</v>
       </c>
       <c r="B48" t="n">
-        <v>91413</v>
+        <v>56826</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5544,21 +5549,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5568,10 +5573,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>286530</v>
+        <v>286459</v>
       </c>
       <c r="R48" t="n">
-        <v>6508258</v>
+        <v>6508392</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5604,6 +5609,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5630,10 +5640,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113399438</v>
+        <v>113399411</v>
       </c>
       <c r="B49" t="n">
-        <v>56826</v>
+        <v>95674</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5642,25 +5652,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5670,10 +5680,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>286835</v>
+        <v>286712</v>
       </c>
       <c r="R49" t="n">
-        <v>6508956</v>
+        <v>6508906</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5706,11 +5716,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5737,10 +5742,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113399431</v>
+        <v>113399449</v>
       </c>
       <c r="B50" t="n">
-        <v>56826</v>
+        <v>91413</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5753,21 +5758,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5777,10 +5782,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>286459</v>
+        <v>286530</v>
       </c>
       <c r="R50" t="n">
-        <v>6508392</v>
+        <v>6508258</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5813,11 +5818,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>113354383</v>
       </c>
       <c r="B3" t="n">
-        <v>90141</v>
+        <v>90142</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113399428</v>
+        <v>113399442</v>
       </c>
       <c r="B4" t="n">
         <v>56826</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>286459</v>
+        <v>286541</v>
       </c>
       <c r="R4" t="n">
-        <v>6508160</v>
+        <v>6508510</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -970,7 +970,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113399422</v>
+        <v>113399419</v>
       </c>
       <c r="B5" t="n">
         <v>56826</v>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>286408</v>
+        <v>286311</v>
       </c>
       <c r="R5" t="n">
-        <v>6507718</v>
+        <v>6507585</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113399405</v>
+        <v>113399457</v>
       </c>
       <c r="B6" t="n">
-        <v>93839</v>
+        <v>96034</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>286655</v>
+        <v>286398</v>
       </c>
       <c r="R6" t="n">
-        <v>6508854</v>
+        <v>6508131</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1206,7 +1206,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113399443</v>
+        <v>113399428</v>
       </c>
       <c r="B7" t="n">
         <v>56826</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>286465</v>
+        <v>286459</v>
       </c>
       <c r="R7" t="n">
-        <v>6508688</v>
+        <v>6508160</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,7 +1313,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113399434</v>
+        <v>113399432</v>
       </c>
       <c r="B8" t="n">
         <v>56826</v>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>286601</v>
+        <v>286495</v>
       </c>
       <c r="R8" t="n">
-        <v>6508623</v>
+        <v>6508424</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1420,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399420</v>
+        <v>113399448</v>
       </c>
       <c r="B9" t="n">
-        <v>56826</v>
+        <v>91413</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,21 +1436,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>286325</v>
+        <v>286525</v>
       </c>
       <c r="R9" t="n">
-        <v>6507609</v>
+        <v>6508258</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399463</v>
+        <v>113399431</v>
       </c>
       <c r="B10" t="n">
-        <v>99655</v>
+        <v>56826</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,25 +1539,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>286229</v>
+        <v>286459</v>
       </c>
       <c r="R10" t="n">
-        <v>6507839</v>
+        <v>6508392</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1603,6 +1603,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399425</v>
+        <v>113399459</v>
       </c>
       <c r="B11" t="n">
-        <v>56826</v>
+        <v>96034</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>286469</v>
+        <v>286600</v>
       </c>
       <c r="R11" t="n">
-        <v>6508059</v>
+        <v>6508882</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1705,11 +1710,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1736,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399455</v>
+        <v>113399449</v>
       </c>
       <c r="B12" t="n">
-        <v>96034</v>
+        <v>91413</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1748,25 +1748,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2606</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>286525</v>
+        <v>286530</v>
       </c>
       <c r="R12" t="n">
-        <v>6508767</v>
+        <v>6508258</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1838,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113399408</v>
+        <v>113399413</v>
       </c>
       <c r="B13" t="n">
-        <v>56810</v>
+        <v>56826</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,16 +1854,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>286479</v>
+        <v>286327</v>
       </c>
       <c r="R13" t="n">
-        <v>6508372</v>
+        <v>6508012</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rnghack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113399457</v>
+        <v>113399418</v>
       </c>
       <c r="B14" t="n">
-        <v>96034</v>
+        <v>56826</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,25 +1957,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>286398</v>
+        <v>286273</v>
       </c>
       <c r="R14" t="n">
-        <v>6508131</v>
+        <v>6507549</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2021,6 +2021,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2047,10 +2052,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399448</v>
+        <v>113399436</v>
       </c>
       <c r="B15" t="n">
-        <v>91413</v>
+        <v>56826</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2063,21 +2068,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>286525</v>
+        <v>286684</v>
       </c>
       <c r="R15" t="n">
-        <v>6508258</v>
+        <v>6508737</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2127,7 +2132,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>9 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2154,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399440</v>
+        <v>113399461</v>
       </c>
       <c r="B16" t="n">
-        <v>56826</v>
+        <v>99655</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2166,25 +2171,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>286483</v>
+        <v>286239</v>
       </c>
       <c r="R16" t="n">
-        <v>6508722</v>
+        <v>6507778</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2230,11 +2235,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2261,10 +2261,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399437</v>
+        <v>113399405</v>
       </c>
       <c r="B17" t="n">
-        <v>56826</v>
+        <v>93839</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2273,25 +2273,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>286715</v>
+        <v>286655</v>
       </c>
       <c r="R17" t="n">
-        <v>6508776</v>
+        <v>6508854</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2337,11 +2337,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2368,7 +2363,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399432</v>
+        <v>113399435</v>
       </c>
       <c r="B18" t="n">
         <v>56826</v>
@@ -2408,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>286495</v>
+        <v>286667</v>
       </c>
       <c r="R18" t="n">
-        <v>6508424</v>
+        <v>6508726</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2475,7 +2470,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399442</v>
+        <v>113399433</v>
       </c>
       <c r="B19" t="n">
         <v>56826</v>
@@ -2515,10 +2510,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>286541</v>
+        <v>286505</v>
       </c>
       <c r="R19" t="n">
-        <v>6508510</v>
+        <v>6508433</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2555,7 +2550,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2582,7 +2577,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399426</v>
+        <v>113399420</v>
       </c>
       <c r="B20" t="n">
         <v>56826</v>
@@ -2622,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>286454</v>
+        <v>286325</v>
       </c>
       <c r="R20" t="n">
-        <v>6508073</v>
+        <v>6507609</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2689,10 +2684,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113399456</v>
+        <v>113399440</v>
       </c>
       <c r="B21" t="n">
-        <v>96034</v>
+        <v>56826</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2696,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2724,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>286522</v>
+        <v>286483</v>
       </c>
       <c r="R21" t="n">
-        <v>6508764</v>
+        <v>6508722</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2765,6 +2760,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2791,10 +2791,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113399435</v>
+        <v>113399409</v>
       </c>
       <c r="B22" t="n">
-        <v>56826</v>
+        <v>56810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,16 +2807,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>286667</v>
+        <v>286461</v>
       </c>
       <c r="R22" t="n">
-        <v>6508726</v>
+        <v>6508704</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2898,7 +2898,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113399423</v>
+        <v>113399421</v>
       </c>
       <c r="B23" t="n">
         <v>56826</v>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>286426</v>
+        <v>286411</v>
       </c>
       <c r="R23" t="n">
-        <v>6507790</v>
+        <v>6507674</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3005,10 +3005,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113399427</v>
+        <v>113399464</v>
       </c>
       <c r="B24" t="n">
-        <v>56826</v>
+        <v>94192</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3017,25 +3017,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>286422</v>
+        <v>286444</v>
       </c>
       <c r="R24" t="n">
-        <v>6508051</v>
+        <v>6508165</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3081,11 +3081,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3112,10 +3107,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113399409</v>
+        <v>113399455</v>
       </c>
       <c r="B25" t="n">
-        <v>56810</v>
+        <v>96034</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3124,25 +3119,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>2606</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3152,10 +3147,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>286461</v>
+        <v>286525</v>
       </c>
       <c r="R25" t="n">
-        <v>6508704</v>
+        <v>6508767</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3188,11 +3183,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3219,10 +3209,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113399461</v>
+        <v>113399460</v>
       </c>
       <c r="B26" t="n">
-        <v>99655</v>
+        <v>96034</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3235,21 +3225,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>2606</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3259,10 +3249,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>286239</v>
+        <v>286595</v>
       </c>
       <c r="R26" t="n">
-        <v>6507778</v>
+        <v>6508872</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3321,7 +3311,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113399430</v>
+        <v>113399439</v>
       </c>
       <c r="B27" t="n">
         <v>56826</v>
@@ -3361,10 +3351,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>286476</v>
+        <v>286834</v>
       </c>
       <c r="R27" t="n">
-        <v>6508348</v>
+        <v>6508948</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3428,7 +3418,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113399421</v>
+        <v>113399414</v>
       </c>
       <c r="B28" t="n">
         <v>56826</v>
@@ -3468,10 +3458,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>286411</v>
+        <v>286242</v>
       </c>
       <c r="R28" t="n">
-        <v>6507674</v>
+        <v>6507840</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3535,7 +3525,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113399414</v>
+        <v>113399437</v>
       </c>
       <c r="B29" t="n">
         <v>56826</v>
@@ -3575,10 +3565,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>286242</v>
+        <v>286715</v>
       </c>
       <c r="R29" t="n">
-        <v>6507840</v>
+        <v>6508776</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3642,10 +3632,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113399404</v>
+        <v>113399426</v>
       </c>
       <c r="B30" t="n">
-        <v>93839</v>
+        <v>56826</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3654,25 +3644,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3682,10 +3672,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>286719</v>
+        <v>286454</v>
       </c>
       <c r="R30" t="n">
-        <v>6508879</v>
+        <v>6508073</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3718,6 +3708,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3744,10 +3739,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113399459</v>
+        <v>113399434</v>
       </c>
       <c r="B31" t="n">
-        <v>96034</v>
+        <v>56826</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3756,25 +3751,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3784,10 +3779,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>286600</v>
+        <v>286601</v>
       </c>
       <c r="R31" t="n">
-        <v>6508882</v>
+        <v>6508623</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3820,6 +3815,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3846,10 +3846,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113399412</v>
+        <v>113399430</v>
       </c>
       <c r="B32" t="n">
-        <v>95674</v>
+        <v>56826</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3858,25 +3858,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>286668</v>
+        <v>286476</v>
       </c>
       <c r="R32" t="n">
-        <v>6508839</v>
+        <v>6508348</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3922,6 +3922,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3948,7 +3953,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113399441</v>
+        <v>113399429</v>
       </c>
       <c r="B33" t="n">
         <v>56826</v>
@@ -3988,10 +3993,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>286510</v>
+        <v>286485</v>
       </c>
       <c r="R33" t="n">
-        <v>6508675</v>
+        <v>6508336</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4055,10 +4060,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113399417</v>
+        <v>113399404</v>
       </c>
       <c r="B34" t="n">
-        <v>56826</v>
+        <v>93839</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4067,25 +4072,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4095,10 +4100,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>286266</v>
+        <v>286719</v>
       </c>
       <c r="R34" t="n">
-        <v>6507549</v>
+        <v>6508879</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4131,11 +4136,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4162,7 +4162,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113399418</v>
+        <v>113399443</v>
       </c>
       <c r="B35" t="n">
         <v>56826</v>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>286273</v>
+        <v>286465</v>
       </c>
       <c r="R35" t="n">
-        <v>6507549</v>
+        <v>6508688</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4269,10 +4269,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113399458</v>
+        <v>113399412</v>
       </c>
       <c r="B36" t="n">
-        <v>96034</v>
+        <v>95674</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4285,21 +4285,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2606</v>
+        <v>2569</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>286751</v>
+        <v>286668</v>
       </c>
       <c r="R36" t="n">
-        <v>6508904</v>
+        <v>6508839</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4371,10 +4371,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113399464</v>
+        <v>113399441</v>
       </c>
       <c r="B37" t="n">
-        <v>94192</v>
+        <v>56826</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4383,25 +4383,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>286444</v>
+        <v>286510</v>
       </c>
       <c r="R37" t="n">
-        <v>6508165</v>
+        <v>6508675</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4447,6 +4447,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4473,7 +4478,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113399439</v>
+        <v>113399423</v>
       </c>
       <c r="B38" t="n">
         <v>56826</v>
@@ -4513,10 +4518,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>286834</v>
+        <v>286426</v>
       </c>
       <c r="R38" t="n">
-        <v>6508948</v>
+        <v>6507790</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4580,10 +4585,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113399410</v>
+        <v>113399408</v>
       </c>
       <c r="B39" t="n">
-        <v>95674</v>
+        <v>56810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4592,25 +4597,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2569</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4620,10 +4625,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>286724</v>
+        <v>286479</v>
       </c>
       <c r="R39" t="n">
-        <v>6508823</v>
+        <v>6508372</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4656,6 +4661,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4682,10 +4692,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113399436</v>
+        <v>113399411</v>
       </c>
       <c r="B40" t="n">
-        <v>56826</v>
+        <v>95674</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4694,25 +4704,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4722,10 +4732,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>286684</v>
+        <v>286712</v>
       </c>
       <c r="R40" t="n">
-        <v>6508737</v>
+        <v>6508906</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4758,11 +4768,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4789,10 +4794,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113399419</v>
+        <v>113399456</v>
       </c>
       <c r="B41" t="n">
-        <v>56826</v>
+        <v>96034</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4801,25 +4806,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4829,10 +4834,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>286311</v>
+        <v>286522</v>
       </c>
       <c r="R41" t="n">
-        <v>6507585</v>
+        <v>6508764</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4865,11 +4870,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4896,7 +4896,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113399433</v>
+        <v>113399425</v>
       </c>
       <c r="B42" t="n">
         <v>56826</v>
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>286505</v>
+        <v>286469</v>
       </c>
       <c r="R42" t="n">
-        <v>6508433</v>
+        <v>6508059</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5003,10 +5003,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399424</v>
+        <v>113399458</v>
       </c>
       <c r="B43" t="n">
-        <v>56826</v>
+        <v>96034</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5015,25 +5015,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286495</v>
+        <v>286751</v>
       </c>
       <c r="R43" t="n">
-        <v>6508076</v>
+        <v>6508904</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5079,11 +5079,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5110,10 +5105,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399429</v>
+        <v>113399410</v>
       </c>
       <c r="B44" t="n">
-        <v>56826</v>
+        <v>95674</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5122,25 +5117,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5150,10 +5145,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>286485</v>
+        <v>286724</v>
       </c>
       <c r="R44" t="n">
-        <v>6508336</v>
+        <v>6508823</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5186,11 +5181,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5217,10 +5207,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113399460</v>
+        <v>113399422</v>
       </c>
       <c r="B45" t="n">
-        <v>96034</v>
+        <v>56826</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5229,25 +5219,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5257,10 +5247,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>286595</v>
+        <v>286408</v>
       </c>
       <c r="R45" t="n">
-        <v>6508872</v>
+        <v>6507718</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5293,6 +5283,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5319,7 +5314,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113399413</v>
+        <v>113399438</v>
       </c>
       <c r="B46" t="n">
         <v>56826</v>
@@ -5359,10 +5354,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>286327</v>
+        <v>286835</v>
       </c>
       <c r="R46" t="n">
-        <v>6508012</v>
+        <v>6508956</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5426,7 +5421,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113399438</v>
+        <v>113399417</v>
       </c>
       <c r="B47" t="n">
         <v>56826</v>
@@ -5466,10 +5461,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>286835</v>
+        <v>286266</v>
       </c>
       <c r="R47" t="n">
-        <v>6508956</v>
+        <v>6507549</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5533,10 +5528,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113399431</v>
+        <v>113399463</v>
       </c>
       <c r="B48" t="n">
-        <v>56826</v>
+        <v>99655</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5545,25 +5540,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5573,10 +5568,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>286459</v>
+        <v>286229</v>
       </c>
       <c r="R48" t="n">
-        <v>6508392</v>
+        <v>6507839</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5609,11 +5604,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5640,10 +5630,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113399411</v>
+        <v>113399427</v>
       </c>
       <c r="B49" t="n">
-        <v>95674</v>
+        <v>56826</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5652,25 +5642,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5680,10 +5670,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>286712</v>
+        <v>286422</v>
       </c>
       <c r="R49" t="n">
-        <v>6508906</v>
+        <v>6508051</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5716,6 +5706,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5742,10 +5737,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113399449</v>
+        <v>113399424</v>
       </c>
       <c r="B50" t="n">
-        <v>91413</v>
+        <v>56826</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5758,21 +5753,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5782,10 +5777,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>286530</v>
+        <v>286495</v>
       </c>
       <c r="R50" t="n">
-        <v>6508258</v>
+        <v>6508076</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5818,6 +5813,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2995,7 +2995,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113399442</v>
+        <v>113399428</v>
       </c>
       <c r="B24" t="n">
         <v>57281</v>
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>286541</v>
+        <v>286459</v>
       </c>
       <c r="R24" t="n">
-        <v>6508509</v>
+        <v>6508160</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3102,7 +3102,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113399428</v>
+        <v>113399426</v>
       </c>
       <c r="B25" t="n">
         <v>57281</v>
@@ -3142,10 +3142,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>286459</v>
+        <v>286454</v>
       </c>
       <c r="R25" t="n">
-        <v>6508160</v>
+        <v>6508073</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3209,10 +3209,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113399426</v>
+        <v>113399408</v>
       </c>
       <c r="B26" t="n">
-        <v>57281</v>
+        <v>57265</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3225,16 +3225,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>286454</v>
+        <v>286480</v>
       </c>
       <c r="R26" t="n">
-        <v>6508073</v>
+        <v>6508372</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3316,10 +3316,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113399408</v>
+        <v>113399435</v>
       </c>
       <c r="B27" t="n">
-        <v>57265</v>
+        <v>57281</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3332,16 +3332,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>286480</v>
+        <v>286667</v>
       </c>
       <c r="R27" t="n">
-        <v>6508372</v>
+        <v>6508726</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rnghack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3423,10 +3423,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113399435</v>
+        <v>113399457</v>
       </c>
       <c r="B28" t="n">
-        <v>57281</v>
+        <v>96283</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3435,25 +3435,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>286667</v>
+        <v>286398</v>
       </c>
       <c r="R28" t="n">
-        <v>6508726</v>
+        <v>6508131</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3499,11 +3499,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3530,10 +3525,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113399457</v>
+        <v>113399464</v>
       </c>
       <c r="B29" t="n">
-        <v>96283</v>
+        <v>94429</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3546,21 +3541,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2606</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3570,10 +3565,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>286398</v>
+        <v>286444</v>
       </c>
       <c r="R29" t="n">
-        <v>6508131</v>
+        <v>6508164</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3632,10 +3627,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113399464</v>
+        <v>113399430</v>
       </c>
       <c r="B30" t="n">
-        <v>94429</v>
+        <v>57281</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3644,25 +3639,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3672,10 +3667,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>286444</v>
+        <v>286477</v>
       </c>
       <c r="R30" t="n">
-        <v>6508164</v>
+        <v>6508348</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3708,6 +3703,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3734,10 +3734,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113399430</v>
+        <v>113399404</v>
       </c>
       <c r="B31" t="n">
-        <v>57281</v>
+        <v>94069</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3746,25 +3746,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>286477</v>
+        <v>286719</v>
       </c>
       <c r="R31" t="n">
-        <v>6508348</v>
+        <v>6508879</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3810,11 +3810,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3841,10 +3836,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113399404</v>
+        <v>113399436</v>
       </c>
       <c r="B32" t="n">
-        <v>94069</v>
+        <v>57281</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3853,25 +3848,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3881,10 +3876,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>286719</v>
+        <v>286684</v>
       </c>
       <c r="R32" t="n">
-        <v>6508879</v>
+        <v>6508737</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3917,6 +3912,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3943,10 +3943,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113399436</v>
+        <v>113399412</v>
       </c>
       <c r="B33" t="n">
-        <v>57281</v>
+        <v>95923</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3955,25 +3955,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>286684</v>
+        <v>286668</v>
       </c>
       <c r="R33" t="n">
-        <v>6508737</v>
+        <v>6508839</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4019,11 +4019,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4050,10 +4045,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113399412</v>
+        <v>113399422</v>
       </c>
       <c r="B34" t="n">
-        <v>95923</v>
+        <v>57281</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4062,25 +4057,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4090,10 +4085,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>286668</v>
+        <v>286408</v>
       </c>
       <c r="R34" t="n">
-        <v>6508839</v>
+        <v>6507719</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4126,6 +4121,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4152,10 +4152,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113399422</v>
+        <v>113399409</v>
       </c>
       <c r="B35" t="n">
-        <v>57281</v>
+        <v>57265</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4168,16 +4168,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>286408</v>
+        <v>286460</v>
       </c>
       <c r="R35" t="n">
-        <v>6507719</v>
+        <v>6508705</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4259,10 +4259,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113399409</v>
+        <v>113399438</v>
       </c>
       <c r="B36" t="n">
-        <v>57265</v>
+        <v>57281</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4275,16 +4275,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>286460</v>
+        <v>286835</v>
       </c>
       <c r="R36" t="n">
-        <v>6508705</v>
+        <v>6508956</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4366,7 +4366,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113399438</v>
+        <v>113399437</v>
       </c>
       <c r="B37" t="n">
         <v>57281</v>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>286835</v>
+        <v>286714</v>
       </c>
       <c r="R37" t="n">
-        <v>6508956</v>
+        <v>6508777</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113399437</v>
+        <v>113399420</v>
       </c>
       <c r="B38" t="n">
         <v>57281</v>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>286714</v>
+        <v>286325</v>
       </c>
       <c r="R38" t="n">
-        <v>6508777</v>
+        <v>6507609</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4580,10 +4580,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113399420</v>
+        <v>113399461</v>
       </c>
       <c r="B39" t="n">
-        <v>57281</v>
+        <v>99909</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4592,25 +4592,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>286325</v>
+        <v>286239</v>
       </c>
       <c r="R39" t="n">
-        <v>6507609</v>
+        <v>6507778</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4656,11 +4656,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4687,10 +4682,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113399461</v>
+        <v>113399413</v>
       </c>
       <c r="B40" t="n">
-        <v>99909</v>
+        <v>57281</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4699,25 +4694,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4727,10 +4722,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>286239</v>
+        <v>286327</v>
       </c>
       <c r="R40" t="n">
-        <v>6507778</v>
+        <v>6508012</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4763,6 +4758,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4789,7 +4789,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113399413</v>
+        <v>113399427</v>
       </c>
       <c r="B41" t="n">
         <v>57281</v>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>286327</v>
+        <v>286421</v>
       </c>
       <c r="R41" t="n">
-        <v>6508012</v>
+        <v>6508051</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113399427</v>
+        <v>113399421</v>
       </c>
       <c r="B42" t="n">
         <v>57281</v>
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>286421</v>
+        <v>286411</v>
       </c>
       <c r="R42" t="n">
-        <v>6508051</v>
+        <v>6507675</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5003,10 +5003,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399421</v>
+        <v>113399456</v>
       </c>
       <c r="B43" t="n">
-        <v>57281</v>
+        <v>96283</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5015,25 +5015,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286411</v>
+        <v>286522</v>
       </c>
       <c r="R43" t="n">
-        <v>6507675</v>
+        <v>6508764</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5079,11 +5079,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5110,10 +5105,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399456</v>
+        <v>113399411</v>
       </c>
       <c r="B44" t="n">
-        <v>96283</v>
+        <v>95923</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5126,21 +5121,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2606</v>
+        <v>2569</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5150,10 +5145,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>286522</v>
+        <v>286712</v>
       </c>
       <c r="R44" t="n">
-        <v>6508764</v>
+        <v>6508906</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5212,10 +5207,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113399411</v>
+        <v>113399424</v>
       </c>
       <c r="B45" t="n">
-        <v>95923</v>
+        <v>57281</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5224,25 +5219,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5252,10 +5247,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>286712</v>
+        <v>286495</v>
       </c>
       <c r="R45" t="n">
-        <v>6508906</v>
+        <v>6508076</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5288,6 +5283,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5314,7 +5314,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113399424</v>
+        <v>113399443</v>
       </c>
       <c r="B46" t="n">
         <v>57281</v>
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>286495</v>
+        <v>286466</v>
       </c>
       <c r="R46" t="n">
-        <v>6508076</v>
+        <v>6508689</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5421,10 +5421,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113399443</v>
+        <v>113399448</v>
       </c>
       <c r="B47" t="n">
-        <v>57281</v>
+        <v>91628</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5437,21 +5437,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>286466</v>
+        <v>286525</v>
       </c>
       <c r="R47" t="n">
-        <v>6508689</v>
+        <v>6508258</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5528,10 +5528,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113399448</v>
+        <v>113399431</v>
       </c>
       <c r="B48" t="n">
-        <v>91628</v>
+        <v>57281</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5544,21 +5544,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5568,10 +5568,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>286525</v>
+        <v>286459</v>
       </c>
       <c r="R48" t="n">
-        <v>6508258</v>
+        <v>6508391</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>9 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5635,7 +5635,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113399431</v>
+        <v>113399414</v>
       </c>
       <c r="B49" t="n">
         <v>57281</v>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>286459</v>
+        <v>286242</v>
       </c>
       <c r="R49" t="n">
-        <v>6508391</v>
+        <v>6507840</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5742,10 +5742,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113399414</v>
+        <v>113399463</v>
       </c>
       <c r="B50" t="n">
-        <v>57281</v>
+        <v>99909</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5754,25 +5754,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5782,10 +5782,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>286242</v>
+        <v>286229</v>
       </c>
       <c r="R50" t="n">
-        <v>6507840</v>
+        <v>6507839</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5820,11 +5820,6 @@
           <t>2023-11-24</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Hack</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5846,108 +5841,6 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>113399463</v>
-      </c>
-      <c r="B51" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Hala, Boh</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>286229</v>
-      </c>
-      <c r="R51" t="n">
-        <v>6507839</v>
-      </c>
-      <c r="S51" t="n">
-        <v>15</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Tanum</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Tanum</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73679582</v>
+        <v>113354383</v>
       </c>
       <c r="B2" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grebbestad, Boh</t>
+          <t>Kärret, Kärret, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>286602.4320459171</v>
+        <v>286292</v>
       </c>
       <c r="R2" t="n">
-        <v>6508615.67207083</v>
+        <v>6507528</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-01-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-01-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +761,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113354383</v>
+        <v>73679584</v>
       </c>
       <c r="B3" t="n">
-        <v>90343</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,38 +784,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kärret (Kärret), Boh</t>
+          <t>Grebbestad, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>286292</v>
+        <v>286595</v>
       </c>
       <c r="R3" t="n">
-        <v>6507528</v>
+        <v>6508432</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,12 +838,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-22</t>
+          <t>2018-01-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-22</t>
+          <t>2018-01-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,27 +858,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113399460</v>
+        <v>113399464</v>
       </c>
       <c r="B4" t="n">
-        <v>96283</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2606</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>286594</v>
+        <v>286444</v>
       </c>
       <c r="R4" t="n">
-        <v>6508872</v>
+        <v>6508164</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -992,37 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113399449</v>
+        <v>113399410</v>
       </c>
       <c r="B5" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1032,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>286530</v>
+        <v>286724</v>
       </c>
       <c r="R5" t="n">
-        <v>6508259</v>
+        <v>6508823</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1094,15 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113399405</v>
+        <v>113399411</v>
       </c>
       <c r="B6" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>286654</v>
+        <v>286712</v>
       </c>
       <c r="R6" t="n">
-        <v>6508853</v>
+        <v>6508906</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1196,15 +1161,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113399455</v>
+        <v>113399412</v>
       </c>
       <c r="B7" t="n">
-        <v>96283</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,21 +1172,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2606</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1236,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>286525</v>
+        <v>286668</v>
       </c>
       <c r="R7" t="n">
-        <v>6508767</v>
+        <v>6508839</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1298,37 +1258,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113399415</v>
+        <v>113399455</v>
       </c>
       <c r="B8" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>286247</v>
+        <v>286525</v>
       </c>
       <c r="R8" t="n">
-        <v>6507756</v>
+        <v>6508767</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1374,11 +1329,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,37 +1355,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399429</v>
+        <v>113399456</v>
       </c>
       <c r="B9" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1445,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>286485</v>
+        <v>286522</v>
       </c>
       <c r="R9" t="n">
-        <v>6508336</v>
+        <v>6508764</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1481,11 +1426,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1512,15 +1452,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399410</v>
+        <v>113399457</v>
       </c>
       <c r="B10" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1528,21 +1463,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>2606</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1552,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>286724</v>
+        <v>286398</v>
       </c>
       <c r="R10" t="n">
-        <v>6508823</v>
+        <v>6508131</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1614,37 +1549,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399423</v>
+        <v>113399458</v>
       </c>
       <c r="B11" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1654,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>286427</v>
+        <v>286751</v>
       </c>
       <c r="R11" t="n">
-        <v>6507789</v>
+        <v>6508904</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1690,11 +1620,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1721,37 +1646,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399441</v>
+        <v>113399459</v>
       </c>
       <c r="B12" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1761,10 +1681,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>286510</v>
+        <v>286600</v>
       </c>
       <c r="R12" t="n">
-        <v>6508675</v>
+        <v>6508882</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,11 +1717,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1828,37 +1743,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113399433</v>
+        <v>113399460</v>
       </c>
       <c r="B13" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1868,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>286505</v>
+        <v>286594</v>
       </c>
       <c r="R13" t="n">
-        <v>6508433</v>
+        <v>6508872</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1904,11 +1814,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1935,37 +1840,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113399417</v>
+        <v>113399404</v>
       </c>
       <c r="B14" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1975,10 +1875,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>286267</v>
+        <v>286719</v>
       </c>
       <c r="R14" t="n">
-        <v>6507549</v>
+        <v>6508879</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2011,11 +1911,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,37 +1937,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399439</v>
+        <v>113399405</v>
       </c>
       <c r="B15" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2082,10 +1972,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>286834</v>
+        <v>286654</v>
       </c>
       <c r="R15" t="n">
-        <v>6508948</v>
+        <v>6508853</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2118,11 +2008,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2149,15 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399459</v>
+        <v>73679582</v>
       </c>
       <c r="B16" t="n">
-        <v>96283</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,37 +2045,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2606</v>
+        <v>5420</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hala, Boh</t>
+          <t>Grebbestad, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>286600</v>
+        <v>286602</v>
       </c>
       <c r="R16" t="n">
-        <v>6508882</v>
+        <v>6508616</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2219,12 +2099,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2018-01-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2018-01-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2239,27 +2119,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399419</v>
+        <v>113399448</v>
       </c>
       <c r="B17" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2267,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2291,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>286311</v>
+        <v>286525</v>
       </c>
       <c r="R17" t="n">
-        <v>6507585</v>
+        <v>6508258</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2331,7 +2206,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2358,15 +2233,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399425</v>
+        <v>113399449</v>
       </c>
       <c r="B18" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,21 +2244,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2398,10 +2268,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>286469</v>
+        <v>286530</v>
       </c>
       <c r="R18" t="n">
-        <v>6508059</v>
+        <v>6508259</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2434,11 +2304,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2465,19 +2330,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399432</v>
+        <v>113399413</v>
       </c>
       <c r="B19" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2505,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>286495</v>
+        <v>286327</v>
       </c>
       <c r="R19" t="n">
-        <v>6508424</v>
+        <v>6508012</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2572,19 +2432,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399418</v>
+        <v>113399414</v>
       </c>
       <c r="B20" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2612,10 +2467,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>286272</v>
+        <v>286242</v>
       </c>
       <c r="R20" t="n">
-        <v>6507549</v>
+        <v>6507840</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2679,15 +2534,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113399458</v>
+        <v>113399415</v>
       </c>
       <c r="B21" t="n">
-        <v>96283</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2695,21 +2545,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2719,10 +2569,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>286751</v>
+        <v>286247</v>
       </c>
       <c r="R21" t="n">
-        <v>6508904</v>
+        <v>6507756</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2755,6 +2605,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2781,19 +2636,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113399434</v>
+        <v>113399416</v>
       </c>
       <c r="B22" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2821,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>286602</v>
+        <v>286249</v>
       </c>
       <c r="R22" t="n">
-        <v>6508623</v>
+        <v>6507749</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2888,19 +2738,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113399440</v>
+        <v>113399417</v>
       </c>
       <c r="B23" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2928,10 +2773,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>286483</v>
+        <v>286267</v>
       </c>
       <c r="R23" t="n">
-        <v>6508722</v>
+        <v>6507549</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2995,19 +2840,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113399428</v>
+        <v>113399418</v>
       </c>
       <c r="B24" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3035,10 +2875,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>286459</v>
+        <v>286272</v>
       </c>
       <c r="R24" t="n">
-        <v>6508160</v>
+        <v>6507549</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3102,19 +2942,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113399426</v>
+        <v>113399419</v>
       </c>
       <c r="B25" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3142,10 +2977,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>286454</v>
+        <v>286311</v>
       </c>
       <c r="R25" t="n">
-        <v>6508073</v>
+        <v>6507585</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3209,32 +3044,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113399408</v>
+        <v>113399420</v>
       </c>
       <c r="B26" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3249,10 +3079,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>286480</v>
+        <v>286325</v>
       </c>
       <c r="R26" t="n">
-        <v>6508372</v>
+        <v>6507609</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3289,7 +3119,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rnghack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3316,19 +3146,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113399435</v>
+        <v>113399421</v>
       </c>
       <c r="B27" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3356,10 +3181,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>286667</v>
+        <v>286411</v>
       </c>
       <c r="R27" t="n">
-        <v>6508726</v>
+        <v>6507675</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3423,15 +3248,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113399457</v>
+        <v>113399422</v>
       </c>
       <c r="B28" t="n">
-        <v>96283</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3439,21 +3259,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3463,10 +3283,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>286398</v>
+        <v>286408</v>
       </c>
       <c r="R28" t="n">
-        <v>6508131</v>
+        <v>6507719</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3499,6 +3319,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3525,15 +3350,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113399464</v>
+        <v>113399423</v>
       </c>
       <c r="B29" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3541,21 +3361,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3565,10 +3385,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>286444</v>
+        <v>286427</v>
       </c>
       <c r="R29" t="n">
-        <v>6508164</v>
+        <v>6507789</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3601,6 +3421,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3627,19 +3452,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113399430</v>
+        <v>113399424</v>
       </c>
       <c r="B30" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3667,10 +3487,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>286477</v>
+        <v>286495</v>
       </c>
       <c r="R30" t="n">
-        <v>6508348</v>
+        <v>6508076</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3734,15 +3554,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113399404</v>
+        <v>113399425</v>
       </c>
       <c r="B31" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3750,21 +3565,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3774,10 +3589,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>286719</v>
+        <v>286469</v>
       </c>
       <c r="R31" t="n">
-        <v>6508879</v>
+        <v>6508059</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3810,6 +3625,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3836,19 +3656,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113399436</v>
+        <v>113399426</v>
       </c>
       <c r="B32" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3876,10 +3691,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>286684</v>
+        <v>286454</v>
       </c>
       <c r="R32" t="n">
-        <v>6508737</v>
+        <v>6508073</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3943,15 +3758,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113399412</v>
+        <v>113399427</v>
       </c>
       <c r="B33" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3959,21 +3769,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3983,10 +3793,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>286668</v>
+        <v>286421</v>
       </c>
       <c r="R33" t="n">
-        <v>6508839</v>
+        <v>6508051</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4019,6 +3829,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4045,19 +3860,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113399422</v>
+        <v>113399428</v>
       </c>
       <c r="B34" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4085,10 +3895,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>286408</v>
+        <v>286459</v>
       </c>
       <c r="R34" t="n">
-        <v>6507719</v>
+        <v>6508160</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4152,32 +3962,27 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113399409</v>
+        <v>113399429</v>
       </c>
       <c r="B35" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4192,10 +3997,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>286460</v>
+        <v>286485</v>
       </c>
       <c r="R35" t="n">
-        <v>6508705</v>
+        <v>6508336</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4232,7 +4037,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4259,19 +4064,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113399438</v>
+        <v>113399430</v>
       </c>
       <c r="B36" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4299,10 +4099,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>286835</v>
+        <v>286477</v>
       </c>
       <c r="R36" t="n">
-        <v>6508956</v>
+        <v>6508348</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4366,19 +4166,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113399437</v>
+        <v>113399431</v>
       </c>
       <c r="B37" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4406,10 +4201,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>286714</v>
+        <v>286459</v>
       </c>
       <c r="R37" t="n">
-        <v>6508777</v>
+        <v>6508391</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4473,19 +4268,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113399420</v>
+        <v>113399432</v>
       </c>
       <c r="B38" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4513,10 +4303,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>286325</v>
+        <v>286495</v>
       </c>
       <c r="R38" t="n">
-        <v>6507609</v>
+        <v>6508424</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4580,15 +4370,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113399461</v>
+        <v>113399433</v>
       </c>
       <c r="B39" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4596,21 +4381,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4620,10 +4405,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>286239</v>
+        <v>286505</v>
       </c>
       <c r="R39" t="n">
-        <v>6507778</v>
+        <v>6508433</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4656,6 +4441,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4682,19 +4472,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113399413</v>
+        <v>113399434</v>
       </c>
       <c r="B40" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4722,10 +4507,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>286327</v>
+        <v>286602</v>
       </c>
       <c r="R40" t="n">
-        <v>6508012</v>
+        <v>6508623</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4789,19 +4574,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113399427</v>
+        <v>113399435</v>
       </c>
       <c r="B41" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4829,10 +4609,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>286421</v>
+        <v>286667</v>
       </c>
       <c r="R41" t="n">
-        <v>6508051</v>
+        <v>6508726</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4896,19 +4676,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113399421</v>
+        <v>113399436</v>
       </c>
       <c r="B42" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4936,10 +4711,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>286411</v>
+        <v>286684</v>
       </c>
       <c r="R42" t="n">
-        <v>6507675</v>
+        <v>6508737</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5003,15 +4778,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113399456</v>
+        <v>113399437</v>
       </c>
       <c r="B43" t="n">
-        <v>96283</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5019,21 +4789,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5043,10 +4813,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>286522</v>
+        <v>286714</v>
       </c>
       <c r="R43" t="n">
-        <v>6508764</v>
+        <v>6508777</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5079,6 +4849,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5105,15 +4880,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113399411</v>
+        <v>113399438</v>
       </c>
       <c r="B44" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5121,21 +4891,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5145,10 +4915,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>286712</v>
+        <v>286835</v>
       </c>
       <c r="R44" t="n">
-        <v>6508906</v>
+        <v>6508956</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5181,6 +4951,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5207,19 +4982,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113399424</v>
+        <v>113399439</v>
       </c>
       <c r="B45" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5247,10 +5017,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>286495</v>
+        <v>286834</v>
       </c>
       <c r="R45" t="n">
-        <v>6508076</v>
+        <v>6508948</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5314,19 +5084,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113399443</v>
+        <v>113399440</v>
       </c>
       <c r="B46" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5354,10 +5119,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>286466</v>
+        <v>286483</v>
       </c>
       <c r="R46" t="n">
-        <v>6508689</v>
+        <v>6508722</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5394,7 +5159,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5421,37 +5186,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113399448</v>
+        <v>113399441</v>
       </c>
       <c r="B47" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5461,10 +5221,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>286525</v>
+        <v>286510</v>
       </c>
       <c r="R47" t="n">
-        <v>6508258</v>
+        <v>6508675</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5501,7 +5261,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>9 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5528,19 +5288,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113399431</v>
+        <v>113399443</v>
       </c>
       <c r="B48" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5568,10 +5323,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>286459</v>
+        <v>286466</v>
       </c>
       <c r="R48" t="n">
-        <v>6508391</v>
+        <v>6508689</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5608,7 +5363,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5635,15 +5390,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113399414</v>
+        <v>113399408</v>
       </c>
       <c r="B49" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5651,16 +5401,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5675,10 +5425,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>286242</v>
+        <v>286480</v>
       </c>
       <c r="R49" t="n">
-        <v>6507840</v>
+        <v>6508372</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5715,7 +5465,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Rnghack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5742,37 +5492,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113399463</v>
+        <v>113399409</v>
       </c>
       <c r="B50" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5782,10 +5527,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>286229</v>
+        <v>286460</v>
       </c>
       <c r="R50" t="n">
-        <v>6507839</v>
+        <v>6508705</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5820,6 +5565,11 @@
           <t>2023-11-24</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5841,6 +5591,336 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>101642899</v>
+      </c>
+      <c r="B51" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Halekrokarna,Tanum, Boh</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>286830</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6509030</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2022-06-14</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2022-06-14</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ytterslänten södra sidan</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>victoria höglund</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>victoria höglund</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>113399461</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hala, Boh</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>286239</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6507778</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>113399463</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hala, Boh</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>286229</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6507839</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52265-2023 artfynd.xlsx
+++ b/artfynd/A 52265-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113354383</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73679584</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399464</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399410</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399411</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399412</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399455</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399456</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399457</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399458</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399459</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,6 +1897,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399460</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1934,6 +1999,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399404</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2031,6 +2101,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399405</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2128,6 +2203,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73679582</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2230,6 +2310,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399448</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2327,6 +2412,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399449</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2429,6 +2519,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399413</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2531,6 +2626,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399414</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2633,6 +2733,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399415</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2735,6 +2840,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399416</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2837,6 +2947,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399417</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2939,6 +3054,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399418</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3041,6 +3161,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399419</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3143,6 +3268,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399420</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3245,6 +3375,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399421</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3347,6 +3482,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399422</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3449,6 +3589,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399423</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3551,6 +3696,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399424</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3653,6 +3803,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399425</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3755,6 +3910,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399426</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3857,6 +4017,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399427</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3959,6 +4124,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399428</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4061,6 +4231,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399429</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4163,6 +4338,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399430</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4265,6 +4445,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399431</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4367,6 +4552,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399432</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4469,6 +4659,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399433</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4571,6 +4766,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399434</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4673,6 +4873,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399435</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4775,6 +4980,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399436</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4877,6 +5087,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399437</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4979,6 +5194,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399438</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5081,6 +5301,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399439</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5183,6 +5408,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399440</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5285,6 +5515,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399441</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5387,6 +5622,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399443</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5489,6 +5729,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399408</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5591,6 +5836,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399409</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5727,6 +5977,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101642899</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5824,6 +6079,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399461</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5921,8 +6181,67 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399463</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>